--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -218,12 +218,72 @@
   </si>
   <si>
     <t>Nº</t>
+  </si>
+  <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Cruzeiro</t>
+  </si>
+  <si>
+    <t>Grêmio</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Sport Recife</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>['14', '22']</t>
+  </si>
+  <si>
+    <t>['33', '45']</t>
+  </si>
+  <si>
+    <t>['4', '21']</t>
+  </si>
+  <si>
+    <t>['8', '51']</t>
+  </si>
+  <si>
+    <t>['45+3']</t>
+  </si>
+  <si>
+    <t>['75']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -276,11 +336,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -784,6 +845,1036 @@
         <v>66</v>
       </c>
     </row>
+    <row r="2" spans="1:68">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7834314</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45745.77083333334</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <v>2.3</v>
+      </c>
+      <c r="S2">
+        <v>7</v>
+      </c>
+      <c r="T2">
+        <v>1.44</v>
+      </c>
+      <c r="U2">
+        <v>2.63</v>
+      </c>
+      <c r="V2">
+        <v>3.25</v>
+      </c>
+      <c r="W2">
+        <v>1.33</v>
+      </c>
+      <c r="X2">
+        <v>10</v>
+      </c>
+      <c r="Y2">
+        <v>1.06</v>
+      </c>
+      <c r="Z2">
+        <v>1.52</v>
+      </c>
+      <c r="AA2">
+        <v>3.88</v>
+      </c>
+      <c r="AB2">
+        <v>6.4</v>
+      </c>
+      <c r="AC2">
+        <v>1.06</v>
+      </c>
+      <c r="AD2">
+        <v>8.5</v>
+      </c>
+      <c r="AE2">
+        <v>1.38</v>
+      </c>
+      <c r="AF2">
+        <v>3</v>
+      </c>
+      <c r="AG2">
+        <v>2.11</v>
+      </c>
+      <c r="AH2">
+        <v>1.68</v>
+      </c>
+      <c r="AI2">
+        <v>2.1</v>
+      </c>
+      <c r="AJ2">
+        <v>1.67</v>
+      </c>
+      <c r="AK2">
+        <v>1.14</v>
+      </c>
+      <c r="AL2">
+        <v>1.27</v>
+      </c>
+      <c r="AM2">
+        <v>2.2</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>4</v>
+      </c>
+      <c r="AV2">
+        <v>2</v>
+      </c>
+      <c r="AW2">
+        <v>12</v>
+      </c>
+      <c r="AX2">
+        <v>7</v>
+      </c>
+      <c r="AY2">
+        <v>19</v>
+      </c>
+      <c r="AZ2">
+        <v>12</v>
+      </c>
+      <c r="BA2">
+        <v>6</v>
+      </c>
+      <c r="BB2">
+        <v>2</v>
+      </c>
+      <c r="BC2">
+        <v>8</v>
+      </c>
+      <c r="BD2">
+        <v>1.44</v>
+      </c>
+      <c r="BE2">
+        <v>7</v>
+      </c>
+      <c r="BF2">
+        <v>3.05</v>
+      </c>
+      <c r="BG2">
+        <v>1.25</v>
+      </c>
+      <c r="BH2">
+        <v>3.4</v>
+      </c>
+      <c r="BI2">
+        <v>1.44</v>
+      </c>
+      <c r="BJ2">
+        <v>2.55</v>
+      </c>
+      <c r="BK2">
+        <v>1.73</v>
+      </c>
+      <c r="BL2">
+        <v>2</v>
+      </c>
+      <c r="BM2">
+        <v>2.14</v>
+      </c>
+      <c r="BN2">
+        <v>1.62</v>
+      </c>
+      <c r="BO2">
+        <v>2.65</v>
+      </c>
+      <c r="BP2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:68">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>7834316</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="2">
+        <v>45745.77083333334</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>3</v>
+      </c>
+      <c r="O3" t="s">
+        <v>81</v>
+      </c>
+      <c r="P3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q3">
+        <v>2.1</v>
+      </c>
+      <c r="R3">
+        <v>2.2</v>
+      </c>
+      <c r="S3">
+        <v>7</v>
+      </c>
+      <c r="T3">
+        <v>1.44</v>
+      </c>
+      <c r="U3">
+        <v>2.63</v>
+      </c>
+      <c r="V3">
+        <v>3.25</v>
+      </c>
+      <c r="W3">
+        <v>1.33</v>
+      </c>
+      <c r="X3">
+        <v>10</v>
+      </c>
+      <c r="Y3">
+        <v>1.06</v>
+      </c>
+      <c r="Z3">
+        <v>1.55</v>
+      </c>
+      <c r="AA3">
+        <v>3.56</v>
+      </c>
+      <c r="AB3">
+        <v>7</v>
+      </c>
+      <c r="AC3">
+        <v>1.04</v>
+      </c>
+      <c r="AD3">
+        <v>9.5</v>
+      </c>
+      <c r="AE3">
+        <v>1.34</v>
+      </c>
+      <c r="AF3">
+        <v>3.22</v>
+      </c>
+      <c r="AG3">
+        <v>2.09</v>
+      </c>
+      <c r="AH3">
+        <v>1.63</v>
+      </c>
+      <c r="AI3">
+        <v>2.25</v>
+      </c>
+      <c r="AJ3">
+        <v>1.57</v>
+      </c>
+      <c r="AK3">
+        <v>1.1</v>
+      </c>
+      <c r="AL3">
+        <v>1.25</v>
+      </c>
+      <c r="AM3">
+        <v>2.45</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>3</v>
+      </c>
+      <c r="AV3">
+        <v>7</v>
+      </c>
+      <c r="AW3">
+        <v>6</v>
+      </c>
+      <c r="AX3">
+        <v>10</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>20</v>
+      </c>
+      <c r="BA3">
+        <v>2</v>
+      </c>
+      <c r="BB3">
+        <v>6</v>
+      </c>
+      <c r="BC3">
+        <v>8</v>
+      </c>
+      <c r="BD3">
+        <v>1.16</v>
+      </c>
+      <c r="BE3">
+        <v>10.25</v>
+      </c>
+      <c r="BF3">
+        <v>7.4</v>
+      </c>
+      <c r="BG3">
+        <v>1.13</v>
+      </c>
+      <c r="BH3">
+        <v>4.5</v>
+      </c>
+      <c r="BI3">
+        <v>1.28</v>
+      </c>
+      <c r="BJ3">
+        <v>3.05</v>
+      </c>
+      <c r="BK3">
+        <v>1.53</v>
+      </c>
+      <c r="BL3">
+        <v>2.27</v>
+      </c>
+      <c r="BM3">
+        <v>1.93</v>
+      </c>
+      <c r="BN3">
+        <v>1.77</v>
+      </c>
+      <c r="BO3">
+        <v>2.45</v>
+      </c>
+      <c r="BP3">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:68">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>7834317</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45745.77083333334</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4" t="s">
+        <v>82</v>
+      </c>
+      <c r="P4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>1.5</v>
+      </c>
+      <c r="U4">
+        <v>2.5</v>
+      </c>
+      <c r="V4">
+        <v>3.5</v>
+      </c>
+      <c r="W4">
+        <v>1.29</v>
+      </c>
+      <c r="X4">
+        <v>11</v>
+      </c>
+      <c r="Y4">
+        <v>1.05</v>
+      </c>
+      <c r="Z4">
+        <v>2.14</v>
+      </c>
+      <c r="AA4">
+        <v>3.32</v>
+      </c>
+      <c r="AB4">
+        <v>3.33</v>
+      </c>
+      <c r="AC4">
+        <v>1.05</v>
+      </c>
+      <c r="AD4">
+        <v>8.5</v>
+      </c>
+      <c r="AE4">
+        <v>1.42</v>
+      </c>
+      <c r="AF4">
+        <v>2.84</v>
+      </c>
+      <c r="AG4">
+        <v>2</v>
+      </c>
+      <c r="AH4">
+        <v>1.75</v>
+      </c>
+      <c r="AI4">
+        <v>1.95</v>
+      </c>
+      <c r="AJ4">
+        <v>1.8</v>
+      </c>
+      <c r="AK4">
+        <v>1.32</v>
+      </c>
+      <c r="AL4">
+        <v>1.35</v>
+      </c>
+      <c r="AM4">
+        <v>1.61</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>3</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>6</v>
+      </c>
+      <c r="AV4">
+        <v>8</v>
+      </c>
+      <c r="AW4">
+        <v>7</v>
+      </c>
+      <c r="AX4">
+        <v>15</v>
+      </c>
+      <c r="AY4">
+        <v>17</v>
+      </c>
+      <c r="AZ4">
+        <v>31</v>
+      </c>
+      <c r="BA4">
+        <v>1</v>
+      </c>
+      <c r="BB4">
+        <v>11</v>
+      </c>
+      <c r="BC4">
+        <v>12</v>
+      </c>
+      <c r="BD4">
+        <v>1.61</v>
+      </c>
+      <c r="BE4">
+        <v>6.9</v>
+      </c>
+      <c r="BF4">
+        <v>3.05</v>
+      </c>
+      <c r="BG4">
+        <v>1.18</v>
+      </c>
+      <c r="BH4">
+        <v>3.84</v>
+      </c>
+      <c r="BI4">
+        <v>1.39</v>
+      </c>
+      <c r="BJ4">
+        <v>2.67</v>
+      </c>
+      <c r="BK4">
+        <v>1.7</v>
+      </c>
+      <c r="BL4">
+        <v>2.05</v>
+      </c>
+      <c r="BM4">
+        <v>2.12</v>
+      </c>
+      <c r="BN4">
+        <v>1.61</v>
+      </c>
+      <c r="BO4">
+        <v>2.78</v>
+      </c>
+      <c r="BP4">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:68">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>7834319</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45745.77083333334</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5" t="s">
+        <v>83</v>
+      </c>
+      <c r="P5" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q5">
+        <v>2.9</v>
+      </c>
+      <c r="R5">
+        <v>1.95</v>
+      </c>
+      <c r="S5">
+        <v>3.7</v>
+      </c>
+      <c r="T5">
+        <v>1.47</v>
+      </c>
+      <c r="U5">
+        <v>2.45</v>
+      </c>
+      <c r="V5">
+        <v>3.2</v>
+      </c>
+      <c r="W5">
+        <v>1.31</v>
+      </c>
+      <c r="X5">
+        <v>8.75</v>
+      </c>
+      <c r="Y5">
+        <v>1.06</v>
+      </c>
+      <c r="Z5">
+        <v>2.26</v>
+      </c>
+      <c r="AA5">
+        <v>3.09</v>
+      </c>
+      <c r="AB5">
+        <v>3.29</v>
+      </c>
+      <c r="AC5">
+        <v>1.08</v>
+      </c>
+      <c r="AD5">
+        <v>7</v>
+      </c>
+      <c r="AE5">
+        <v>1.41</v>
+      </c>
+      <c r="AF5">
+        <v>2.65</v>
+      </c>
+      <c r="AG5">
+        <v>2.1</v>
+      </c>
+      <c r="AH5">
+        <v>1.67</v>
+      </c>
+      <c r="AI5">
+        <v>1.95</v>
+      </c>
+      <c r="AJ5">
+        <v>1.73</v>
+      </c>
+      <c r="AK5">
+        <v>1.33</v>
+      </c>
+      <c r="AL5">
+        <v>1.34</v>
+      </c>
+      <c r="AM5">
+        <v>1.58</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>3</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>4</v>
+      </c>
+      <c r="AV5">
+        <v>2</v>
+      </c>
+      <c r="AW5">
+        <v>2</v>
+      </c>
+      <c r="AX5">
+        <v>14</v>
+      </c>
+      <c r="AY5">
+        <v>6</v>
+      </c>
+      <c r="AZ5">
+        <v>22</v>
+      </c>
+      <c r="BA5">
+        <v>4</v>
+      </c>
+      <c r="BB5">
+        <v>5</v>
+      </c>
+      <c r="BC5">
+        <v>9</v>
+      </c>
+      <c r="BD5">
+        <v>1.94</v>
+      </c>
+      <c r="BE5">
+        <v>6.55</v>
+      </c>
+      <c r="BF5">
+        <v>2.35</v>
+      </c>
+      <c r="BG5">
+        <v>1.22</v>
+      </c>
+      <c r="BH5">
+        <v>3.5</v>
+      </c>
+      <c r="BI5">
+        <v>1.44</v>
+      </c>
+      <c r="BJ5">
+        <v>2.51</v>
+      </c>
+      <c r="BK5">
+        <v>1.77</v>
+      </c>
+      <c r="BL5">
+        <v>1.93</v>
+      </c>
+      <c r="BM5">
+        <v>2.27</v>
+      </c>
+      <c r="BN5">
+        <v>1.53</v>
+      </c>
+      <c r="BO5">
+        <v>2.97</v>
+      </c>
+      <c r="BP5">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:68">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>7834320</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45745.77083333334</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P6" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q6">
+        <v>2.75</v>
+      </c>
+      <c r="R6">
+        <v>2.05</v>
+      </c>
+      <c r="S6">
+        <v>4.33</v>
+      </c>
+      <c r="T6">
+        <v>1.44</v>
+      </c>
+      <c r="U6">
+        <v>2.63</v>
+      </c>
+      <c r="V6">
+        <v>3.25</v>
+      </c>
+      <c r="W6">
+        <v>1.33</v>
+      </c>
+      <c r="X6">
+        <v>10</v>
+      </c>
+      <c r="Y6">
+        <v>1.06</v>
+      </c>
+      <c r="Z6">
+        <v>2.04</v>
+      </c>
+      <c r="AA6">
+        <v>3.29</v>
+      </c>
+      <c r="AB6">
+        <v>3.64</v>
+      </c>
+      <c r="AC6">
+        <v>1.04</v>
+      </c>
+      <c r="AD6">
+        <v>9.5</v>
+      </c>
+      <c r="AE6">
+        <v>1.37</v>
+      </c>
+      <c r="AF6">
+        <v>3.09</v>
+      </c>
+      <c r="AG6">
+        <v>2.2</v>
+      </c>
+      <c r="AH6">
+        <v>1.61</v>
+      </c>
+      <c r="AI6">
+        <v>1.95</v>
+      </c>
+      <c r="AJ6">
+        <v>1.8</v>
+      </c>
+      <c r="AK6">
+        <v>1.27</v>
+      </c>
+      <c r="AL6">
+        <v>1.33</v>
+      </c>
+      <c r="AM6">
+        <v>1.72</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>3</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>5</v>
+      </c>
+      <c r="AV6">
+        <v>6</v>
+      </c>
+      <c r="AW6">
+        <v>5</v>
+      </c>
+      <c r="AX6">
+        <v>8</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
+        <v>16</v>
+      </c>
+      <c r="BA6">
+        <v>3</v>
+      </c>
+      <c r="BB6">
+        <v>5</v>
+      </c>
+      <c r="BC6">
+        <v>8</v>
+      </c>
+      <c r="BD6">
+        <v>1.82</v>
+      </c>
+      <c r="BE6">
+        <v>6.65</v>
+      </c>
+      <c r="BF6">
+        <v>2.54</v>
+      </c>
+      <c r="BG6">
+        <v>1.19</v>
+      </c>
+      <c r="BH6">
+        <v>3.8</v>
+      </c>
+      <c r="BI6">
+        <v>1.39</v>
+      </c>
+      <c r="BJ6">
+        <v>2.67</v>
+      </c>
+      <c r="BK6">
+        <v>1.73</v>
+      </c>
+      <c r="BL6">
+        <v>2</v>
+      </c>
+      <c r="BM6">
+        <v>2.14</v>
+      </c>
+      <c r="BN6">
+        <v>1.6</v>
+      </c>
+      <c r="BO6">
+        <v>2.81</v>
+      </c>
+      <c r="BP6">
+        <v>1.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -241,6 +241,9 @@
     <t>Juventude</t>
   </si>
   <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
@@ -256,6 +259,9 @@
     <t>Vitória</t>
   </si>
   <si>
+    <t>Internacional</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -271,10 +277,16 @@
     <t>['8', '51']</t>
   </si>
   <si>
+    <t>['54']</t>
+  </si>
+  <si>
     <t>['45+3']</t>
   </si>
   <si>
     <t>['75']</t>
+  </si>
+  <si>
+    <t>['34']</t>
   </si>
 </sst>
 </file>
@@ -636,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BP7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -868,7 +880,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -889,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1074,7 +1086,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1095,10 +1107,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q3">
         <v>2.1</v>
@@ -1280,7 +1292,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1301,10 +1313,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1486,7 +1498,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1507,10 +1519,10 @@
         <v>2</v>
       </c>
       <c r="O5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q5">
         <v>2.9</v>
@@ -1692,7 +1704,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1713,10 +1725,10 @@
         <v>2</v>
       </c>
       <c r="O6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -1873,6 +1885,212 @@
       </c>
       <c r="BP6">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:68">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7834311</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45745.875</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7">
+        <v>2.5</v>
+      </c>
+      <c r="R7">
+        <v>2.05</v>
+      </c>
+      <c r="S7">
+        <v>5.5</v>
+      </c>
+      <c r="T7">
+        <v>1.4</v>
+      </c>
+      <c r="U7">
+        <v>2.75</v>
+      </c>
+      <c r="V7">
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <v>1.36</v>
+      </c>
+      <c r="X7">
+        <v>8</v>
+      </c>
+      <c r="Y7">
+        <v>1.08</v>
+      </c>
+      <c r="Z7">
+        <v>1.7</v>
+      </c>
+      <c r="AA7">
+        <v>3.64</v>
+      </c>
+      <c r="AB7">
+        <v>4.8</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>1.98</v>
+      </c>
+      <c r="AH7">
+        <v>1.77</v>
+      </c>
+      <c r="AI7">
+        <v>2.1</v>
+      </c>
+      <c r="AJ7">
+        <v>1.67</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>5</v>
+      </c>
+      <c r="AV7">
+        <v>2</v>
+      </c>
+      <c r="AW7">
+        <v>12</v>
+      </c>
+      <c r="AX7">
+        <v>2</v>
+      </c>
+      <c r="AY7">
+        <v>19</v>
+      </c>
+      <c r="AZ7">
+        <v>5</v>
+      </c>
+      <c r="BA7">
+        <v>4</v>
+      </c>
+      <c r="BB7">
+        <v>2</v>
+      </c>
+      <c r="BC7">
+        <v>6</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>1.83</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="101">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -244,6 +244,15 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
+    <t>Bahia</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
@@ -262,6 +271,15 @@
     <t>Internacional</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -280,6 +298,12 @@
     <t>['54']</t>
   </si>
   <si>
+    <t>['53', '78']</t>
+  </si>
+  <si>
+    <t>['45+1']</t>
+  </si>
+  <si>
     <t>['45+3']</t>
   </si>
   <si>
@@ -287,6 +311,12 @@
   </si>
   <si>
     <t>['34']</t>
+  </si>
+  <si>
+    <t>['21']</t>
+  </si>
+  <si>
+    <t>['90']</t>
   </si>
 </sst>
 </file>
@@ -648,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP7"/>
+  <dimension ref="A1:BP10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -880,7 +910,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -901,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1086,7 +1116,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1107,10 +1137,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="P3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="Q3">
         <v>2.1</v>
@@ -1292,7 +1322,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1313,10 +1343,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1498,7 +1528,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1519,10 +1549,10 @@
         <v>2</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="P5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Q5">
         <v>2.9</v>
@@ -1704,7 +1734,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1725,10 +1755,10 @@
         <v>2</v>
       </c>
       <c r="O6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="P6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -1910,7 +1940,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1931,10 +1961,10 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2091,6 +2121,624 @@
       </c>
       <c r="BP7">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>7834313</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45746.66666666666</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q8">
+        <v>2.3</v>
+      </c>
+      <c r="R8">
+        <v>2.2</v>
+      </c>
+      <c r="S8">
+        <v>5.5</v>
+      </c>
+      <c r="T8">
+        <v>1.4</v>
+      </c>
+      <c r="U8">
+        <v>2.75</v>
+      </c>
+      <c r="V8">
+        <v>3</v>
+      </c>
+      <c r="W8">
+        <v>1.36</v>
+      </c>
+      <c r="X8">
+        <v>8</v>
+      </c>
+      <c r="Y8">
+        <v>1.08</v>
+      </c>
+      <c r="Z8">
+        <v>1.69</v>
+      </c>
+      <c r="AA8">
+        <v>3.45</v>
+      </c>
+      <c r="AB8">
+        <v>5.3</v>
+      </c>
+      <c r="AC8">
+        <v>1.06</v>
+      </c>
+      <c r="AD8">
+        <v>8.5</v>
+      </c>
+      <c r="AE8">
+        <v>1.3</v>
+      </c>
+      <c r="AF8">
+        <v>3.4</v>
+      </c>
+      <c r="AG8">
+        <v>1.94</v>
+      </c>
+      <c r="AH8">
+        <v>1.8</v>
+      </c>
+      <c r="AI8">
+        <v>1.91</v>
+      </c>
+      <c r="AJ8">
+        <v>1.91</v>
+      </c>
+      <c r="AK8">
+        <v>1.17</v>
+      </c>
+      <c r="AL8">
+        <v>1.26</v>
+      </c>
+      <c r="AM8">
+        <v>2.1</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>4</v>
+      </c>
+      <c r="AV8">
+        <v>6</v>
+      </c>
+      <c r="AW8">
+        <v>10</v>
+      </c>
+      <c r="AX8">
+        <v>8</v>
+      </c>
+      <c r="AY8">
+        <v>18</v>
+      </c>
+      <c r="AZ8">
+        <v>17</v>
+      </c>
+      <c r="BA8">
+        <v>2</v>
+      </c>
+      <c r="BB8">
+        <v>2</v>
+      </c>
+      <c r="BC8">
+        <v>4</v>
+      </c>
+      <c r="BD8">
+        <v>1.36</v>
+      </c>
+      <c r="BE8">
+        <v>7.5</v>
+      </c>
+      <c r="BF8">
+        <v>3.4</v>
+      </c>
+      <c r="BG8">
+        <v>1.25</v>
+      </c>
+      <c r="BH8">
+        <v>3.4</v>
+      </c>
+      <c r="BI8">
+        <v>1.44</v>
+      </c>
+      <c r="BJ8">
+        <v>2.55</v>
+      </c>
+      <c r="BK8">
+        <v>1.73</v>
+      </c>
+      <c r="BL8">
+        <v>2</v>
+      </c>
+      <c r="BM8">
+        <v>2.12</v>
+      </c>
+      <c r="BN8">
+        <v>1.63</v>
+      </c>
+      <c r="BO8">
+        <v>2.65</v>
+      </c>
+      <c r="BP8">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:68">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>7834312</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>45746.77083333334</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
+      </c>
+      <c r="H9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>3</v>
+      </c>
+      <c r="O9" t="s">
+        <v>94</v>
+      </c>
+      <c r="P9" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q9">
+        <v>3</v>
+      </c>
+      <c r="R9">
+        <v>2.05</v>
+      </c>
+      <c r="S9">
+        <v>3.75</v>
+      </c>
+      <c r="T9">
+        <v>1.5</v>
+      </c>
+      <c r="U9">
+        <v>2.5</v>
+      </c>
+      <c r="V9">
+        <v>3.4</v>
+      </c>
+      <c r="W9">
+        <v>1.3</v>
+      </c>
+      <c r="X9">
+        <v>10</v>
+      </c>
+      <c r="Y9">
+        <v>1.06</v>
+      </c>
+      <c r="Z9">
+        <v>2.45</v>
+      </c>
+      <c r="AA9">
+        <v>3.18</v>
+      </c>
+      <c r="AB9">
+        <v>2.88</v>
+      </c>
+      <c r="AC9">
+        <v>1.08</v>
+      </c>
+      <c r="AD9">
+        <v>7.5</v>
+      </c>
+      <c r="AE9">
+        <v>1.42</v>
+      </c>
+      <c r="AF9">
+        <v>2.85</v>
+      </c>
+      <c r="AG9">
+        <v>2.1</v>
+      </c>
+      <c r="AH9">
+        <v>1.67</v>
+      </c>
+      <c r="AI9">
+        <v>1.91</v>
+      </c>
+      <c r="AJ9">
+        <v>1.91</v>
+      </c>
+      <c r="AK9">
+        <v>1.39</v>
+      </c>
+      <c r="AL9">
+        <v>1.34</v>
+      </c>
+      <c r="AM9">
+        <v>1.51</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>3</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>6</v>
+      </c>
+      <c r="AV9">
+        <v>3</v>
+      </c>
+      <c r="AW9">
+        <v>7</v>
+      </c>
+      <c r="AX9">
+        <v>9</v>
+      </c>
+      <c r="AY9">
+        <v>13</v>
+      </c>
+      <c r="AZ9">
+        <v>16</v>
+      </c>
+      <c r="BA9">
+        <v>2</v>
+      </c>
+      <c r="BB9">
+        <v>3</v>
+      </c>
+      <c r="BC9">
+        <v>5</v>
+      </c>
+      <c r="BD9">
+        <v>2.16</v>
+      </c>
+      <c r="BE9">
+        <v>6.4</v>
+      </c>
+      <c r="BF9">
+        <v>2.11</v>
+      </c>
+      <c r="BG9">
+        <v>1.25</v>
+      </c>
+      <c r="BH9">
+        <v>3.28</v>
+      </c>
+      <c r="BI9">
+        <v>1.49</v>
+      </c>
+      <c r="BJ9">
+        <v>2.38</v>
+      </c>
+      <c r="BK9">
+        <v>1.85</v>
+      </c>
+      <c r="BL9">
+        <v>1.85</v>
+      </c>
+      <c r="BM9">
+        <v>2.42</v>
+      </c>
+      <c r="BN9">
+        <v>1.47</v>
+      </c>
+      <c r="BO9">
+        <v>3.2</v>
+      </c>
+      <c r="BP9">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:68">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>7834318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2">
+        <v>45746.83333333334</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10" t="s">
+        <v>95</v>
+      </c>
+      <c r="P10" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q10">
+        <v>2.6</v>
+      </c>
+      <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>4.33</v>
+      </c>
+      <c r="T10">
+        <v>1.4</v>
+      </c>
+      <c r="U10">
+        <v>2.75</v>
+      </c>
+      <c r="V10">
+        <v>2.75</v>
+      </c>
+      <c r="W10">
+        <v>1.4</v>
+      </c>
+      <c r="X10">
+        <v>8</v>
+      </c>
+      <c r="Y10">
+        <v>1.08</v>
+      </c>
+      <c r="Z10">
+        <v>1.95</v>
+      </c>
+      <c r="AA10">
+        <v>3.36</v>
+      </c>
+      <c r="AB10">
+        <v>3.85</v>
+      </c>
+      <c r="AC10">
+        <v>1.05</v>
+      </c>
+      <c r="AD10">
+        <v>9</v>
+      </c>
+      <c r="AE10">
+        <v>1.3</v>
+      </c>
+      <c r="AF10">
+        <v>3.45</v>
+      </c>
+      <c r="AG10">
+        <v>1.87</v>
+      </c>
+      <c r="AH10">
+        <v>1.87</v>
+      </c>
+      <c r="AI10">
+        <v>1.75</v>
+      </c>
+      <c r="AJ10">
+        <v>2</v>
+      </c>
+      <c r="AK10">
+        <v>1.27</v>
+      </c>
+      <c r="AL10">
+        <v>1.3</v>
+      </c>
+      <c r="AM10">
+        <v>1.77</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>1</v>
+      </c>
+      <c r="AQ10">
+        <v>1</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>6</v>
+      </c>
+      <c r="AV10">
+        <v>5</v>
+      </c>
+      <c r="AW10">
+        <v>9</v>
+      </c>
+      <c r="AX10">
+        <v>5</v>
+      </c>
+      <c r="AY10">
+        <v>17</v>
+      </c>
+      <c r="AZ10">
+        <v>13</v>
+      </c>
+      <c r="BA10">
+        <v>3</v>
+      </c>
+      <c r="BB10">
+        <v>5</v>
+      </c>
+      <c r="BC10">
+        <v>8</v>
+      </c>
+      <c r="BD10">
+        <v>1.34</v>
+      </c>
+      <c r="BE10">
+        <v>7.75</v>
+      </c>
+      <c r="BF10">
+        <v>4</v>
+      </c>
+      <c r="BG10">
+        <v>1.16</v>
+      </c>
+      <c r="BH10">
+        <v>4.5</v>
+      </c>
+      <c r="BI10">
+        <v>1.31</v>
+      </c>
+      <c r="BJ10">
+        <v>3</v>
+      </c>
+      <c r="BK10">
+        <v>1.57</v>
+      </c>
+      <c r="BL10">
+        <v>2.2</v>
+      </c>
+      <c r="BM10">
+        <v>1.98</v>
+      </c>
+      <c r="BN10">
+        <v>1.7</v>
+      </c>
+      <c r="BO10">
+        <v>2.6</v>
+      </c>
+      <c r="BP10">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="105">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -253,6 +253,9 @@
     <t>Bahia</t>
   </si>
   <si>
+    <t>Bragantino</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Ceará</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
@@ -304,6 +310,9 @@
     <t>['45+1']</t>
   </si>
   <si>
+    <t>['45+1', '90+3']</t>
+  </si>
+  <si>
     <t>['45+3']</t>
   </si>
   <si>
@@ -317,6 +326,9 @@
   </si>
   <si>
     <t>['90']</t>
+  </si>
+  <si>
+    <t>['12', '23']</t>
   </si>
 </sst>
 </file>
@@ -678,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP10"/>
+  <dimension ref="A1:BP11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -910,7 +922,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -931,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -1116,7 +1128,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1137,10 +1149,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q3">
         <v>2.1</v>
@@ -1322,7 +1334,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1343,10 +1355,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1528,7 +1540,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1549,10 +1561,10 @@
         <v>2</v>
       </c>
       <c r="O5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q5">
         <v>2.9</v>
@@ -1734,7 +1746,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1755,10 +1767,10 @@
         <v>2</v>
       </c>
       <c r="O6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q6">
         <v>2.75</v>
@@ -1940,7 +1952,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1961,10 +1973,10 @@
         <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2146,7 +2158,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2167,10 +2179,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q8">
         <v>2.3</v>
@@ -2352,7 +2364,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2373,10 +2385,10 @@
         <v>3</v>
       </c>
       <c r="O9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2558,7 +2570,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2579,10 +2591,10 @@
         <v>2</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -2739,6 +2751,212 @@
       </c>
       <c r="BP10">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:68">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>7834315</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="2">
+        <v>45747.83333333334</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
+      <c r="O11" t="s">
+        <v>98</v>
+      </c>
+      <c r="P11" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11">
+        <v>2.88</v>
+      </c>
+      <c r="R11">
+        <v>2.05</v>
+      </c>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11">
+        <v>1.44</v>
+      </c>
+      <c r="U11">
+        <v>2.63</v>
+      </c>
+      <c r="V11">
+        <v>3.4</v>
+      </c>
+      <c r="W11">
+        <v>1.3</v>
+      </c>
+      <c r="X11">
+        <v>10</v>
+      </c>
+      <c r="Y11">
+        <v>1.06</v>
+      </c>
+      <c r="Z11">
+        <v>2.11</v>
+      </c>
+      <c r="AA11">
+        <v>3.15</v>
+      </c>
+      <c r="AB11">
+        <v>3.6</v>
+      </c>
+      <c r="AC11">
+        <v>1.07</v>
+      </c>
+      <c r="AD11">
+        <v>8</v>
+      </c>
+      <c r="AE11">
+        <v>1.38</v>
+      </c>
+      <c r="AF11">
+        <v>3</v>
+      </c>
+      <c r="AG11">
+        <v>2.11</v>
+      </c>
+      <c r="AH11">
+        <v>1.73</v>
+      </c>
+      <c r="AI11">
+        <v>1.91</v>
+      </c>
+      <c r="AJ11">
+        <v>1.91</v>
+      </c>
+      <c r="AK11">
+        <v>1.28</v>
+      </c>
+      <c r="AL11">
+        <v>1.33</v>
+      </c>
+      <c r="AM11">
+        <v>1.7</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>8</v>
+      </c>
+      <c r="AV11">
+        <v>7</v>
+      </c>
+      <c r="AW11">
+        <v>11</v>
+      </c>
+      <c r="AX11">
+        <v>7</v>
+      </c>
+      <c r="AY11">
+        <v>23</v>
+      </c>
+      <c r="AZ11">
+        <v>14</v>
+      </c>
+      <c r="BA11">
+        <v>9</v>
+      </c>
+      <c r="BB11">
+        <v>2</v>
+      </c>
+      <c r="BC11">
+        <v>11</v>
+      </c>
+      <c r="BD11">
+        <v>1.94</v>
+      </c>
+      <c r="BE11">
+        <v>6.8</v>
+      </c>
+      <c r="BF11">
+        <v>2.32</v>
+      </c>
+      <c r="BG11">
+        <v>1.12</v>
+      </c>
+      <c r="BH11">
+        <v>4.8</v>
+      </c>
+      <c r="BI11">
+        <v>1.26</v>
+      </c>
+      <c r="BJ11">
+        <v>3.22</v>
+      </c>
+      <c r="BK11">
+        <v>1.49</v>
+      </c>
+      <c r="BL11">
+        <v>2.38</v>
+      </c>
+      <c r="BM11">
+        <v>1.84</v>
+      </c>
+      <c r="BN11">
+        <v>1.86</v>
+      </c>
+      <c r="BO11">
+        <v>2.32</v>
+      </c>
+      <c r="BP11">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="107">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -256,6 +256,12 @@
     <t>Bragantino</t>
   </si>
   <si>
+    <t>Ceará</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
@@ -280,12 +286,6 @@
     <t>Santos</t>
   </si>
   <si>
-    <t>Corinthians</t>
-  </si>
-  <si>
-    <t>Ceará</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>['45+1', '90+3']</t>
+  </si>
+  <si>
+    <t>['26', '90+5']</t>
+  </si>
+  <si>
+    <t>['12', '27', '90+1']</t>
   </si>
   <si>
     <t>['45+3']</t>
@@ -690,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP11"/>
+  <dimension ref="A1:BP13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -922,7 +928,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1128,7 +1134,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1152,7 +1158,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q3">
         <v>2.1</v>
@@ -1334,7 +1340,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1358,7 +1364,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1540,7 +1546,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1746,7 +1752,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1952,7 +1958,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1976,7 +1982,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2158,7 +2164,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2364,7 +2370,7 @@
         <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2388,7 +2394,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2570,7 +2576,7 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I10">
         <v>1</v>
@@ -2594,7 +2600,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -2776,7 +2782,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -2800,7 +2806,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -2957,6 +2963,418 @@
       </c>
       <c r="BP11">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:68">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>7834329</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="2">
+        <v>45752.77083333334</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>99</v>
+      </c>
+      <c r="P12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12">
+        <v>2.05</v>
+      </c>
+      <c r="S12">
+        <v>4</v>
+      </c>
+      <c r="T12">
+        <v>1.5</v>
+      </c>
+      <c r="U12">
+        <v>2.5</v>
+      </c>
+      <c r="V12">
+        <v>3.4</v>
+      </c>
+      <c r="W12">
+        <v>1.3</v>
+      </c>
+      <c r="X12">
+        <v>10</v>
+      </c>
+      <c r="Y12">
+        <v>1.06</v>
+      </c>
+      <c r="Z12">
+        <v>2.65</v>
+      </c>
+      <c r="AA12">
+        <v>3.18</v>
+      </c>
+      <c r="AB12">
+        <v>2.65</v>
+      </c>
+      <c r="AC12">
+        <v>1.08</v>
+      </c>
+      <c r="AD12">
+        <v>7.5</v>
+      </c>
+      <c r="AE12">
+        <v>1.4</v>
+      </c>
+      <c r="AF12">
+        <v>2.9</v>
+      </c>
+      <c r="AG12">
+        <v>2.15</v>
+      </c>
+      <c r="AH12">
+        <v>1.67</v>
+      </c>
+      <c r="AI12">
+        <v>1.95</v>
+      </c>
+      <c r="AJ12">
+        <v>1.8</v>
+      </c>
+      <c r="AK12">
+        <v>1.35</v>
+      </c>
+      <c r="AL12">
+        <v>1.33</v>
+      </c>
+      <c r="AM12">
+        <v>1.58</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>3</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>7</v>
+      </c>
+      <c r="AV12">
+        <v>4</v>
+      </c>
+      <c r="AW12">
+        <v>6</v>
+      </c>
+      <c r="AX12">
+        <v>9</v>
+      </c>
+      <c r="AY12">
+        <v>13</v>
+      </c>
+      <c r="AZ12">
+        <v>13</v>
+      </c>
+      <c r="BA12">
+        <v>3</v>
+      </c>
+      <c r="BB12">
+        <v>10</v>
+      </c>
+      <c r="BC12">
+        <v>13</v>
+      </c>
+      <c r="BD12">
+        <v>1.68</v>
+      </c>
+      <c r="BE12">
+        <v>7</v>
+      </c>
+      <c r="BF12">
+        <v>2.55</v>
+      </c>
+      <c r="BG12">
+        <v>1.15</v>
+      </c>
+      <c r="BH12">
+        <v>4.6</v>
+      </c>
+      <c r="BI12">
+        <v>1.29</v>
+      </c>
+      <c r="BJ12">
+        <v>3.1</v>
+      </c>
+      <c r="BK12">
+        <v>1.53</v>
+      </c>
+      <c r="BL12">
+        <v>2.25</v>
+      </c>
+      <c r="BM12">
+        <v>1.93</v>
+      </c>
+      <c r="BN12">
+        <v>1.73</v>
+      </c>
+      <c r="BO12">
+        <v>2.5</v>
+      </c>
+      <c r="BP12">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:68">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>7834323</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="2">
+        <v>45752.77083333334</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>3</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>3</v>
+      </c>
+      <c r="O13" t="s">
+        <v>100</v>
+      </c>
+      <c r="P13" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q13">
+        <v>2.25</v>
+      </c>
+      <c r="R13">
+        <v>2.2</v>
+      </c>
+      <c r="S13">
+        <v>5.5</v>
+      </c>
+      <c r="T13">
+        <v>1.44</v>
+      </c>
+      <c r="U13">
+        <v>2.63</v>
+      </c>
+      <c r="V13">
+        <v>3</v>
+      </c>
+      <c r="W13">
+        <v>1.36</v>
+      </c>
+      <c r="X13">
+        <v>9</v>
+      </c>
+      <c r="Y13">
+        <v>1.07</v>
+      </c>
+      <c r="Z13">
+        <v>1.62</v>
+      </c>
+      <c r="AA13">
+        <v>3.88</v>
+      </c>
+      <c r="AB13">
+        <v>5.1</v>
+      </c>
+      <c r="AC13">
+        <v>1.06</v>
+      </c>
+      <c r="AD13">
+        <v>8.5</v>
+      </c>
+      <c r="AE13">
+        <v>1.35</v>
+      </c>
+      <c r="AF13">
+        <v>3.1</v>
+      </c>
+      <c r="AG13">
+        <v>1.85</v>
+      </c>
+      <c r="AH13">
+        <v>1.85</v>
+      </c>
+      <c r="AI13">
+        <v>2</v>
+      </c>
+      <c r="AJ13">
+        <v>1.75</v>
+      </c>
+      <c r="AK13">
+        <v>1.14</v>
+      </c>
+      <c r="AL13">
+        <v>1.27</v>
+      </c>
+      <c r="AM13">
+        <v>2.2</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>3</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>4</v>
+      </c>
+      <c r="AV13">
+        <v>4</v>
+      </c>
+      <c r="AW13">
+        <v>3</v>
+      </c>
+      <c r="AX13">
+        <v>7</v>
+      </c>
+      <c r="AY13">
+        <v>8</v>
+      </c>
+      <c r="AZ13">
+        <v>12</v>
+      </c>
+      <c r="BA13">
+        <v>1</v>
+      </c>
+      <c r="BB13">
+        <v>4</v>
+      </c>
+      <c r="BC13">
+        <v>5</v>
+      </c>
+      <c r="BD13">
+        <v>1.49</v>
+      </c>
+      <c r="BE13">
+        <v>6.75</v>
+      </c>
+      <c r="BF13">
+        <v>3.25</v>
+      </c>
+      <c r="BG13">
+        <v>1.16</v>
+      </c>
+      <c r="BH13">
+        <v>4.5</v>
+      </c>
+      <c r="BI13">
+        <v>1.31</v>
+      </c>
+      <c r="BJ13">
+        <v>3</v>
+      </c>
+      <c r="BK13">
+        <v>1.57</v>
+      </c>
+      <c r="BL13">
+        <v>2.15</v>
+      </c>
+      <c r="BM13">
+        <v>1.98</v>
+      </c>
+      <c r="BN13">
+        <v>1.68</v>
+      </c>
+      <c r="BO13">
+        <v>2.6</v>
+      </c>
+      <c r="BP13">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="119">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -262,27 +262,27 @@
     <t>Corinthians</t>
   </si>
   <si>
+    <t>Botafogo</t>
+  </si>
+  <si>
+    <t>Atlético Mineiro</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
-    <t>Atlético Mineiro</t>
-  </si>
-  <si>
-    <t>Fluminense</t>
-  </si>
-  <si>
-    <t>Vitória</t>
-  </si>
-  <si>
-    <t>Internacional</t>
-  </si>
-  <si>
-    <t>Botafogo</t>
-  </si>
-  <si>
     <t>Santos</t>
   </si>
   <si>
@@ -319,6 +319,27 @@
     <t>['12', '27', '90+1']</t>
   </si>
   <si>
+    <t>['24', '62']</t>
+  </si>
+  <si>
+    <t>['35', '90+2']</t>
+  </si>
+  <si>
+    <t>['90+3']</t>
+  </si>
+  <si>
+    <t>['31', '37', '77']</t>
+  </si>
+  <si>
+    <t>['77']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['50', '81']</t>
+  </si>
+  <si>
     <t>['45+3']</t>
   </si>
   <si>
@@ -335,6 +356,21 @@
   </si>
   <si>
     <t>['12', '23']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['62', '87']</t>
+  </si>
+  <si>
+    <t>['33', '90+1']</t>
+  </si>
+  <si>
+    <t>['17', '90']</t>
   </si>
 </sst>
 </file>
@@ -696,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP13"/>
+  <dimension ref="A1:BP21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -928,7 +964,7 @@
         <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1134,7 +1170,7 @@
         <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I3">
         <v>2</v>
@@ -1158,7 +1194,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Q3">
         <v>2.1</v>
@@ -1340,7 +1376,7 @@
         <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -1364,7 +1400,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1546,7 +1582,7 @@
         <v>73</v>
       </c>
       <c r="H5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -1752,7 +1788,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -1958,7 +1994,7 @@
         <v>75</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1982,7 +2018,7 @@
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Q7">
         <v>2.5</v>
@@ -2164,7 +2200,7 @@
         <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -2394,7 +2430,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2600,7 +2636,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -2806,7 +2842,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3117,19 +3153,19 @@
         <v>9</v>
       </c>
       <c r="AY12">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ12">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA12">
         <v>3</v>
       </c>
       <c r="BB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD12">
         <v>1.68</v>
@@ -3375,6 +3411,1654 @@
       </c>
       <c r="BP13">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:68">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>7834322</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2">
+        <v>45752.875</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14" t="s">
+        <v>101</v>
+      </c>
+      <c r="P14" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q14">
+        <v>2.1</v>
+      </c>
+      <c r="R14">
+        <v>2.25</v>
+      </c>
+      <c r="S14">
+        <v>6.5</v>
+      </c>
+      <c r="T14">
+        <v>1.4</v>
+      </c>
+      <c r="U14">
+        <v>2.75</v>
+      </c>
+      <c r="V14">
+        <v>2.75</v>
+      </c>
+      <c r="W14">
+        <v>1.4</v>
+      </c>
+      <c r="X14">
+        <v>8</v>
+      </c>
+      <c r="Y14">
+        <v>1.08</v>
+      </c>
+      <c r="Z14">
+        <v>1.49</v>
+      </c>
+      <c r="AA14">
+        <v>3.96</v>
+      </c>
+      <c r="AB14">
+        <v>6.8</v>
+      </c>
+      <c r="AC14">
+        <v>1.05</v>
+      </c>
+      <c r="AD14">
+        <v>9.5</v>
+      </c>
+      <c r="AE14">
+        <v>1.29</v>
+      </c>
+      <c r="AF14">
+        <v>3.3</v>
+      </c>
+      <c r="AG14">
+        <v>1.87</v>
+      </c>
+      <c r="AH14">
+        <v>1.87</v>
+      </c>
+      <c r="AI14">
+        <v>2.05</v>
+      </c>
+      <c r="AJ14">
+        <v>1.7</v>
+      </c>
+      <c r="AK14">
+        <v>1.12</v>
+      </c>
+      <c r="AL14">
+        <v>1.22</v>
+      </c>
+      <c r="AM14">
+        <v>2.5</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>3</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>7</v>
+      </c>
+      <c r="AV14">
+        <v>4</v>
+      </c>
+      <c r="AW14">
+        <v>10</v>
+      </c>
+      <c r="AX14">
+        <v>12</v>
+      </c>
+      <c r="AY14">
+        <v>22</v>
+      </c>
+      <c r="AZ14">
+        <v>20</v>
+      </c>
+      <c r="BA14">
+        <v>3</v>
+      </c>
+      <c r="BB14">
+        <v>3</v>
+      </c>
+      <c r="BC14">
+        <v>6</v>
+      </c>
+      <c r="BD14">
+        <v>1.3</v>
+      </c>
+      <c r="BE14">
+        <v>7.5</v>
+      </c>
+      <c r="BF14">
+        <v>3.8</v>
+      </c>
+      <c r="BG14">
+        <v>1.27</v>
+      </c>
+      <c r="BH14">
+        <v>3.3</v>
+      </c>
+      <c r="BI14">
+        <v>1.48</v>
+      </c>
+      <c r="BJ14">
+        <v>2.45</v>
+      </c>
+      <c r="BK14">
+        <v>1.77</v>
+      </c>
+      <c r="BL14">
+        <v>1.92</v>
+      </c>
+      <c r="BM14">
+        <v>2.18</v>
+      </c>
+      <c r="BN14">
+        <v>1.58</v>
+      </c>
+      <c r="BO14">
+        <v>2.8</v>
+      </c>
+      <c r="BP14">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:68">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>7834326</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2">
+        <v>45753.66666666666</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>90</v>
+      </c>
+      <c r="P15" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q15">
+        <v>2.75</v>
+      </c>
+      <c r="R15">
+        <v>1.95</v>
+      </c>
+      <c r="S15">
+        <v>5</v>
+      </c>
+      <c r="T15">
+        <v>1.53</v>
+      </c>
+      <c r="U15">
+        <v>2.38</v>
+      </c>
+      <c r="V15">
+        <v>3.75</v>
+      </c>
+      <c r="W15">
+        <v>1.25</v>
+      </c>
+      <c r="X15">
+        <v>11</v>
+      </c>
+      <c r="Y15">
+        <v>1.05</v>
+      </c>
+      <c r="Z15">
+        <v>2.21</v>
+      </c>
+      <c r="AA15">
+        <v>3.23</v>
+      </c>
+      <c r="AB15">
+        <v>3.23</v>
+      </c>
+      <c r="AC15">
+        <v>1.09</v>
+      </c>
+      <c r="AD15">
+        <v>6.5</v>
+      </c>
+      <c r="AE15">
+        <v>1.49</v>
+      </c>
+      <c r="AF15">
+        <v>2.4</v>
+      </c>
+      <c r="AG15">
+        <v>2.05</v>
+      </c>
+      <c r="AH15">
+        <v>1.66</v>
+      </c>
+      <c r="AI15">
+        <v>2.1</v>
+      </c>
+      <c r="AJ15">
+        <v>1.67</v>
+      </c>
+      <c r="AK15">
+        <v>1.23</v>
+      </c>
+      <c r="AL15">
+        <v>1.33</v>
+      </c>
+      <c r="AM15">
+        <v>1.78</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>1</v>
+      </c>
+      <c r="AQ15">
+        <v>1</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>7</v>
+      </c>
+      <c r="AV15">
+        <v>5</v>
+      </c>
+      <c r="AW15">
+        <v>19</v>
+      </c>
+      <c r="AX15">
+        <v>3</v>
+      </c>
+      <c r="AY15">
+        <v>35</v>
+      </c>
+      <c r="AZ15">
+        <v>9</v>
+      </c>
+      <c r="BA15">
+        <v>12</v>
+      </c>
+      <c r="BB15">
+        <v>4</v>
+      </c>
+      <c r="BC15">
+        <v>16</v>
+      </c>
+      <c r="BD15">
+        <v>1.68</v>
+      </c>
+      <c r="BE15">
+        <v>6.4</v>
+      </c>
+      <c r="BF15">
+        <v>2.43</v>
+      </c>
+      <c r="BG15">
+        <v>1.34</v>
+      </c>
+      <c r="BH15">
+        <v>2.9</v>
+      </c>
+      <c r="BI15">
+        <v>1.58</v>
+      </c>
+      <c r="BJ15">
+        <v>2.18</v>
+      </c>
+      <c r="BK15">
+        <v>1.95</v>
+      </c>
+      <c r="BL15">
+        <v>1.75</v>
+      </c>
+      <c r="BM15">
+        <v>2.48</v>
+      </c>
+      <c r="BN15">
+        <v>1.47</v>
+      </c>
+      <c r="BO15">
+        <v>3.2</v>
+      </c>
+      <c r="BP15">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:68">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>7834321</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2">
+        <v>45753.66666666666</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16" t="s">
+        <v>102</v>
+      </c>
+      <c r="P16" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q16">
+        <v>2.6</v>
+      </c>
+      <c r="R16">
+        <v>2.05</v>
+      </c>
+      <c r="S16">
+        <v>5</v>
+      </c>
+      <c r="T16">
+        <v>1.5</v>
+      </c>
+      <c r="U16">
+        <v>2.5</v>
+      </c>
+      <c r="V16">
+        <v>3.4</v>
+      </c>
+      <c r="W16">
+        <v>1.3</v>
+      </c>
+      <c r="X16">
+        <v>10</v>
+      </c>
+      <c r="Y16">
+        <v>1.06</v>
+      </c>
+      <c r="Z16">
+        <v>1.78</v>
+      </c>
+      <c r="AA16">
+        <v>3.41</v>
+      </c>
+      <c r="AB16">
+        <v>4.6</v>
+      </c>
+      <c r="AC16">
+        <v>1.08</v>
+      </c>
+      <c r="AD16">
+        <v>7.5</v>
+      </c>
+      <c r="AE16">
+        <v>1.42</v>
+      </c>
+      <c r="AF16">
+        <v>2.85</v>
+      </c>
+      <c r="AG16">
+        <v>2.2</v>
+      </c>
+      <c r="AH16">
+        <v>1.61</v>
+      </c>
+      <c r="AI16">
+        <v>2</v>
+      </c>
+      <c r="AJ16">
+        <v>1.75</v>
+      </c>
+      <c r="AK16">
+        <v>1.21</v>
+      </c>
+      <c r="AL16">
+        <v>1.31</v>
+      </c>
+      <c r="AM16">
+        <v>1.88</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>3</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>6</v>
+      </c>
+      <c r="AV16">
+        <v>6</v>
+      </c>
+      <c r="AW16">
+        <v>10</v>
+      </c>
+      <c r="AX16">
+        <v>12</v>
+      </c>
+      <c r="AY16">
+        <v>19</v>
+      </c>
+      <c r="AZ16">
+        <v>24</v>
+      </c>
+      <c r="BA16">
+        <v>6</v>
+      </c>
+      <c r="BB16">
+        <v>6</v>
+      </c>
+      <c r="BC16">
+        <v>12</v>
+      </c>
+      <c r="BD16">
+        <v>1.5</v>
+      </c>
+      <c r="BE16">
+        <v>7</v>
+      </c>
+      <c r="BF16">
+        <v>2.8</v>
+      </c>
+      <c r="BG16">
+        <v>1.17</v>
+      </c>
+      <c r="BH16">
+        <v>4.35</v>
+      </c>
+      <c r="BI16">
+        <v>1.3</v>
+      </c>
+      <c r="BJ16">
+        <v>3.15</v>
+      </c>
+      <c r="BK16">
+        <v>1.5</v>
+      </c>
+      <c r="BL16">
+        <v>2.35</v>
+      </c>
+      <c r="BM16">
+        <v>1.8</v>
+      </c>
+      <c r="BN16">
+        <v>1.89</v>
+      </c>
+      <c r="BO16">
+        <v>2.23</v>
+      </c>
+      <c r="BP16">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:68">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>7834325</v>
+      </c>
+      <c r="C17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="2">
+        <v>45753.77083333334</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17" t="s">
+        <v>103</v>
+      </c>
+      <c r="P17" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q17">
+        <v>3.3</v>
+      </c>
+      <c r="R17">
+        <v>1.93</v>
+      </c>
+      <c r="S17">
+        <v>3.25</v>
+      </c>
+      <c r="T17">
+        <v>1.49</v>
+      </c>
+      <c r="U17">
+        <v>2.4</v>
+      </c>
+      <c r="V17">
+        <v>3.25</v>
+      </c>
+      <c r="W17">
+        <v>1.29</v>
+      </c>
+      <c r="X17">
+        <v>9</v>
+      </c>
+      <c r="Y17">
+        <v>1.06</v>
+      </c>
+      <c r="Z17">
+        <v>3.15</v>
+      </c>
+      <c r="AA17">
+        <v>3.2</v>
+      </c>
+      <c r="AB17">
+        <v>2.27</v>
+      </c>
+      <c r="AC17">
+        <v>1.09</v>
+      </c>
+      <c r="AD17">
+        <v>7</v>
+      </c>
+      <c r="AE17">
+        <v>1.42</v>
+      </c>
+      <c r="AF17">
+        <v>2.6</v>
+      </c>
+      <c r="AG17">
+        <v>2.11</v>
+      </c>
+      <c r="AH17">
+        <v>1.62</v>
+      </c>
+      <c r="AI17">
+        <v>1.98</v>
+      </c>
+      <c r="AJ17">
+        <v>1.73</v>
+      </c>
+      <c r="AK17">
+        <v>1.46</v>
+      </c>
+      <c r="AL17">
+        <v>1.35</v>
+      </c>
+      <c r="AM17">
+        <v>1.44</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>1</v>
+      </c>
+      <c r="AQ17">
+        <v>1</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>6</v>
+      </c>
+      <c r="AV17">
+        <v>4</v>
+      </c>
+      <c r="AW17">
+        <v>15</v>
+      </c>
+      <c r="AX17">
+        <v>4</v>
+      </c>
+      <c r="AY17">
+        <v>24</v>
+      </c>
+      <c r="AZ17">
+        <v>10</v>
+      </c>
+      <c r="BA17">
+        <v>8</v>
+      </c>
+      <c r="BB17">
+        <v>1</v>
+      </c>
+      <c r="BC17">
+        <v>9</v>
+      </c>
+      <c r="BD17">
+        <v>2.07</v>
+      </c>
+      <c r="BE17">
+        <v>6.75</v>
+      </c>
+      <c r="BF17">
+        <v>1.9</v>
+      </c>
+      <c r="BG17">
+        <v>1.2</v>
+      </c>
+      <c r="BH17">
+        <v>3.9</v>
+      </c>
+      <c r="BI17">
+        <v>1.36</v>
+      </c>
+      <c r="BJ17">
+        <v>2.8</v>
+      </c>
+      <c r="BK17">
+        <v>1.6</v>
+      </c>
+      <c r="BL17">
+        <v>2.17</v>
+      </c>
+      <c r="BM17">
+        <v>1.96</v>
+      </c>
+      <c r="BN17">
+        <v>1.74</v>
+      </c>
+      <c r="BO17">
+        <v>2.43</v>
+      </c>
+      <c r="BP17">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:68">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>7834327</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="2">
+        <v>45753.77083333334</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>3</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q18">
+        <v>2.5</v>
+      </c>
+      <c r="R18">
+        <v>2.05</v>
+      </c>
+      <c r="S18">
+        <v>5.5</v>
+      </c>
+      <c r="T18">
+        <v>1.5</v>
+      </c>
+      <c r="U18">
+        <v>2.5</v>
+      </c>
+      <c r="V18">
+        <v>3.4</v>
+      </c>
+      <c r="W18">
+        <v>1.3</v>
+      </c>
+      <c r="X18">
+        <v>10</v>
+      </c>
+      <c r="Y18">
+        <v>1.06</v>
+      </c>
+      <c r="Z18">
+        <v>1.77</v>
+      </c>
+      <c r="AA18">
+        <v>3.45</v>
+      </c>
+      <c r="AB18">
+        <v>4.7</v>
+      </c>
+      <c r="AC18">
+        <v>1.07</v>
+      </c>
+      <c r="AD18">
+        <v>8</v>
+      </c>
+      <c r="AE18">
+        <v>1.4</v>
+      </c>
+      <c r="AF18">
+        <v>2.9</v>
+      </c>
+      <c r="AG18">
+        <v>2.25</v>
+      </c>
+      <c r="AH18">
+        <v>1.6</v>
+      </c>
+      <c r="AI18">
+        <v>2.05</v>
+      </c>
+      <c r="AJ18">
+        <v>1.7</v>
+      </c>
+      <c r="AK18">
+        <v>1.2</v>
+      </c>
+      <c r="AL18">
+        <v>1.3</v>
+      </c>
+      <c r="AM18">
+        <v>1.95</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>3</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>12</v>
+      </c>
+      <c r="AV18">
+        <v>2</v>
+      </c>
+      <c r="AW18">
+        <v>13</v>
+      </c>
+      <c r="AX18">
+        <v>5</v>
+      </c>
+      <c r="AY18">
+        <v>33</v>
+      </c>
+      <c r="AZ18">
+        <v>9</v>
+      </c>
+      <c r="BA18">
+        <v>9</v>
+      </c>
+      <c r="BB18">
+        <v>2</v>
+      </c>
+      <c r="BC18">
+        <v>11</v>
+      </c>
+      <c r="BD18">
+        <v>1.5</v>
+      </c>
+      <c r="BE18">
+        <v>6.5</v>
+      </c>
+      <c r="BF18">
+        <v>2.9</v>
+      </c>
+      <c r="BG18">
+        <v>1.3</v>
+      </c>
+      <c r="BH18">
+        <v>3.15</v>
+      </c>
+      <c r="BI18">
+        <v>1.5</v>
+      </c>
+      <c r="BJ18">
+        <v>2.4</v>
+      </c>
+      <c r="BK18">
+        <v>1.8</v>
+      </c>
+      <c r="BL18">
+        <v>1.88</v>
+      </c>
+      <c r="BM18">
+        <v>2.23</v>
+      </c>
+      <c r="BN18">
+        <v>1.56</v>
+      </c>
+      <c r="BO18">
+        <v>2.88</v>
+      </c>
+      <c r="BP18">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:68">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>7834328</v>
+      </c>
+      <c r="C19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2">
+        <v>45753.77083333334</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19">
+        <v>3</v>
+      </c>
+      <c r="O19" t="s">
+        <v>105</v>
+      </c>
+      <c r="P19" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q19">
+        <v>5</v>
+      </c>
+      <c r="R19">
+        <v>2.05</v>
+      </c>
+      <c r="S19">
+        <v>2.6</v>
+      </c>
+      <c r="T19">
+        <v>1.5</v>
+      </c>
+      <c r="U19">
+        <v>2.5</v>
+      </c>
+      <c r="V19">
+        <v>3.4</v>
+      </c>
+      <c r="W19">
+        <v>1.3</v>
+      </c>
+      <c r="X19">
+        <v>10</v>
+      </c>
+      <c r="Y19">
+        <v>1.06</v>
+      </c>
+      <c r="Z19">
+        <v>4.9</v>
+      </c>
+      <c r="AA19">
+        <v>3.71</v>
+      </c>
+      <c r="AB19">
+        <v>1.68</v>
+      </c>
+      <c r="AC19">
+        <v>1.07</v>
+      </c>
+      <c r="AD19">
+        <v>8</v>
+      </c>
+      <c r="AE19">
+        <v>1.4</v>
+      </c>
+      <c r="AF19">
+        <v>2.9</v>
+      </c>
+      <c r="AG19">
+        <v>1.85</v>
+      </c>
+      <c r="AH19">
+        <v>1.89</v>
+      </c>
+      <c r="AI19">
+        <v>2</v>
+      </c>
+      <c r="AJ19">
+        <v>1.75</v>
+      </c>
+      <c r="AK19">
+        <v>1.9</v>
+      </c>
+      <c r="AL19">
+        <v>1.3</v>
+      </c>
+      <c r="AM19">
+        <v>1.21</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>3</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>4</v>
+      </c>
+      <c r="AV19">
+        <v>8</v>
+      </c>
+      <c r="AW19">
+        <v>2</v>
+      </c>
+      <c r="AX19">
+        <v>7</v>
+      </c>
+      <c r="AY19">
+        <v>7</v>
+      </c>
+      <c r="AZ19">
+        <v>15</v>
+      </c>
+      <c r="BA19">
+        <v>2</v>
+      </c>
+      <c r="BB19">
+        <v>6</v>
+      </c>
+      <c r="BC19">
+        <v>8</v>
+      </c>
+      <c r="BD19">
+        <v>2.45</v>
+      </c>
+      <c r="BE19">
+        <v>6.75</v>
+      </c>
+      <c r="BF19">
+        <v>1.65</v>
+      </c>
+      <c r="BG19">
+        <v>1.2</v>
+      </c>
+      <c r="BH19">
+        <v>3.8</v>
+      </c>
+      <c r="BI19">
+        <v>1.37</v>
+      </c>
+      <c r="BJ19">
+        <v>2.8</v>
+      </c>
+      <c r="BK19">
+        <v>1.61</v>
+      </c>
+      <c r="BL19">
+        <v>2.15</v>
+      </c>
+      <c r="BM19">
+        <v>1.96</v>
+      </c>
+      <c r="BN19">
+        <v>1.74</v>
+      </c>
+      <c r="BO19">
+        <v>2.43</v>
+      </c>
+      <c r="BP19">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:68">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>7834330</v>
+      </c>
+      <c r="C20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2">
+        <v>45753.77083333334</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20" t="s">
+        <v>106</v>
+      </c>
+      <c r="P20" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q20">
+        <v>5</v>
+      </c>
+      <c r="R20">
+        <v>2.05</v>
+      </c>
+      <c r="S20">
+        <v>2.5</v>
+      </c>
+      <c r="T20">
+        <v>1.44</v>
+      </c>
+      <c r="U20">
+        <v>2.63</v>
+      </c>
+      <c r="V20">
+        <v>3.4</v>
+      </c>
+      <c r="W20">
+        <v>1.3</v>
+      </c>
+      <c r="X20">
+        <v>10</v>
+      </c>
+      <c r="Y20">
+        <v>1.06</v>
+      </c>
+      <c r="Z20">
+        <v>5.1</v>
+      </c>
+      <c r="AA20">
+        <v>3.45</v>
+      </c>
+      <c r="AB20">
+        <v>1.71</v>
+      </c>
+      <c r="AC20">
+        <v>1.07</v>
+      </c>
+      <c r="AD20">
+        <v>8</v>
+      </c>
+      <c r="AE20">
+        <v>1.38</v>
+      </c>
+      <c r="AF20">
+        <v>2.95</v>
+      </c>
+      <c r="AG20">
+        <v>2.08</v>
+      </c>
+      <c r="AH20">
+        <v>1.7</v>
+      </c>
+      <c r="AI20">
+        <v>2</v>
+      </c>
+      <c r="AJ20">
+        <v>1.75</v>
+      </c>
+      <c r="AK20">
+        <v>1.98</v>
+      </c>
+      <c r="AL20">
+        <v>1.3</v>
+      </c>
+      <c r="AM20">
+        <v>1.19</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>3</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>3</v>
+      </c>
+      <c r="AV20">
+        <v>5</v>
+      </c>
+      <c r="AW20">
+        <v>7</v>
+      </c>
+      <c r="AX20">
+        <v>3</v>
+      </c>
+      <c r="AY20">
+        <v>11</v>
+      </c>
+      <c r="AZ20">
+        <v>8</v>
+      </c>
+      <c r="BA20">
+        <v>6</v>
+      </c>
+      <c r="BB20">
+        <v>3</v>
+      </c>
+      <c r="BC20">
+        <v>9</v>
+      </c>
+      <c r="BD20">
+        <v>2.33</v>
+      </c>
+      <c r="BE20">
+        <v>7</v>
+      </c>
+      <c r="BF20">
+        <v>1.7</v>
+      </c>
+      <c r="BG20">
+        <v>1.21</v>
+      </c>
+      <c r="BH20">
+        <v>3.8</v>
+      </c>
+      <c r="BI20">
+        <v>1.38</v>
+      </c>
+      <c r="BJ20">
+        <v>2.7</v>
+      </c>
+      <c r="BK20">
+        <v>1.63</v>
+      </c>
+      <c r="BL20">
+        <v>2.12</v>
+      </c>
+      <c r="BM20">
+        <v>1.98</v>
+      </c>
+      <c r="BN20">
+        <v>1.72</v>
+      </c>
+      <c r="BO20">
+        <v>2.45</v>
+      </c>
+      <c r="BP20">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:68">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>7834324</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45753.85416666666</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>4</v>
+      </c>
+      <c r="O21" t="s">
+        <v>107</v>
+      </c>
+      <c r="P21" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q21">
+        <v>2.75</v>
+      </c>
+      <c r="R21">
+        <v>2</v>
+      </c>
+      <c r="S21">
+        <v>4.5</v>
+      </c>
+      <c r="T21">
+        <v>1.5</v>
+      </c>
+      <c r="U21">
+        <v>2.5</v>
+      </c>
+      <c r="V21">
+        <v>3.4</v>
+      </c>
+      <c r="W21">
+        <v>1.3</v>
+      </c>
+      <c r="X21">
+        <v>10</v>
+      </c>
+      <c r="Y21">
+        <v>1.06</v>
+      </c>
+      <c r="Z21">
+        <v>2.02</v>
+      </c>
+      <c r="AA21">
+        <v>2.95</v>
+      </c>
+      <c r="AB21">
+        <v>4.3</v>
+      </c>
+      <c r="AC21">
+        <v>1.09</v>
+      </c>
+      <c r="AD21">
+        <v>7</v>
+      </c>
+      <c r="AE21">
+        <v>1.42</v>
+      </c>
+      <c r="AF21">
+        <v>2.8</v>
+      </c>
+      <c r="AG21">
+        <v>2.15</v>
+      </c>
+      <c r="AH21">
+        <v>1.65</v>
+      </c>
+      <c r="AI21">
+        <v>1.95</v>
+      </c>
+      <c r="AJ21">
+        <v>1.8</v>
+      </c>
+      <c r="AK21">
+        <v>1.25</v>
+      </c>
+      <c r="AL21">
+        <v>1.33</v>
+      </c>
+      <c r="AM21">
+        <v>1.73</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>1</v>
+      </c>
+      <c r="AQ21">
+        <v>1</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>7</v>
+      </c>
+      <c r="AV21">
+        <v>4</v>
+      </c>
+      <c r="AW21">
+        <v>15</v>
+      </c>
+      <c r="AX21">
+        <v>7</v>
+      </c>
+      <c r="AY21">
+        <v>29</v>
+      </c>
+      <c r="AZ21">
+        <v>14</v>
+      </c>
+      <c r="BA21">
+        <v>9</v>
+      </c>
+      <c r="BB21">
+        <v>3</v>
+      </c>
+      <c r="BC21">
+        <v>12</v>
+      </c>
+      <c r="BD21">
+        <v>1.58</v>
+      </c>
+      <c r="BE21">
+        <v>6.75</v>
+      </c>
+      <c r="BF21">
+        <v>2.65</v>
+      </c>
+      <c r="BG21">
+        <v>1.3</v>
+      </c>
+      <c r="BH21">
+        <v>3.1</v>
+      </c>
+      <c r="BI21">
+        <v>1.53</v>
+      </c>
+      <c r="BJ21">
+        <v>2.32</v>
+      </c>
+      <c r="BK21">
+        <v>1.87</v>
+      </c>
+      <c r="BL21">
+        <v>1.82</v>
+      </c>
+      <c r="BM21">
+        <v>2.35</v>
+      </c>
+      <c r="BN21">
+        <v>1.5</v>
+      </c>
+      <c r="BO21">
+        <v>3.05</v>
+      </c>
+      <c r="BP21">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="221">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,15 @@
     <t>['45', '72', '77']</t>
   </si>
   <si>
+    <t>['71', '74']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['30', '90+4']</t>
+  </si>
+  <si>
     <t>['75']</t>
   </si>
   <si>
@@ -656,6 +665,18 @@
   </si>
   <si>
     <t>['11', '83']</t>
+  </si>
+  <si>
+    <t>['40', '45+6', '74']</t>
+  </si>
+  <si>
+    <t>['15', '41', '90+2']</t>
+  </si>
+  <si>
+    <t>['36']</t>
+  </si>
+  <si>
+    <t>['26', '40', '69']</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP111"/>
+  <dimension ref="A1:BP117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1351,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ2">
         <v>1.17</v>
@@ -1685,7 +1706,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1763,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ4">
         <v>1.33</v>
@@ -1969,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5">
         <v>0.17</v>
@@ -2097,7 +2118,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2384,7 +2405,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ7">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2715,7 +2736,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2796,7 +2817,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ9">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2921,7 +2942,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3002,7 +3023,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ10">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3127,7 +3148,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3205,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ11">
         <v>0.4</v>
@@ -3414,7 +3435,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4029,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>0.6</v>
@@ -4157,7 +4178,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4363,7 +4384,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4569,7 +4590,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -4647,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18">
         <v>2</v>
@@ -5062,7 +5083,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ20">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5187,7 +5208,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5268,7 +5289,7 @@
         <v>1</v>
       </c>
       <c r="AQ21">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5471,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ22">
         <v>0.83</v>
@@ -5599,7 +5620,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5886,7 +5907,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ24">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR24">
         <v>1.52</v>
@@ -6217,7 +6238,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6423,7 +6444,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6501,10 +6522,10 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ27">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR27">
         <v>1.57</v>
@@ -6629,7 +6650,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -6707,7 +6728,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ28">
         <v>2</v>
@@ -6916,7 +6937,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ29">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR29">
         <v>1.73</v>
@@ -7119,10 +7140,10 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ30">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR30">
         <v>0.8</v>
@@ -7247,7 +7268,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7325,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ31">
         <v>0.5</v>
@@ -7534,7 +7555,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR32">
         <v>1.51</v>
@@ -7659,7 +7680,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7865,7 +7886,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8071,7 +8092,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8277,7 +8298,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -8767,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ38">
         <v>0.5</v>
@@ -9388,7 +9409,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ41">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR41">
         <v>0.97</v>
@@ -9513,7 +9534,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10003,10 +10024,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ44">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR44">
         <v>1.34</v>
@@ -10131,7 +10152,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10415,7 +10436,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>0.83</v>
@@ -10543,7 +10564,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10621,10 +10642,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ47">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR47">
         <v>1.4</v>
@@ -10749,7 +10770,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -10827,7 +10848,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ48">
         <v>2.5</v>
@@ -10955,7 +10976,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11239,10 +11260,10 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ50">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR50">
         <v>1.82</v>
@@ -11779,7 +11800,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -11985,7 +12006,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -12684,7 +12705,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ57">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR57">
         <v>2.08</v>
@@ -12890,7 +12911,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ58">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR58">
         <v>1.54</v>
@@ -13096,7 +13117,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
         <v>1.41</v>
@@ -13221,7 +13242,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13299,7 +13320,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ60">
         <v>0.8</v>
@@ -13427,7 +13448,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -13711,7 +13732,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ62">
         <v>0.5</v>
@@ -14045,7 +14066,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14126,7 +14147,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ64">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR64">
         <v>1.36</v>
@@ -14663,7 +14684,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -14947,10 +14968,10 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ68">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR68">
         <v>1.24</v>
@@ -15075,7 +15096,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15359,7 +15380,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15487,7 +15508,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15771,7 +15792,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ72">
         <v>0</v>
@@ -15899,7 +15920,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -15980,7 +16001,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ73">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR73">
         <v>1.93</v>
@@ -16105,7 +16126,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16183,7 +16204,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ74">
         <v>2</v>
@@ -16311,7 +16332,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16389,10 +16410,10 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ75">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR75">
         <v>1.47</v>
@@ -16598,7 +16619,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ76">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR76">
         <v>2.03</v>
@@ -16723,7 +16744,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -16804,7 +16825,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ77">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -17135,7 +17156,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -17213,7 +17234,7 @@
         <v>1</v>
       </c>
       <c r="AP79">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1.17</v>
@@ -17422,7 +17443,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ80">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR80">
         <v>2.13</v>
@@ -18165,7 +18186,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18243,7 +18264,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ84">
         <v>0.8</v>
@@ -18371,7 +18392,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18658,7 +18679,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ86">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR86">
         <v>1.66</v>
@@ -19195,7 +19216,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19273,7 +19294,7 @@
         <v>3</v>
       </c>
       <c r="AP89">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ89">
         <v>2.5</v>
@@ -19813,7 +19834,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -19894,7 +19915,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ92">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR92">
         <v>1.88</v>
@@ -20019,7 +20040,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20097,7 +20118,7 @@
         <v>0.6</v>
       </c>
       <c r="AP93">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20303,10 +20324,10 @@
         <v>0.25</v>
       </c>
       <c r="AP94">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AR94">
         <v>2.33</v>
@@ -20509,10 +20530,10 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ95">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="AR95">
         <v>1.25</v>
@@ -20718,7 +20739,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ96">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AR96">
         <v>1.8</v>
@@ -20843,7 +20864,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21049,7 +21070,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21127,10 +21148,10 @@
         <v>0</v>
       </c>
       <c r="AP98">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ98">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR98">
         <v>1.47</v>
@@ -21255,7 +21276,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21333,10 +21354,10 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ99">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AR99">
         <v>1.53</v>
@@ -21539,7 +21560,7 @@
         <v>0</v>
       </c>
       <c r="AP100">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ100">
         <v>0</v>
@@ -21667,7 +21688,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21873,7 +21894,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22285,7 +22306,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22491,7 +22512,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -23109,7 +23130,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23521,7 +23542,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23884,6 +23905,1242 @@
       </c>
       <c r="BP111">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="112" spans="1:68">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>7834425</v>
+      </c>
+      <c r="C112" t="s">
+        <v>68</v>
+      </c>
+      <c r="D112" t="s">
+        <v>69</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45820.79166666666</v>
+      </c>
+      <c r="F112">
+        <v>12</v>
+      </c>
+      <c r="G112" t="s">
+        <v>79</v>
+      </c>
+      <c r="H112" t="s">
+        <v>78</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>2</v>
+      </c>
+      <c r="K112">
+        <v>2</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>3</v>
+      </c>
+      <c r="N112">
+        <v>3</v>
+      </c>
+      <c r="O112" t="s">
+        <v>93</v>
+      </c>
+      <c r="P112" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q112">
+        <v>2.96</v>
+      </c>
+      <c r="R112">
+        <v>1.98</v>
+      </c>
+      <c r="S112">
+        <v>3.8</v>
+      </c>
+      <c r="T112">
+        <v>1.48</v>
+      </c>
+      <c r="U112">
+        <v>2.72</v>
+      </c>
+      <c r="V112">
+        <v>3.2</v>
+      </c>
+      <c r="W112">
+        <v>1.3</v>
+      </c>
+      <c r="X112">
+        <v>8.25</v>
+      </c>
+      <c r="Y112">
+        <v>1.05</v>
+      </c>
+      <c r="Z112">
+        <v>2.28</v>
+      </c>
+      <c r="AA112">
+        <v>3</v>
+      </c>
+      <c r="AB112">
+        <v>3.44</v>
+      </c>
+      <c r="AC112">
+        <v>1.02</v>
+      </c>
+      <c r="AD112">
+        <v>7</v>
+      </c>
+      <c r="AE112">
+        <v>1.41</v>
+      </c>
+      <c r="AF112">
+        <v>2.8</v>
+      </c>
+      <c r="AG112">
+        <v>2.36</v>
+      </c>
+      <c r="AH112">
+        <v>1.6</v>
+      </c>
+      <c r="AI112">
+        <v>1.92</v>
+      </c>
+      <c r="AJ112">
+        <v>1.79</v>
+      </c>
+      <c r="AK112">
+        <v>1.25</v>
+      </c>
+      <c r="AL112">
+        <v>1.33</v>
+      </c>
+      <c r="AM112">
+        <v>1.64</v>
+      </c>
+      <c r="AN112">
+        <v>2.17</v>
+      </c>
+      <c r="AO112">
+        <v>0.8</v>
+      </c>
+      <c r="AP112">
+        <v>1.86</v>
+      </c>
+      <c r="AQ112">
+        <v>1.17</v>
+      </c>
+      <c r="AR112">
+        <v>1.69</v>
+      </c>
+      <c r="AS112">
+        <v>1.26</v>
+      </c>
+      <c r="AT112">
+        <v>2.95</v>
+      </c>
+      <c r="AU112">
+        <v>3</v>
+      </c>
+      <c r="AV112">
+        <v>6</v>
+      </c>
+      <c r="AW112">
+        <v>7</v>
+      </c>
+      <c r="AX112">
+        <v>9</v>
+      </c>
+      <c r="AY112">
+        <v>10</v>
+      </c>
+      <c r="AZ112">
+        <v>15</v>
+      </c>
+      <c r="BA112">
+        <v>4</v>
+      </c>
+      <c r="BB112">
+        <v>1</v>
+      </c>
+      <c r="BC112">
+        <v>5</v>
+      </c>
+      <c r="BD112">
+        <v>1.7</v>
+      </c>
+      <c r="BE112">
+        <v>6.75</v>
+      </c>
+      <c r="BF112">
+        <v>2.35</v>
+      </c>
+      <c r="BG112">
+        <v>1.2</v>
+      </c>
+      <c r="BH112">
+        <v>4</v>
+      </c>
+      <c r="BI112">
+        <v>1.34</v>
+      </c>
+      <c r="BJ112">
+        <v>2.82</v>
+      </c>
+      <c r="BK112">
+        <v>1.52</v>
+      </c>
+      <c r="BL112">
+        <v>2.15</v>
+      </c>
+      <c r="BM112">
+        <v>2</v>
+      </c>
+      <c r="BN112">
+        <v>1.75</v>
+      </c>
+      <c r="BO112">
+        <v>2.48</v>
+      </c>
+      <c r="BP112">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="113" spans="1:68">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7834428</v>
+      </c>
+      <c r="C113" t="s">
+        <v>68</v>
+      </c>
+      <c r="D113" t="s">
+        <v>69</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45820.79166666666</v>
+      </c>
+      <c r="F113">
+        <v>12</v>
+      </c>
+      <c r="G113" t="s">
+        <v>86</v>
+      </c>
+      <c r="H113" t="s">
+        <v>74</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113" t="s">
+        <v>93</v>
+      </c>
+      <c r="P113" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q113">
+        <v>4.75</v>
+      </c>
+      <c r="R113">
+        <v>2</v>
+      </c>
+      <c r="S113">
+        <v>3</v>
+      </c>
+      <c r="T113">
+        <v>1.49</v>
+      </c>
+      <c r="U113">
+        <v>2.35</v>
+      </c>
+      <c r="V113">
+        <v>3.4</v>
+      </c>
+      <c r="W113">
+        <v>1.28</v>
+      </c>
+      <c r="X113">
+        <v>7.8</v>
+      </c>
+      <c r="Y113">
+        <v>1.04</v>
+      </c>
+      <c r="Z113">
+        <v>3.52</v>
+      </c>
+      <c r="AA113">
+        <v>3</v>
+      </c>
+      <c r="AB113">
+        <v>2.33</v>
+      </c>
+      <c r="AC113">
+        <v>1.11</v>
+      </c>
+      <c r="AD113">
+        <v>6.15</v>
+      </c>
+      <c r="AE113">
+        <v>1.44</v>
+      </c>
+      <c r="AF113">
+        <v>2.44</v>
+      </c>
+      <c r="AG113">
+        <v>2.55</v>
+      </c>
+      <c r="AH113">
+        <v>1.53</v>
+      </c>
+      <c r="AI113">
+        <v>1.93</v>
+      </c>
+      <c r="AJ113">
+        <v>1.75</v>
+      </c>
+      <c r="AK113">
+        <v>1.58</v>
+      </c>
+      <c r="AL113">
+        <v>1.35</v>
+      </c>
+      <c r="AM113">
+        <v>1.25</v>
+      </c>
+      <c r="AN113">
+        <v>1.4</v>
+      </c>
+      <c r="AO113">
+        <v>1.4</v>
+      </c>
+      <c r="AP113">
+        <v>1.33</v>
+      </c>
+      <c r="AQ113">
+        <v>1.33</v>
+      </c>
+      <c r="AR113">
+        <v>1.63</v>
+      </c>
+      <c r="AS113">
+        <v>1.54</v>
+      </c>
+      <c r="AT113">
+        <v>3.17</v>
+      </c>
+      <c r="AU113">
+        <v>3</v>
+      </c>
+      <c r="AV113">
+        <v>3</v>
+      </c>
+      <c r="AW113">
+        <v>8</v>
+      </c>
+      <c r="AX113">
+        <v>16</v>
+      </c>
+      <c r="AY113">
+        <v>11</v>
+      </c>
+      <c r="AZ113">
+        <v>19</v>
+      </c>
+      <c r="BA113">
+        <v>9</v>
+      </c>
+      <c r="BB113">
+        <v>4</v>
+      </c>
+      <c r="BC113">
+        <v>13</v>
+      </c>
+      <c r="BD113">
+        <v>2</v>
+      </c>
+      <c r="BE113">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF113">
+        <v>1.97</v>
+      </c>
+      <c r="BG113">
+        <v>1.21</v>
+      </c>
+      <c r="BH113">
+        <v>3.8</v>
+      </c>
+      <c r="BI113">
+        <v>1.38</v>
+      </c>
+      <c r="BJ113">
+        <v>2.75</v>
+      </c>
+      <c r="BK113">
+        <v>1.8</v>
+      </c>
+      <c r="BL113">
+        <v>1.91</v>
+      </c>
+      <c r="BM113">
+        <v>2.04</v>
+      </c>
+      <c r="BN113">
+        <v>1.71</v>
+      </c>
+      <c r="BO113">
+        <v>2.52</v>
+      </c>
+      <c r="BP113">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="114" spans="1:68">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>7834429</v>
+      </c>
+      <c r="C114" t="s">
+        <v>68</v>
+      </c>
+      <c r="D114" t="s">
+        <v>69</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45820.8125</v>
+      </c>
+      <c r="F114">
+        <v>12</v>
+      </c>
+      <c r="G114" t="s">
+        <v>70</v>
+      </c>
+      <c r="H114" t="s">
+        <v>89</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114">
+        <v>2</v>
+      </c>
+      <c r="L114">
+        <v>2</v>
+      </c>
+      <c r="M114">
+        <v>3</v>
+      </c>
+      <c r="N114">
+        <v>5</v>
+      </c>
+      <c r="O114" t="s">
+        <v>167</v>
+      </c>
+      <c r="P114" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q114">
+        <v>2.88</v>
+      </c>
+      <c r="R114">
+        <v>2.09</v>
+      </c>
+      <c r="S114">
+        <v>4.1</v>
+      </c>
+      <c r="T114">
+        <v>1.51</v>
+      </c>
+      <c r="U114">
+        <v>2.4</v>
+      </c>
+      <c r="V114">
+        <v>3.2</v>
+      </c>
+      <c r="W114">
+        <v>1.29</v>
+      </c>
+      <c r="X114">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y114">
+        <v>1.04</v>
+      </c>
+      <c r="Z114">
+        <v>2.29</v>
+      </c>
+      <c r="AA114">
+        <v>3.05</v>
+      </c>
+      <c r="AB114">
+        <v>3.24</v>
+      </c>
+      <c r="AC114">
+        <v>1.08</v>
+      </c>
+      <c r="AD114">
+        <v>7</v>
+      </c>
+      <c r="AE114">
+        <v>1.44</v>
+      </c>
+      <c r="AF114">
+        <v>2.65</v>
+      </c>
+      <c r="AG114">
+        <v>2.38</v>
+      </c>
+      <c r="AH114">
+        <v>1.56</v>
+      </c>
+      <c r="AI114">
+        <v>2.07</v>
+      </c>
+      <c r="AJ114">
+        <v>1.8</v>
+      </c>
+      <c r="AK114">
+        <v>1.27</v>
+      </c>
+      <c r="AL114">
+        <v>1.34</v>
+      </c>
+      <c r="AM114">
+        <v>1.62</v>
+      </c>
+      <c r="AN114">
+        <v>1.4</v>
+      </c>
+      <c r="AO114">
+        <v>0.5</v>
+      </c>
+      <c r="AP114">
+        <v>1.17</v>
+      </c>
+      <c r="AQ114">
+        <v>0.86</v>
+      </c>
+      <c r="AR114">
+        <v>1.47</v>
+      </c>
+      <c r="AS114">
+        <v>1.15</v>
+      </c>
+      <c r="AT114">
+        <v>2.62</v>
+      </c>
+      <c r="AU114">
+        <v>11</v>
+      </c>
+      <c r="AV114">
+        <v>5</v>
+      </c>
+      <c r="AW114">
+        <v>25</v>
+      </c>
+      <c r="AX114">
+        <v>4</v>
+      </c>
+      <c r="AY114">
+        <v>36</v>
+      </c>
+      <c r="AZ114">
+        <v>9</v>
+      </c>
+      <c r="BA114">
+        <v>15</v>
+      </c>
+      <c r="BB114">
+        <v>0</v>
+      </c>
+      <c r="BC114">
+        <v>15</v>
+      </c>
+      <c r="BD114">
+        <v>1.78</v>
+      </c>
+      <c r="BE114">
+        <v>6.85</v>
+      </c>
+      <c r="BF114">
+        <v>2.3</v>
+      </c>
+      <c r="BG114">
+        <v>1.15</v>
+      </c>
+      <c r="BH114">
+        <v>3.88</v>
+      </c>
+      <c r="BI114">
+        <v>1.39</v>
+      </c>
+      <c r="BJ114">
+        <v>2.93</v>
+      </c>
+      <c r="BK114">
+        <v>1.58</v>
+      </c>
+      <c r="BL114">
+        <v>2.17</v>
+      </c>
+      <c r="BM114">
+        <v>2.03</v>
+      </c>
+      <c r="BN114">
+        <v>1.72</v>
+      </c>
+      <c r="BO114">
+        <v>2.3</v>
+      </c>
+      <c r="BP114">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="115" spans="1:68">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>7834427</v>
+      </c>
+      <c r="C115" t="s">
+        <v>68</v>
+      </c>
+      <c r="D115" t="s">
+        <v>69</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45820.83333333334</v>
+      </c>
+      <c r="F115">
+        <v>12</v>
+      </c>
+      <c r="G115" t="s">
+        <v>72</v>
+      </c>
+      <c r="H115" t="s">
+        <v>80</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="K115">
+        <v>2</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115">
+        <v>2</v>
+      </c>
+      <c r="O115" t="s">
+        <v>168</v>
+      </c>
+      <c r="P115" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q115">
+        <v>3.08</v>
+      </c>
+      <c r="R115">
+        <v>1.85</v>
+      </c>
+      <c r="S115">
+        <v>4.1</v>
+      </c>
+      <c r="T115">
+        <v>1.6</v>
+      </c>
+      <c r="U115">
+        <v>2.25</v>
+      </c>
+      <c r="V115">
+        <v>3.58</v>
+      </c>
+      <c r="W115">
+        <v>1.25</v>
+      </c>
+      <c r="X115">
+        <v>8</v>
+      </c>
+      <c r="Y115">
+        <v>1.01</v>
+      </c>
+      <c r="Z115">
+        <v>2.2</v>
+      </c>
+      <c r="AA115">
+        <v>3.03</v>
+      </c>
+      <c r="AB115">
+        <v>3.25</v>
+      </c>
+      <c r="AC115">
+        <v>1.12</v>
+      </c>
+      <c r="AD115">
+        <v>5.75</v>
+      </c>
+      <c r="AE115">
+        <v>1.59</v>
+      </c>
+      <c r="AF115">
+        <v>2.4</v>
+      </c>
+      <c r="AG115">
+        <v>2.7</v>
+      </c>
+      <c r="AH115">
+        <v>1.42</v>
+      </c>
+      <c r="AI115">
+        <v>2.15</v>
+      </c>
+      <c r="AJ115">
+        <v>1.67</v>
+      </c>
+      <c r="AK115">
+        <v>1.25</v>
+      </c>
+      <c r="AL115">
+        <v>1.34</v>
+      </c>
+      <c r="AM115">
+        <v>1.6</v>
+      </c>
+      <c r="AN115">
+        <v>1.83</v>
+      </c>
+      <c r="AO115">
+        <v>0.4</v>
+      </c>
+      <c r="AP115">
+        <v>1.71</v>
+      </c>
+      <c r="AQ115">
+        <v>0.5</v>
+      </c>
+      <c r="AR115">
+        <v>1.22</v>
+      </c>
+      <c r="AS115">
+        <v>1.05</v>
+      </c>
+      <c r="AT115">
+        <v>2.27</v>
+      </c>
+      <c r="AU115">
+        <v>8</v>
+      </c>
+      <c r="AV115">
+        <v>4</v>
+      </c>
+      <c r="AW115">
+        <v>13</v>
+      </c>
+      <c r="AX115">
+        <v>9</v>
+      </c>
+      <c r="AY115">
+        <v>21</v>
+      </c>
+      <c r="AZ115">
+        <v>13</v>
+      </c>
+      <c r="BA115">
+        <v>4</v>
+      </c>
+      <c r="BB115">
+        <v>6</v>
+      </c>
+      <c r="BC115">
+        <v>10</v>
+      </c>
+      <c r="BD115">
+        <v>1.87</v>
+      </c>
+      <c r="BE115">
+        <v>6.65</v>
+      </c>
+      <c r="BF115">
+        <v>2.38</v>
+      </c>
+      <c r="BG115">
+        <v>1.25</v>
+      </c>
+      <c r="BH115">
+        <v>3.45</v>
+      </c>
+      <c r="BI115">
+        <v>1.5</v>
+      </c>
+      <c r="BJ115">
+        <v>2.49</v>
+      </c>
+      <c r="BK115">
+        <v>2.08</v>
+      </c>
+      <c r="BL115">
+        <v>2</v>
+      </c>
+      <c r="BM115">
+        <v>2</v>
+      </c>
+      <c r="BN115">
+        <v>1.73</v>
+      </c>
+      <c r="BO115">
+        <v>3</v>
+      </c>
+      <c r="BP115">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="116" spans="1:68">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>7834424</v>
+      </c>
+      <c r="C116" t="s">
+        <v>68</v>
+      </c>
+      <c r="D116" t="s">
+        <v>69</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45820.89583333334</v>
+      </c>
+      <c r="F116">
+        <v>12</v>
+      </c>
+      <c r="G116" t="s">
+        <v>73</v>
+      </c>
+      <c r="H116" t="s">
+        <v>77</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>2</v>
+      </c>
+      <c r="K116">
+        <v>2</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>3</v>
+      </c>
+      <c r="N116">
+        <v>4</v>
+      </c>
+      <c r="O116" t="s">
+        <v>105</v>
+      </c>
+      <c r="P116" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q116">
+        <v>2.15</v>
+      </c>
+      <c r="R116">
+        <v>1.9</v>
+      </c>
+      <c r="S116">
+        <v>6</v>
+      </c>
+      <c r="T116">
+        <v>1.55</v>
+      </c>
+      <c r="U116">
+        <v>2.35</v>
+      </c>
+      <c r="V116">
+        <v>3.6</v>
+      </c>
+      <c r="W116">
+        <v>1.25</v>
+      </c>
+      <c r="X116">
+        <v>10.5</v>
+      </c>
+      <c r="Y116">
+        <v>1.05</v>
+      </c>
+      <c r="Z116">
+        <v>1.8</v>
+      </c>
+      <c r="AA116">
+        <v>3.33</v>
+      </c>
+      <c r="AB116">
+        <v>5.1</v>
+      </c>
+      <c r="AC116">
+        <v>1.11</v>
+      </c>
+      <c r="AD116">
+        <v>5.75</v>
+      </c>
+      <c r="AE116">
+        <v>1.57</v>
+      </c>
+      <c r="AF116">
+        <v>2.5</v>
+      </c>
+      <c r="AG116">
+        <v>2.55</v>
+      </c>
+      <c r="AH116">
+        <v>1.46</v>
+      </c>
+      <c r="AI116">
+        <v>2.45</v>
+      </c>
+      <c r="AJ116">
+        <v>1.59</v>
+      </c>
+      <c r="AK116">
+        <v>1.36</v>
+      </c>
+      <c r="AL116">
+        <v>1.32</v>
+      </c>
+      <c r="AM116">
+        <v>2.05</v>
+      </c>
+      <c r="AN116">
+        <v>1.5</v>
+      </c>
+      <c r="AO116">
+        <v>0</v>
+      </c>
+      <c r="AP116">
+        <v>1.29</v>
+      </c>
+      <c r="AQ116">
+        <v>0.5</v>
+      </c>
+      <c r="AR116">
+        <v>1.47</v>
+      </c>
+      <c r="AS116">
+        <v>1.49</v>
+      </c>
+      <c r="AT116">
+        <v>2.96</v>
+      </c>
+      <c r="AU116">
+        <v>4</v>
+      </c>
+      <c r="AV116">
+        <v>10</v>
+      </c>
+      <c r="AW116">
+        <v>8</v>
+      </c>
+      <c r="AX116">
+        <v>5</v>
+      </c>
+      <c r="AY116">
+        <v>12</v>
+      </c>
+      <c r="AZ116">
+        <v>15</v>
+      </c>
+      <c r="BA116">
+        <v>4</v>
+      </c>
+      <c r="BB116">
+        <v>3</v>
+      </c>
+      <c r="BC116">
+        <v>7</v>
+      </c>
+      <c r="BD116">
+        <v>1.6</v>
+      </c>
+      <c r="BE116">
+        <v>7.8</v>
+      </c>
+      <c r="BF116">
+        <v>2.81</v>
+      </c>
+      <c r="BG116">
+        <v>1.2</v>
+      </c>
+      <c r="BH116">
+        <v>3.6</v>
+      </c>
+      <c r="BI116">
+        <v>1.45</v>
+      </c>
+      <c r="BJ116">
+        <v>2.62</v>
+      </c>
+      <c r="BK116">
+        <v>1.72</v>
+      </c>
+      <c r="BL116">
+        <v>2.05</v>
+      </c>
+      <c r="BM116">
+        <v>2.1</v>
+      </c>
+      <c r="BN116">
+        <v>1.67</v>
+      </c>
+      <c r="BO116">
+        <v>2.62</v>
+      </c>
+      <c r="BP116">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="117" spans="1:68">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>7834426</v>
+      </c>
+      <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" t="s">
+        <v>69</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45820.89583333334</v>
+      </c>
+      <c r="F117">
+        <v>12</v>
+      </c>
+      <c r="G117" t="s">
+        <v>83</v>
+      </c>
+      <c r="H117" t="s">
+        <v>88</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>1</v>
+      </c>
+      <c r="L117">
+        <v>2</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>2</v>
+      </c>
+      <c r="O117" t="s">
+        <v>169</v>
+      </c>
+      <c r="P117" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q117">
+        <v>2.5</v>
+      </c>
+      <c r="R117">
+        <v>2.02</v>
+      </c>
+      <c r="S117">
+        <v>5.05</v>
+      </c>
+      <c r="T117">
+        <v>1.5</v>
+      </c>
+      <c r="U117">
+        <v>2.66</v>
+      </c>
+      <c r="V117">
+        <v>3.32</v>
+      </c>
+      <c r="W117">
+        <v>1.31</v>
+      </c>
+      <c r="X117">
+        <v>8.5</v>
+      </c>
+      <c r="Y117">
+        <v>1.05</v>
+      </c>
+      <c r="Z117">
+        <v>1.81</v>
+      </c>
+      <c r="AA117">
+        <v>3.05</v>
+      </c>
+      <c r="AB117">
+        <v>3.95</v>
+      </c>
+      <c r="AC117">
+        <v>1.05</v>
+      </c>
+      <c r="AD117">
+        <v>7.5</v>
+      </c>
+      <c r="AE117">
+        <v>1.4</v>
+      </c>
+      <c r="AF117">
+        <v>2.6</v>
+      </c>
+      <c r="AG117">
+        <v>2.25</v>
+      </c>
+      <c r="AH117">
+        <v>1.55</v>
+      </c>
+      <c r="AI117">
+        <v>2.04</v>
+      </c>
+      <c r="AJ117">
+        <v>1.68</v>
+      </c>
+      <c r="AK117">
+        <v>1.22</v>
+      </c>
+      <c r="AL117">
+        <v>1.32</v>
+      </c>
+      <c r="AM117">
+        <v>1.96</v>
+      </c>
+      <c r="AN117">
+        <v>1.8</v>
+      </c>
+      <c r="AO117">
+        <v>0.67</v>
+      </c>
+      <c r="AP117">
+        <v>2</v>
+      </c>
+      <c r="AQ117">
+        <v>0.57</v>
+      </c>
+      <c r="AR117">
+        <v>2.13</v>
+      </c>
+      <c r="AS117">
+        <v>1.35</v>
+      </c>
+      <c r="AT117">
+        <v>3.48</v>
+      </c>
+      <c r="AU117">
+        <v>6</v>
+      </c>
+      <c r="AV117">
+        <v>3</v>
+      </c>
+      <c r="AW117">
+        <v>10</v>
+      </c>
+      <c r="AX117">
+        <v>7</v>
+      </c>
+      <c r="AY117">
+        <v>16</v>
+      </c>
+      <c r="AZ117">
+        <v>10</v>
+      </c>
+      <c r="BA117">
+        <v>6</v>
+      </c>
+      <c r="BB117">
+        <v>5</v>
+      </c>
+      <c r="BC117">
+        <v>11</v>
+      </c>
+      <c r="BD117">
+        <v>1.6</v>
+      </c>
+      <c r="BE117">
+        <v>7</v>
+      </c>
+      <c r="BF117">
+        <v>2.63</v>
+      </c>
+      <c r="BG117">
+        <v>1.3</v>
+      </c>
+      <c r="BH117">
+        <v>3.2</v>
+      </c>
+      <c r="BI117">
+        <v>1.44</v>
+      </c>
+      <c r="BJ117">
+        <v>2.3</v>
+      </c>
+      <c r="BK117">
+        <v>1.9</v>
+      </c>
+      <c r="BL117">
+        <v>1.83</v>
+      </c>
+      <c r="BM117">
+        <v>2.38</v>
+      </c>
+      <c r="BN117">
+        <v>1.55</v>
+      </c>
+      <c r="BO117">
+        <v>3.02</v>
+      </c>
+      <c r="BP117">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="223">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,9 @@
     <t>['30', '90+4']</t>
   </si>
   <si>
+    <t>['61', '90+6']</t>
+  </si>
+  <si>
     <t>['75']</t>
   </si>
   <si>
@@ -677,6 +680,9 @@
   </si>
   <si>
     <t>['26', '40', '69']</t>
+  </si>
+  <si>
+    <t>['48', '78']</t>
   </si>
 </sst>
 </file>
@@ -1038,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP117"/>
+  <dimension ref="A1:BP120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1581,7 +1587,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ3">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1706,7 +1712,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2118,7 +2124,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2402,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ7">
         <v>0.57</v>
@@ -2611,7 +2617,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ8">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2736,7 +2742,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2814,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ9">
         <v>0.86</v>
@@ -2942,7 +2948,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3148,7 +3154,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4053,7 +4059,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4178,7 +4184,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4384,7 +4390,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4590,7 +4596,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -5080,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ20">
         <v>1.33</v>
@@ -5208,7 +5214,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5495,7 +5501,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ22">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR22">
         <v>2.29</v>
@@ -5620,7 +5626,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6110,7 +6116,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ25">
         <v>0.17</v>
@@ -6238,7 +6244,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6444,7 +6450,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6650,7 +6656,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -7268,7 +7274,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7349,7 +7355,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR31">
         <v>2.54</v>
@@ -7680,7 +7686,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7761,7 +7767,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ33">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
         <v>1.9</v>
@@ -7886,7 +7892,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8092,7 +8098,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8298,7 +8304,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -8582,7 +8588,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ37">
         <v>2.5</v>
@@ -8994,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ39">
         <v>0</v>
@@ -9534,7 +9540,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9818,7 +9824,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ43">
         <v>2</v>
@@ -10152,7 +10158,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10439,7 +10445,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR46">
         <v>2.97</v>
@@ -10564,7 +10570,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10770,7 +10776,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -10976,7 +10982,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11057,7 +11063,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ49">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR49">
         <v>1.66</v>
@@ -11672,7 +11678,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
         <v>0</v>
@@ -11800,7 +11806,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -11881,7 +11887,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ53">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>1.35</v>
@@ -12006,7 +12012,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -12702,7 +12708,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ57">
         <v>0.5</v>
@@ -13242,7 +13248,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13448,7 +13454,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -14066,7 +14072,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14353,7 +14359,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR65">
         <v>1.2</v>
@@ -14559,7 +14565,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ66">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR66">
         <v>1.57</v>
@@ -14684,7 +14690,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -14762,7 +14768,7 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ67">
         <v>2.5</v>
@@ -15096,7 +15102,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15508,7 +15514,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15920,7 +15926,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16126,7 +16132,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16332,7 +16338,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16616,7 +16622,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ76">
         <v>1.17</v>
@@ -16744,7 +16750,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17031,7 +17037,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ78">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17156,7 +17162,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -18058,7 +18064,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ83">
         <v>0.5</v>
@@ -18186,7 +18192,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18392,7 +18398,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18885,7 +18891,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ87">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR87">
         <v>1.46</v>
@@ -19088,10 +19094,10 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ88">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR88">
         <v>1.9</v>
@@ -19216,7 +19222,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19706,7 +19712,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -19834,7 +19840,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20040,7 +20046,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20864,7 +20870,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21070,7 +21076,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21276,7 +21282,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21688,7 +21694,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21769,7 +21775,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ101">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR101">
         <v>1.36</v>
@@ -21894,7 +21900,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -21972,7 +21978,7 @@
         <v>1.75</v>
       </c>
       <c r="AP102">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AQ102">
         <v>2</v>
@@ -22306,7 +22312,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22512,7 +22518,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -22593,7 +22599,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR105">
         <v>1.78</v>
@@ -22796,7 +22802,7 @@
         <v>0.6</v>
       </c>
       <c r="AP106">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ106">
         <v>0.5</v>
@@ -23005,7 +23011,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR107">
         <v>1.58</v>
@@ -23130,7 +23136,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23542,7 +23548,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23620,7 +23626,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AQ110">
         <v>1.17</v>
@@ -23954,7 +23960,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24366,7 +24372,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24572,7 +24578,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24778,7 +24784,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25141,6 +25147,624 @@
       </c>
       <c r="BP117">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="118" spans="1:68">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>7834431</v>
+      </c>
+      <c r="C118" t="s">
+        <v>68</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45850.6875</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118" t="s">
+        <v>75</v>
+      </c>
+      <c r="H118" t="s">
+        <v>73</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>2</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>2</v>
+      </c>
+      <c r="O118" t="s">
+        <v>170</v>
+      </c>
+      <c r="P118" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q118">
+        <v>2.09</v>
+      </c>
+      <c r="R118">
+        <v>2.15</v>
+      </c>
+      <c r="S118">
+        <v>8.5</v>
+      </c>
+      <c r="T118">
+        <v>1.4</v>
+      </c>
+      <c r="U118">
+        <v>2.8</v>
+      </c>
+      <c r="V118">
+        <v>3.2</v>
+      </c>
+      <c r="W118">
+        <v>1.27</v>
+      </c>
+      <c r="X118">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y118">
+        <v>1.04</v>
+      </c>
+      <c r="Z118">
+        <v>1.45</v>
+      </c>
+      <c r="AA118">
+        <v>4.05</v>
+      </c>
+      <c r="AB118">
+        <v>6.9</v>
+      </c>
+      <c r="AC118">
+        <v>1.06</v>
+      </c>
+      <c r="AD118">
+        <v>7</v>
+      </c>
+      <c r="AE118">
+        <v>1.36</v>
+      </c>
+      <c r="AF118">
+        <v>3</v>
+      </c>
+      <c r="AG118">
+        <v>2.41</v>
+      </c>
+      <c r="AH118">
+        <v>1.6</v>
+      </c>
+      <c r="AI118">
+        <v>2.38</v>
+      </c>
+      <c r="AJ118">
+        <v>1.48</v>
+      </c>
+      <c r="AK118">
+        <v>1.09</v>
+      </c>
+      <c r="AL118">
+        <v>1.22</v>
+      </c>
+      <c r="AM118">
+        <v>2.62</v>
+      </c>
+      <c r="AN118">
+        <v>2.33</v>
+      </c>
+      <c r="AO118">
+        <v>0.6</v>
+      </c>
+      <c r="AP118">
+        <v>2.43</v>
+      </c>
+      <c r="AQ118">
+        <v>0.5</v>
+      </c>
+      <c r="AR118">
+        <v>1.94</v>
+      </c>
+      <c r="AS118">
+        <v>1.32</v>
+      </c>
+      <c r="AT118">
+        <v>3.26</v>
+      </c>
+      <c r="AU118">
+        <v>7</v>
+      </c>
+      <c r="AV118">
+        <v>0</v>
+      </c>
+      <c r="AW118">
+        <v>3</v>
+      </c>
+      <c r="AX118">
+        <v>3</v>
+      </c>
+      <c r="AY118">
+        <v>10</v>
+      </c>
+      <c r="AZ118">
+        <v>3</v>
+      </c>
+      <c r="BA118">
+        <v>5</v>
+      </c>
+      <c r="BB118">
+        <v>1</v>
+      </c>
+      <c r="BC118">
+        <v>6</v>
+      </c>
+      <c r="BD118">
+        <v>1.24</v>
+      </c>
+      <c r="BE118">
+        <v>10.5</v>
+      </c>
+      <c r="BF118">
+        <v>5.5</v>
+      </c>
+      <c r="BG118">
+        <v>1.33</v>
+      </c>
+      <c r="BH118">
+        <v>3.2</v>
+      </c>
+      <c r="BI118">
+        <v>1.52</v>
+      </c>
+      <c r="BJ118">
+        <v>2.36</v>
+      </c>
+      <c r="BK118">
+        <v>1.91</v>
+      </c>
+      <c r="BL118">
+        <v>1.8</v>
+      </c>
+      <c r="BM118">
+        <v>2.3</v>
+      </c>
+      <c r="BN118">
+        <v>1.5</v>
+      </c>
+      <c r="BO118">
+        <v>3.07</v>
+      </c>
+      <c r="BP118">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="119" spans="1:68">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>7834437</v>
+      </c>
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45850.6875</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119" t="s">
+        <v>88</v>
+      </c>
+      <c r="H119" t="s">
+        <v>86</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>1</v>
+      </c>
+      <c r="O119" t="s">
+        <v>143</v>
+      </c>
+      <c r="P119" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q119">
+        <v>2</v>
+      </c>
+      <c r="R119">
+        <v>2.1</v>
+      </c>
+      <c r="S119">
+        <v>5.75</v>
+      </c>
+      <c r="T119">
+        <v>1.45</v>
+      </c>
+      <c r="U119">
+        <v>2.63</v>
+      </c>
+      <c r="V119">
+        <v>3</v>
+      </c>
+      <c r="W119">
+        <v>1.33</v>
+      </c>
+      <c r="X119">
+        <v>9</v>
+      </c>
+      <c r="Y119">
+        <v>1.06</v>
+      </c>
+      <c r="Z119">
+        <v>1.66</v>
+      </c>
+      <c r="AA119">
+        <v>3.6</v>
+      </c>
+      <c r="AB119">
+        <v>6</v>
+      </c>
+      <c r="AC119">
+        <v>1.03</v>
+      </c>
+      <c r="AD119">
+        <v>7.8</v>
+      </c>
+      <c r="AE119">
+        <v>1.33</v>
+      </c>
+      <c r="AF119">
+        <v>3</v>
+      </c>
+      <c r="AG119">
+        <v>2.15</v>
+      </c>
+      <c r="AH119">
+        <v>1.65</v>
+      </c>
+      <c r="AI119">
+        <v>2.1</v>
+      </c>
+      <c r="AJ119">
+        <v>1.67</v>
+      </c>
+      <c r="AK119">
+        <v>1.13</v>
+      </c>
+      <c r="AL119">
+        <v>1.28</v>
+      </c>
+      <c r="AM119">
+        <v>2.15</v>
+      </c>
+      <c r="AN119">
+        <v>1.4</v>
+      </c>
+      <c r="AO119">
+        <v>0.5</v>
+      </c>
+      <c r="AP119">
+        <v>1.67</v>
+      </c>
+      <c r="AQ119">
+        <v>0.43</v>
+      </c>
+      <c r="AR119">
+        <v>2.2</v>
+      </c>
+      <c r="AS119">
+        <v>1.41</v>
+      </c>
+      <c r="AT119">
+        <v>3.61</v>
+      </c>
+      <c r="AU119">
+        <v>4</v>
+      </c>
+      <c r="AV119">
+        <v>5</v>
+      </c>
+      <c r="AW119">
+        <v>9</v>
+      </c>
+      <c r="AX119">
+        <v>4</v>
+      </c>
+      <c r="AY119">
+        <v>13</v>
+      </c>
+      <c r="AZ119">
+        <v>9</v>
+      </c>
+      <c r="BA119">
+        <v>2</v>
+      </c>
+      <c r="BB119">
+        <v>5</v>
+      </c>
+      <c r="BC119">
+        <v>7</v>
+      </c>
+      <c r="BD119">
+        <v>1.38</v>
+      </c>
+      <c r="BE119">
+        <v>9.5</v>
+      </c>
+      <c r="BF119">
+        <v>3.8</v>
+      </c>
+      <c r="BG119">
+        <v>1.28</v>
+      </c>
+      <c r="BH119">
+        <v>3.52</v>
+      </c>
+      <c r="BI119">
+        <v>1.5</v>
+      </c>
+      <c r="BJ119">
+        <v>2.57</v>
+      </c>
+      <c r="BK119">
+        <v>1.75</v>
+      </c>
+      <c r="BL119">
+        <v>1.96</v>
+      </c>
+      <c r="BM119">
+        <v>2.21</v>
+      </c>
+      <c r="BN119">
+        <v>1.53</v>
+      </c>
+      <c r="BO119">
+        <v>2.75</v>
+      </c>
+      <c r="BP119">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:68">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7834432</v>
+      </c>
+      <c r="C120" t="s">
+        <v>68</v>
+      </c>
+      <c r="D120" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45850.77083333334</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120" t="s">
+        <v>77</v>
+      </c>
+      <c r="H120" t="s">
+        <v>82</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>2</v>
+      </c>
+      <c r="N120">
+        <v>2</v>
+      </c>
+      <c r="O120" t="s">
+        <v>93</v>
+      </c>
+      <c r="P120" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q120">
+        <v>4.47</v>
+      </c>
+      <c r="R120">
+        <v>1.99</v>
+      </c>
+      <c r="S120">
+        <v>2.8</v>
+      </c>
+      <c r="T120">
+        <v>1.5</v>
+      </c>
+      <c r="U120">
+        <v>2.45</v>
+      </c>
+      <c r="V120">
+        <v>3.47</v>
+      </c>
+      <c r="W120">
+        <v>1.3</v>
+      </c>
+      <c r="X120">
+        <v>8</v>
+      </c>
+      <c r="Y120">
+        <v>1.04</v>
+      </c>
+      <c r="Z120">
+        <v>2.92</v>
+      </c>
+      <c r="AA120">
+        <v>2.96</v>
+      </c>
+      <c r="AB120">
+        <v>2.28</v>
+      </c>
+      <c r="AC120">
+        <v>1.07</v>
+      </c>
+      <c r="AD120">
+        <v>7.5</v>
+      </c>
+      <c r="AE120">
+        <v>1.46</v>
+      </c>
+      <c r="AF120">
+        <v>2.62</v>
+      </c>
+      <c r="AG120">
+        <v>2.33</v>
+      </c>
+      <c r="AH120">
+        <v>1.53</v>
+      </c>
+      <c r="AI120">
+        <v>1.93</v>
+      </c>
+      <c r="AJ120">
+        <v>1.75</v>
+      </c>
+      <c r="AK120">
+        <v>1.34</v>
+      </c>
+      <c r="AL120">
+        <v>1.33</v>
+      </c>
+      <c r="AM120">
+        <v>1.29</v>
+      </c>
+      <c r="AN120">
+        <v>1.67</v>
+      </c>
+      <c r="AO120">
+        <v>0.83</v>
+      </c>
+      <c r="AP120">
+        <v>1.43</v>
+      </c>
+      <c r="AQ120">
+        <v>1.14</v>
+      </c>
+      <c r="AR120">
+        <v>1.55</v>
+      </c>
+      <c r="AS120">
+        <v>1.37</v>
+      </c>
+      <c r="AT120">
+        <v>2.92</v>
+      </c>
+      <c r="AU120">
+        <v>6</v>
+      </c>
+      <c r="AV120">
+        <v>7</v>
+      </c>
+      <c r="AW120">
+        <v>3</v>
+      </c>
+      <c r="AX120">
+        <v>10</v>
+      </c>
+      <c r="AY120">
+        <v>9</v>
+      </c>
+      <c r="AZ120">
+        <v>17</v>
+      </c>
+      <c r="BA120">
+        <v>5</v>
+      </c>
+      <c r="BB120">
+        <v>3</v>
+      </c>
+      <c r="BC120">
+        <v>8</v>
+      </c>
+      <c r="BD120">
+        <v>2.38</v>
+      </c>
+      <c r="BE120">
+        <v>8</v>
+      </c>
+      <c r="BF120">
+        <v>1.95</v>
+      </c>
+      <c r="BG120">
+        <v>1.29</v>
+      </c>
+      <c r="BH120">
+        <v>3.35</v>
+      </c>
+      <c r="BI120">
+        <v>1.5</v>
+      </c>
+      <c r="BJ120">
+        <v>2.38</v>
+      </c>
+      <c r="BK120">
+        <v>1.8</v>
+      </c>
+      <c r="BL120">
+        <v>1.94</v>
+      </c>
+      <c r="BM120">
+        <v>2.26</v>
+      </c>
+      <c r="BN120">
+        <v>1.55</v>
+      </c>
+      <c r="BO120">
+        <v>3.4</v>
+      </c>
+      <c r="BP120">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="225">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -529,6 +529,9 @@
     <t>['61', '90+6']</t>
   </si>
   <si>
+    <t>['53', '90+7']</t>
+  </si>
+  <si>
     <t>['75']</t>
   </si>
   <si>
@@ -683,6 +686,9 @@
   </si>
   <si>
     <t>['48', '78']</t>
+  </si>
+  <si>
+    <t>['90+1']</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP120"/>
+  <dimension ref="A1:BP121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1712,7 +1718,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1793,7 +1799,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ4">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2124,7 +2130,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2742,7 +2748,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2948,7 +2954,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3026,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ10">
         <v>0.5</v>
@@ -3154,7 +3160,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4184,7 +4190,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4390,7 +4396,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4596,7 +4602,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -5214,7 +5220,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5626,7 +5632,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6244,7 +6250,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6322,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ26">
         <v>1</v>
@@ -6450,7 +6456,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6656,7 +6662,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -7274,7 +7280,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7686,7 +7692,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7892,7 +7898,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8098,7 +8104,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8304,7 +8310,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -9209,7 +9215,7 @@
         <v>1</v>
       </c>
       <c r="AQ40">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR40">
         <v>2.4</v>
@@ -9540,7 +9546,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10158,7 +10164,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10570,7 +10576,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10776,7 +10782,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -10982,7 +10988,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11472,7 +11478,7 @@
         <v>0.5</v>
       </c>
       <c r="AP51">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ51">
         <v>0.4</v>
@@ -11806,7 +11812,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12012,7 +12018,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -12093,7 +12099,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR54">
         <v>1.85</v>
@@ -13248,7 +13254,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13454,7 +13460,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -14072,7 +14078,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14562,7 +14568,7 @@
         <v>0.33</v>
       </c>
       <c r="AP66">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ66">
         <v>1.14</v>
@@ -14690,7 +14696,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -15102,7 +15108,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15514,7 +15520,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15595,7 +15601,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ71">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR71">
         <v>1.79</v>
@@ -15926,7 +15932,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16132,7 +16138,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16338,7 +16344,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16750,7 +16756,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17162,7 +17168,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -18192,7 +18198,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18398,7 +18404,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18888,7 +18894,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ87">
         <v>0.43</v>
@@ -19222,7 +19228,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19509,7 +19515,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ90">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR90">
         <v>1.65</v>
@@ -19840,7 +19846,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20046,7 +20052,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20870,7 +20876,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21076,7 +21082,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21282,7 +21288,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21694,7 +21700,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21772,7 +21778,7 @@
         <v>0.75</v>
       </c>
       <c r="AP101">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ101">
         <v>0.5</v>
@@ -21900,7 +21906,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22312,7 +22318,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22518,7 +22524,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -23136,7 +23142,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23217,7 +23223,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ108">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR108">
         <v>1.34</v>
@@ -23548,7 +23554,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23960,7 +23966,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24372,7 +24378,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24578,7 +24584,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24784,7 +24790,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25295,16 +25301,16 @@
         <v>0</v>
       </c>
       <c r="AW118">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AX118">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY118">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AZ118">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BA118">
         <v>5</v>
@@ -25501,16 +25507,16 @@
         <v>5</v>
       </c>
       <c r="AW119">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AX119">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY119">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AZ119">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA119">
         <v>2</v>
@@ -25608,7 +25614,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25707,16 +25713,16 @@
         <v>7</v>
       </c>
       <c r="AW120">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX120">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AY120">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ120">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BA120">
         <v>5</v>
@@ -25764,6 +25770,212 @@
         <v>3.4</v>
       </c>
       <c r="BP120">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="121" spans="1:68">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>7834438</v>
+      </c>
+      <c r="C121" t="s">
+        <v>68</v>
+      </c>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45850.875</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121" t="s">
+        <v>78</v>
+      </c>
+      <c r="H121" t="s">
+        <v>83</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>3</v>
+      </c>
+      <c r="O121" t="s">
+        <v>171</v>
+      </c>
+      <c r="P121" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q121">
+        <v>2.8</v>
+      </c>
+      <c r="R121">
+        <v>1.95</v>
+      </c>
+      <c r="S121">
+        <v>3.85</v>
+      </c>
+      <c r="T121">
+        <v>1.49</v>
+      </c>
+      <c r="U121">
+        <v>2.45</v>
+      </c>
+      <c r="V121">
+        <v>3.25</v>
+      </c>
+      <c r="W121">
+        <v>1.32</v>
+      </c>
+      <c r="X121">
+        <v>7.8</v>
+      </c>
+      <c r="Y121">
+        <v>1.02</v>
+      </c>
+      <c r="Z121">
+        <v>2.16</v>
+      </c>
+      <c r="AA121">
+        <v>2.75</v>
+      </c>
+      <c r="AB121">
+        <v>3.41</v>
+      </c>
+      <c r="AC121">
+        <v>1.09</v>
+      </c>
+      <c r="AD121">
+        <v>7</v>
+      </c>
+      <c r="AE121">
+        <v>1.37</v>
+      </c>
+      <c r="AF121">
+        <v>2.67</v>
+      </c>
+      <c r="AG121">
+        <v>2.33</v>
+      </c>
+      <c r="AH121">
+        <v>1.53</v>
+      </c>
+      <c r="AI121">
+        <v>2</v>
+      </c>
+      <c r="AJ121">
+        <v>1.73</v>
+      </c>
+      <c r="AK121">
+        <v>1.29</v>
+      </c>
+      <c r="AL121">
+        <v>1.36</v>
+      </c>
+      <c r="AM121">
+        <v>1.61</v>
+      </c>
+      <c r="AN121">
+        <v>2.33</v>
+      </c>
+      <c r="AO121">
+        <v>1.33</v>
+      </c>
+      <c r="AP121">
+        <v>2.43</v>
+      </c>
+      <c r="AQ121">
+        <v>1.14</v>
+      </c>
+      <c r="AR121">
+        <v>1.43</v>
+      </c>
+      <c r="AS121">
+        <v>1.9</v>
+      </c>
+      <c r="AT121">
+        <v>3.33</v>
+      </c>
+      <c r="AU121">
+        <v>6</v>
+      </c>
+      <c r="AV121">
+        <v>3</v>
+      </c>
+      <c r="AW121">
+        <v>13</v>
+      </c>
+      <c r="AX121">
+        <v>8</v>
+      </c>
+      <c r="AY121">
+        <v>19</v>
+      </c>
+      <c r="AZ121">
+        <v>11</v>
+      </c>
+      <c r="BA121">
+        <v>4</v>
+      </c>
+      <c r="BB121">
+        <v>7</v>
+      </c>
+      <c r="BC121">
+        <v>11</v>
+      </c>
+      <c r="BD121">
+        <v>1.66</v>
+      </c>
+      <c r="BE121">
+        <v>7.5</v>
+      </c>
+      <c r="BF121">
+        <v>2.45</v>
+      </c>
+      <c r="BG121">
+        <v>1.25</v>
+      </c>
+      <c r="BH121">
+        <v>3.6</v>
+      </c>
+      <c r="BI121">
+        <v>1.42</v>
+      </c>
+      <c r="BJ121">
+        <v>2.62</v>
+      </c>
+      <c r="BK121">
+        <v>1.73</v>
+      </c>
+      <c r="BL121">
+        <v>1.9</v>
+      </c>
+      <c r="BM121">
+        <v>2.23</v>
+      </c>
+      <c r="BN121">
+        <v>1.6</v>
+      </c>
+      <c r="BO121">
+        <v>3.3</v>
+      </c>
+      <c r="BP121">
         <v>1.26</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -25160,7 +25160,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7834431</v>
+        <v>7834437</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25175,10 +25175,10 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H118" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -25190,175 +25190,175 @@
         <v>0</v>
       </c>
       <c r="L118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M118">
         <v>0</v>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="P118" t="s">
         <v>93</v>
       </c>
       <c r="Q118">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="R118">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>8.5</v>
+        <v>5.75</v>
       </c>
       <c r="T118">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="U118">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="V118">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="W118">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X118">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y118">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z118">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AA118">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AB118">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="AC118">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AD118">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AE118">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF118">
         <v>3</v>
       </c>
       <c r="AG118">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="AH118">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AI118">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AJ118">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AK118">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AL118">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AM118">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AN118">
-        <v>2.33</v>
+        <v>1.4</v>
       </c>
       <c r="AO118">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>2.43</v>
+        <v>1.67</v>
       </c>
       <c r="AQ118">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AR118">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AS118">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AT118">
-        <v>3.26</v>
+        <v>3.61</v>
       </c>
       <c r="AU118">
+        <v>4</v>
+      </c>
+      <c r="AV118">
+        <v>5</v>
+      </c>
+      <c r="AW118">
+        <v>17</v>
+      </c>
+      <c r="AX118">
         <v>7</v>
       </c>
-      <c r="AV118">
-        <v>0</v>
-      </c>
-      <c r="AW118">
-        <v>11</v>
-      </c>
-      <c r="AX118">
-        <v>6</v>
-      </c>
       <c r="AY118">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ118">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BA118">
+        <v>2</v>
+      </c>
+      <c r="BB118">
         <v>5</v>
       </c>
-      <c r="BB118">
-        <v>1</v>
-      </c>
       <c r="BC118">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD118">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="BE118">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BF118">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="BG118">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BH118">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="BI118">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BJ118">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="BK118">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BL118">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="BM118">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="BN118">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO118">
-        <v>3.07</v>
+        <v>2.75</v>
       </c>
       <c r="BP118">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="119" spans="1:68">
@@ -25366,7 +25366,7 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>7834437</v>
+        <v>7834431</v>
       </c>
       <c r="C119" t="s">
         <v>68</v>
@@ -25381,10 +25381,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H119" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -25396,175 +25396,175 @@
         <v>0</v>
       </c>
       <c r="L119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M119">
         <v>0</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="P119" t="s">
         <v>93</v>
       </c>
       <c r="Q119">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="R119">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S119">
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="T119">
+        <v>1.4</v>
+      </c>
+      <c r="U119">
+        <v>2.8</v>
+      </c>
+      <c r="V119">
+        <v>3.2</v>
+      </c>
+      <c r="W119">
+        <v>1.27</v>
+      </c>
+      <c r="X119">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y119">
+        <v>1.04</v>
+      </c>
+      <c r="Z119">
         <v>1.45</v>
       </c>
-      <c r="U119">
-        <v>2.63</v>
-      </c>
-      <c r="V119">
-        <v>3</v>
-      </c>
-      <c r="W119">
-        <v>1.33</v>
-      </c>
-      <c r="X119">
-        <v>9</v>
-      </c>
-      <c r="Y119">
+      <c r="AA119">
+        <v>4.05</v>
+      </c>
+      <c r="AB119">
+        <v>6.9</v>
+      </c>
+      <c r="AC119">
         <v>1.06</v>
       </c>
-      <c r="Z119">
-        <v>1.66</v>
-      </c>
-      <c r="AA119">
-        <v>3.6</v>
-      </c>
-      <c r="AB119">
-        <v>6</v>
-      </c>
-      <c r="AC119">
-        <v>1.03</v>
-      </c>
       <c r="AD119">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AE119">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF119">
         <v>3</v>
       </c>
       <c r="AG119">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="AH119">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI119">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AJ119">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AK119">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AL119">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AM119">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AN119">
-        <v>1.4</v>
+        <v>2.33</v>
       </c>
       <c r="AO119">
+        <v>0.6</v>
+      </c>
+      <c r="AP119">
+        <v>2.43</v>
+      </c>
+      <c r="AQ119">
         <v>0.5</v>
       </c>
-      <c r="AP119">
-        <v>1.67</v>
-      </c>
-      <c r="AQ119">
-        <v>0.43</v>
-      </c>
       <c r="AR119">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AS119">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AT119">
-        <v>3.61</v>
+        <v>3.26</v>
       </c>
       <c r="AU119">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV119">
+        <v>0</v>
+      </c>
+      <c r="AW119">
+        <v>11</v>
+      </c>
+      <c r="AX119">
+        <v>6</v>
+      </c>
+      <c r="AY119">
+        <v>18</v>
+      </c>
+      <c r="AZ119">
+        <v>6</v>
+      </c>
+      <c r="BA119">
         <v>5</v>
       </c>
-      <c r="AW119">
-        <v>17</v>
-      </c>
-      <c r="AX119">
-        <v>7</v>
-      </c>
-      <c r="AY119">
-        <v>21</v>
-      </c>
-      <c r="AZ119">
-        <v>12</v>
-      </c>
-      <c r="BA119">
-        <v>2</v>
-      </c>
       <c r="BB119">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BC119">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD119">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="BE119">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF119">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG119">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BH119">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="BI119">
+        <v>1.52</v>
+      </c>
+      <c r="BJ119">
+        <v>2.36</v>
+      </c>
+      <c r="BK119">
+        <v>1.91</v>
+      </c>
+      <c r="BL119">
+        <v>1.8</v>
+      </c>
+      <c r="BM119">
+        <v>2.3</v>
+      </c>
+      <c r="BN119">
         <v>1.5</v>
       </c>
-      <c r="BJ119">
-        <v>2.57</v>
-      </c>
-      <c r="BK119">
-        <v>1.75</v>
-      </c>
-      <c r="BL119">
-        <v>1.96</v>
-      </c>
-      <c r="BM119">
-        <v>2.21</v>
-      </c>
-      <c r="BN119">
-        <v>1.53</v>
-      </c>
       <c r="BO119">
-        <v>2.75</v>
+        <v>3.07</v>
       </c>
       <c r="BP119">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="120" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -25301,16 +25301,16 @@
         <v>5</v>
       </c>
       <c r="AW118">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AX118">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY118">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AZ118">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA118">
         <v>2</v>
@@ -25507,16 +25507,16 @@
         <v>0</v>
       </c>
       <c r="AW119">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AX119">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY119">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ119">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BA119">
         <v>5</v>
@@ -25713,16 +25713,16 @@
         <v>7</v>
       </c>
       <c r="AW120">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX120">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AY120">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ120">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA120">
         <v>5</v>
@@ -25919,16 +25919,16 @@
         <v>3</v>
       </c>
       <c r="AW121">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX121">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY121">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ121">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA121">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="228">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -532,6 +532,9 @@
     <t>['53', '90+7']</t>
   </si>
   <si>
+    <t>['33', '25', '54', '77']</t>
+  </si>
+  <si>
     <t>['75']</t>
   </si>
   <si>
@@ -689,6 +692,12 @@
   </si>
   <si>
     <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['31', '90+7']</t>
+  </si>
+  <si>
+    <t>['57']</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP121"/>
+  <dimension ref="A1:BP124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1384,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ2">
         <v>1.17</v>
@@ -1718,7 +1727,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2130,7 +2139,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2208,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2748,7 +2757,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2954,7 +2963,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3160,7 +3169,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3241,7 +3250,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ11">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3444,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ12">
         <v>0.5</v>
@@ -3653,7 +3662,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ13">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4190,7 +4199,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4271,7 +4280,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4396,7 +4405,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4602,7 +4611,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -5220,7 +5229,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5632,7 +5641,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5713,7 +5722,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ23">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR23">
         <v>1.18</v>
@@ -6250,7 +6259,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6456,7 +6465,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6662,7 +6671,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -7152,7 +7161,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ30">
         <v>0.57</v>
@@ -7280,7 +7289,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7692,7 +7701,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7898,7 +7907,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -7979,7 +7988,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ34">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR34">
         <v>1.15</v>
@@ -8104,7 +8113,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8185,7 +8194,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ35">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR35">
         <v>2.31</v>
@@ -8310,7 +8319,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -8388,7 +8397,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ36">
         <v>1.17</v>
@@ -9418,7 +9427,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ41">
         <v>1.17</v>
@@ -9546,7 +9555,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9624,7 +9633,7 @@
         <v>0.5</v>
       </c>
       <c r="AP42">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ42">
         <v>0.17</v>
@@ -10164,7 +10173,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10576,7 +10585,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10782,7 +10791,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -10860,7 +10869,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ48">
         <v>2.5</v>
@@ -10988,7 +10997,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11481,7 +11490,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ51">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR51">
         <v>1.54</v>
@@ -11812,7 +11821,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12018,7 +12027,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -13126,7 +13135,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ59">
         <v>0.5</v>
@@ -13254,7 +13263,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13335,7 +13344,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ60">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR60">
         <v>1.37</v>
@@ -13460,7 +13469,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -13541,7 +13550,7 @@
         <v>1</v>
       </c>
       <c r="AQ61">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14078,7 +14087,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14156,7 +14165,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ64">
         <v>0.57</v>
@@ -14696,7 +14705,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -15108,7 +15117,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15186,7 +15195,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ69">
         <v>2</v>
@@ -15520,7 +15529,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15804,7 +15813,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
         <v>0</v>
@@ -15932,7 +15941,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16138,7 +16147,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16219,7 +16228,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ74">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR74">
         <v>1.19</v>
@@ -16344,7 +16353,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16756,7 +16765,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17168,7 +17177,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -17661,7 +17670,7 @@
         <v>1</v>
       </c>
       <c r="AQ81">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR81">
         <v>1.87</v>
@@ -18198,7 +18207,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18279,7 +18288,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ84">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR84">
         <v>1.35</v>
@@ -18404,7 +18413,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18688,7 +18697,7 @@
         <v>0</v>
       </c>
       <c r="AP86">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ86">
         <v>0.86</v>
@@ -19228,7 +19237,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19512,7 +19521,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ90">
         <v>1.14</v>
@@ -19846,7 +19855,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20052,7 +20061,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20876,7 +20885,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21082,7 +21091,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21288,7 +21297,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21366,7 +21375,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ99">
         <v>1.33</v>
@@ -21700,7 +21709,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21906,7 +21915,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -21987,7 +21996,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ102">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AR102">
         <v>1.38</v>
@@ -22318,7 +22327,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22399,7 +22408,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ104">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AR104">
         <v>1.59</v>
@@ -22524,7 +22533,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -23014,7 +23023,7 @@
         <v>0.4</v>
       </c>
       <c r="AP107">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ107">
         <v>0.43</v>
@@ -23142,7 +23151,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23426,7 +23435,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AQ109">
         <v>2.5</v>
@@ -23554,7 +23563,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23841,7 +23850,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ111">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="AR111">
         <v>1.95</v>
@@ -23966,7 +23975,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24378,7 +24387,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24456,7 +24465,7 @@
         <v>0.5</v>
       </c>
       <c r="AP114">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AQ114">
         <v>0.86</v>
@@ -24584,7 +24593,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24790,7 +24799,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25301,16 +25310,16 @@
         <v>5</v>
       </c>
       <c r="AW118">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AX118">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY118">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AZ118">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BA118">
         <v>2</v>
@@ -25507,16 +25516,16 @@
         <v>0</v>
       </c>
       <c r="AW119">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AX119">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY119">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AZ119">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BA119">
         <v>5</v>
@@ -25614,7 +25623,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25713,16 +25722,16 @@
         <v>7</v>
       </c>
       <c r="AW120">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX120">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AY120">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ120">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BA120">
         <v>5</v>
@@ -25820,7 +25829,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q121">
         <v>2.8</v>
@@ -25919,16 +25928,16 @@
         <v>3</v>
       </c>
       <c r="AW121">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX121">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AY121">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ121">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA121">
         <v>4</v>
@@ -25977,6 +25986,624 @@
       </c>
       <c r="BP121">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="122" spans="1:68">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>7834433</v>
+      </c>
+      <c r="C122" t="s">
+        <v>68</v>
+      </c>
+      <c r="D122" t="s">
+        <v>69</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45851.79166666666</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122" t="s">
+        <v>80</v>
+      </c>
+      <c r="H122" t="s">
+        <v>79</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="K122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="M122">
+        <v>2</v>
+      </c>
+      <c r="N122">
+        <v>3</v>
+      </c>
+      <c r="O122" t="s">
+        <v>113</v>
+      </c>
+      <c r="P122" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q122">
+        <v>3</v>
+      </c>
+      <c r="R122">
+        <v>1.81</v>
+      </c>
+      <c r="S122">
+        <v>4.6</v>
+      </c>
+      <c r="T122">
+        <v>1.53</v>
+      </c>
+      <c r="U122">
+        <v>2.35</v>
+      </c>
+      <c r="V122">
+        <v>3.94</v>
+      </c>
+      <c r="W122">
+        <v>1.25</v>
+      </c>
+      <c r="X122">
+        <v>7.8</v>
+      </c>
+      <c r="Y122">
+        <v>1.05</v>
+      </c>
+      <c r="Z122">
+        <v>2.02</v>
+      </c>
+      <c r="AA122">
+        <v>2.96</v>
+      </c>
+      <c r="AB122">
+        <v>3.5</v>
+      </c>
+      <c r="AC122">
+        <v>1.12</v>
+      </c>
+      <c r="AD122">
+        <v>6.5</v>
+      </c>
+      <c r="AE122">
+        <v>1.55</v>
+      </c>
+      <c r="AF122">
+        <v>2.6</v>
+      </c>
+      <c r="AG122">
+        <v>2.4</v>
+      </c>
+      <c r="AH122">
+        <v>1.5</v>
+      </c>
+      <c r="AI122">
+        <v>2.19</v>
+      </c>
+      <c r="AJ122">
+        <v>1.65</v>
+      </c>
+      <c r="AK122">
+        <v>1.4</v>
+      </c>
+      <c r="AL122">
+        <v>1.33</v>
+      </c>
+      <c r="AM122">
+        <v>1.65</v>
+      </c>
+      <c r="AN122">
+        <v>2.17</v>
+      </c>
+      <c r="AO122">
+        <v>2</v>
+      </c>
+      <c r="AP122">
+        <v>1.86</v>
+      </c>
+      <c r="AQ122">
+        <v>2.17</v>
+      </c>
+      <c r="AR122">
+        <v>1.58</v>
+      </c>
+      <c r="AS122">
+        <v>1.55</v>
+      </c>
+      <c r="AT122">
+        <v>3.13</v>
+      </c>
+      <c r="AU122">
+        <v>9</v>
+      </c>
+      <c r="AV122">
+        <v>4</v>
+      </c>
+      <c r="AW122">
+        <v>5</v>
+      </c>
+      <c r="AX122">
+        <v>6</v>
+      </c>
+      <c r="AY122">
+        <v>14</v>
+      </c>
+      <c r="AZ122">
+        <v>10</v>
+      </c>
+      <c r="BA122">
+        <v>10</v>
+      </c>
+      <c r="BB122">
+        <v>2</v>
+      </c>
+      <c r="BC122">
+        <v>12</v>
+      </c>
+      <c r="BD122">
+        <v>1.57</v>
+      </c>
+      <c r="BE122">
+        <v>7</v>
+      </c>
+      <c r="BF122">
+        <v>2.48</v>
+      </c>
+      <c r="BG122">
+        <v>1.15</v>
+      </c>
+      <c r="BH122">
+        <v>4.25</v>
+      </c>
+      <c r="BI122">
+        <v>1.42</v>
+      </c>
+      <c r="BJ122">
+        <v>2.62</v>
+      </c>
+      <c r="BK122">
+        <v>1.67</v>
+      </c>
+      <c r="BL122">
+        <v>2.16</v>
+      </c>
+      <c r="BM122">
+        <v>2</v>
+      </c>
+      <c r="BN122">
+        <v>1.72</v>
+      </c>
+      <c r="BO122">
+        <v>2.57</v>
+      </c>
+      <c r="BP122">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:68">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>7834436</v>
+      </c>
+      <c r="C123" t="s">
+        <v>68</v>
+      </c>
+      <c r="D123" t="s">
+        <v>69</v>
+      </c>
+      <c r="E123" s="2">
+        <v>45851.85416666666</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123" t="s">
+        <v>74</v>
+      </c>
+      <c r="H123" t="s">
+        <v>72</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>2</v>
+      </c>
+      <c r="L123">
+        <v>4</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>5</v>
+      </c>
+      <c r="O123" t="s">
+        <v>172</v>
+      </c>
+      <c r="P123" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q123">
+        <v>2.31</v>
+      </c>
+      <c r="R123">
+        <v>2.06</v>
+      </c>
+      <c r="S123">
+        <v>5.5</v>
+      </c>
+      <c r="T123">
+        <v>1.45</v>
+      </c>
+      <c r="U123">
+        <v>2.55</v>
+      </c>
+      <c r="V123">
+        <v>3</v>
+      </c>
+      <c r="W123">
+        <v>1.33</v>
+      </c>
+      <c r="X123">
+        <v>7</v>
+      </c>
+      <c r="Y123">
+        <v>1.06</v>
+      </c>
+      <c r="Z123">
+        <v>1.69</v>
+      </c>
+      <c r="AA123">
+        <v>3.12</v>
+      </c>
+      <c r="AB123">
+        <v>4.8</v>
+      </c>
+      <c r="AC123">
+        <v>1.01</v>
+      </c>
+      <c r="AD123">
+        <v>8</v>
+      </c>
+      <c r="AE123">
+        <v>1.32</v>
+      </c>
+      <c r="AF123">
+        <v>3.1</v>
+      </c>
+      <c r="AG123">
+        <v>2.15</v>
+      </c>
+      <c r="AH123">
+        <v>1.62</v>
+      </c>
+      <c r="AI123">
+        <v>2.1</v>
+      </c>
+      <c r="AJ123">
+        <v>1.7</v>
+      </c>
+      <c r="AK123">
+        <v>1.3</v>
+      </c>
+      <c r="AL123">
+        <v>1.29</v>
+      </c>
+      <c r="AM123">
+        <v>2.3</v>
+      </c>
+      <c r="AN123">
+        <v>2.67</v>
+      </c>
+      <c r="AO123">
+        <v>0.8</v>
+      </c>
+      <c r="AP123">
+        <v>2.71</v>
+      </c>
+      <c r="AQ123">
+        <v>0.67</v>
+      </c>
+      <c r="AR123">
+        <v>1.65</v>
+      </c>
+      <c r="AS123">
+        <v>1.63</v>
+      </c>
+      <c r="AT123">
+        <v>3.28</v>
+      </c>
+      <c r="AU123">
+        <v>10</v>
+      </c>
+      <c r="AV123">
+        <v>3</v>
+      </c>
+      <c r="AW123">
+        <v>8</v>
+      </c>
+      <c r="AX123">
+        <v>9</v>
+      </c>
+      <c r="AY123">
+        <v>18</v>
+      </c>
+      <c r="AZ123">
+        <v>12</v>
+      </c>
+      <c r="BA123">
+        <v>6</v>
+      </c>
+      <c r="BB123">
+        <v>3</v>
+      </c>
+      <c r="BC123">
+        <v>9</v>
+      </c>
+      <c r="BD123">
+        <v>1.48</v>
+      </c>
+      <c r="BE123">
+        <v>8.1</v>
+      </c>
+      <c r="BF123">
+        <v>3.5</v>
+      </c>
+      <c r="BG123">
+        <v>1.2</v>
+      </c>
+      <c r="BH123">
+        <v>4.15</v>
+      </c>
+      <c r="BI123">
+        <v>1.33</v>
+      </c>
+      <c r="BJ123">
+        <v>3.02</v>
+      </c>
+      <c r="BK123">
+        <v>1.57</v>
+      </c>
+      <c r="BL123">
+        <v>2.25</v>
+      </c>
+      <c r="BM123">
+        <v>1.91</v>
+      </c>
+      <c r="BN123">
+        <v>1.8</v>
+      </c>
+      <c r="BO123">
+        <v>2.4</v>
+      </c>
+      <c r="BP123">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:68">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7834439</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>69</v>
+      </c>
+      <c r="E124" s="2">
+        <v>45851.85416666666</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124" t="s">
+        <v>70</v>
+      </c>
+      <c r="H124" t="s">
+        <v>81</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124" t="s">
+        <v>93</v>
+      </c>
+      <c r="P124" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q124">
+        <v>3.17</v>
+      </c>
+      <c r="R124">
+        <v>1.86</v>
+      </c>
+      <c r="S124">
+        <v>4.05</v>
+      </c>
+      <c r="T124">
+        <v>1.5</v>
+      </c>
+      <c r="U124">
+        <v>2.5</v>
+      </c>
+      <c r="V124">
+        <v>3.7</v>
+      </c>
+      <c r="W124">
+        <v>1.29</v>
+      </c>
+      <c r="X124">
+        <v>10</v>
+      </c>
+      <c r="Y124">
+        <v>1.05</v>
+      </c>
+      <c r="Z124">
+        <v>1.97</v>
+      </c>
+      <c r="AA124">
+        <v>3.01</v>
+      </c>
+      <c r="AB124">
+        <v>3.57</v>
+      </c>
+      <c r="AC124">
+        <v>1.11</v>
+      </c>
+      <c r="AD124">
+        <v>6</v>
+      </c>
+      <c r="AE124">
+        <v>1.44</v>
+      </c>
+      <c r="AF124">
+        <v>2.5</v>
+      </c>
+      <c r="AG124">
+        <v>2.4</v>
+      </c>
+      <c r="AH124">
+        <v>1.5</v>
+      </c>
+      <c r="AI124">
+        <v>1.93</v>
+      </c>
+      <c r="AJ124">
+        <v>1.75</v>
+      </c>
+      <c r="AK124">
+        <v>1.36</v>
+      </c>
+      <c r="AL124">
+        <v>1.34</v>
+      </c>
+      <c r="AM124">
+        <v>1.62</v>
+      </c>
+      <c r="AN124">
+        <v>1.17</v>
+      </c>
+      <c r="AO124">
+        <v>0.4</v>
+      </c>
+      <c r="AP124">
+        <v>1</v>
+      </c>
+      <c r="AQ124">
+        <v>0.83</v>
+      </c>
+      <c r="AR124">
+        <v>1.81</v>
+      </c>
+      <c r="AS124">
+        <v>1.26</v>
+      </c>
+      <c r="AT124">
+        <v>3.07</v>
+      </c>
+      <c r="AU124">
+        <v>0</v>
+      </c>
+      <c r="AV124">
+        <v>4</v>
+      </c>
+      <c r="AW124">
+        <v>5</v>
+      </c>
+      <c r="AX124">
+        <v>8</v>
+      </c>
+      <c r="AY124">
+        <v>5</v>
+      </c>
+      <c r="AZ124">
+        <v>12</v>
+      </c>
+      <c r="BA124">
+        <v>3</v>
+      </c>
+      <c r="BB124">
+        <v>5</v>
+      </c>
+      <c r="BC124">
+        <v>8</v>
+      </c>
+      <c r="BD124">
+        <v>1.57</v>
+      </c>
+      <c r="BE124">
+        <v>9</v>
+      </c>
+      <c r="BF124">
+        <v>2.75</v>
+      </c>
+      <c r="BG124">
+        <v>1.19</v>
+      </c>
+      <c r="BH124">
+        <v>3.95</v>
+      </c>
+      <c r="BI124">
+        <v>1.3</v>
+      </c>
+      <c r="BJ124">
+        <v>2.92</v>
+      </c>
+      <c r="BK124">
+        <v>1.78</v>
+      </c>
+      <c r="BL124">
+        <v>2.2</v>
+      </c>
+      <c r="BM124">
+        <v>2</v>
+      </c>
+      <c r="BN124">
+        <v>1.76</v>
+      </c>
+      <c r="BO124">
+        <v>2.48</v>
+      </c>
+      <c r="BP124">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="229">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -533,6 +533,9 @@
   </si>
   <si>
     <t>['33', '25', '54', '77']</t>
+  </si>
+  <si>
+    <t>['12', '49']</t>
   </si>
   <si>
     <t>['75']</t>
@@ -1059,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP124"/>
+  <dimension ref="A1:BP125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1599,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ3">
         <v>0.43</v>
@@ -1727,7 +1730,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2014,7 +2017,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ5">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2139,7 +2142,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2757,7 +2760,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2963,7 +2966,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3169,7 +3172,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4199,7 +4202,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4405,7 +4408,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4611,7 +4614,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -5229,7 +5232,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5641,7 +5644,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5719,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ23">
         <v>0.83</v>
@@ -6134,7 +6137,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ25">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR25">
         <v>1.71</v>
@@ -6259,7 +6262,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6465,7 +6468,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6671,7 +6674,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -7289,7 +7292,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7701,7 +7704,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7907,7 +7910,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8113,7 +8116,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8319,7 +8322,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -9555,7 +9558,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9636,7 +9639,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ42">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR42">
         <v>1.15</v>
@@ -10173,7 +10176,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10251,7 +10254,7 @@
         <v>0.5</v>
       </c>
       <c r="AP45">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ45">
         <v>1</v>
@@ -10585,7 +10588,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10791,7 +10794,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -10997,7 +11000,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11821,7 +11824,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12027,7 +12030,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -13263,7 +13266,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13469,7 +13472,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -13962,7 +13965,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ63">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR63">
         <v>1.64</v>
@@ -14087,7 +14090,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14705,7 +14708,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -15117,7 +15120,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15529,7 +15532,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15607,7 +15610,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ71">
         <v>1.14</v>
@@ -15941,7 +15944,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16147,7 +16150,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16353,7 +16356,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16765,7 +16768,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17177,7 +17180,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -17876,7 +17879,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ82">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR82">
         <v>1.43</v>
@@ -18207,7 +18210,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18413,7 +18416,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18491,7 +18494,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ85">
         <v>1.17</v>
@@ -19237,7 +19240,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19855,7 +19858,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20061,7 +20064,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20885,7 +20888,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21091,7 +21094,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21297,7 +21300,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21709,7 +21712,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21915,7 +21918,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22202,7 +22205,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ103">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AR103">
         <v>1.82</v>
@@ -22327,7 +22330,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22405,7 +22408,7 @@
         <v>0.25</v>
       </c>
       <c r="AP104">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ104">
         <v>0.67</v>
@@ -22533,7 +22536,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -23151,7 +23154,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23563,7 +23566,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23975,7 +23978,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24387,7 +24390,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24593,7 +24596,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24799,7 +24802,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25623,7 +25626,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25829,7 +25832,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q121">
         <v>2.8</v>
@@ -26035,7 +26038,7 @@
         <v>113</v>
       </c>
       <c r="P122" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26131,19 +26134,19 @@
         <v>9</v>
       </c>
       <c r="AV122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW122">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX122">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY122">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ122">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA122">
         <v>10</v>
@@ -26340,16 +26343,16 @@
         <v>3</v>
       </c>
       <c r="AW123">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX123">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY123">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ123">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA123">
         <v>6</v>
@@ -26447,7 +26450,7 @@
         <v>93</v>
       </c>
       <c r="P124" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q124">
         <v>3.17</v>
@@ -26546,13 +26549,13 @@
         <v>4</v>
       </c>
       <c r="AW124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX124">
         <v>8</v>
       </c>
       <c r="AY124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ124">
         <v>12</v>
@@ -26604,6 +26607,212 @@
       </c>
       <c r="BP124">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="125" spans="1:68">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>7834440</v>
+      </c>
+      <c r="C125" t="s">
+        <v>68</v>
+      </c>
+      <c r="D125" t="s">
+        <v>69</v>
+      </c>
+      <c r="E125" s="2">
+        <v>45852.83333333334</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125" t="s">
+        <v>71</v>
+      </c>
+      <c r="H125" t="s">
+        <v>85</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>2</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>2</v>
+      </c>
+      <c r="O125" t="s">
+        <v>173</v>
+      </c>
+      <c r="P125" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q125">
+        <v>3.2</v>
+      </c>
+      <c r="R125">
+        <v>2</v>
+      </c>
+      <c r="S125">
+        <v>3.4</v>
+      </c>
+      <c r="T125">
+        <v>1.5</v>
+      </c>
+      <c r="U125">
+        <v>2.64</v>
+      </c>
+      <c r="V125">
+        <v>3.25</v>
+      </c>
+      <c r="W125">
+        <v>1.28</v>
+      </c>
+      <c r="X125">
+        <v>9.5</v>
+      </c>
+      <c r="Y125">
+        <v>1.06</v>
+      </c>
+      <c r="Z125">
+        <v>2.7</v>
+      </c>
+      <c r="AA125">
+        <v>3.1</v>
+      </c>
+      <c r="AB125">
+        <v>2.7</v>
+      </c>
+      <c r="AC125">
+        <v>1.06</v>
+      </c>
+      <c r="AD125">
+        <v>7</v>
+      </c>
+      <c r="AE125">
+        <v>1.4</v>
+      </c>
+      <c r="AF125">
+        <v>2.62</v>
+      </c>
+      <c r="AG125">
+        <v>2.4</v>
+      </c>
+      <c r="AH125">
+        <v>1.57</v>
+      </c>
+      <c r="AI125">
+        <v>1.95</v>
+      </c>
+      <c r="AJ125">
+        <v>1.85</v>
+      </c>
+      <c r="AK125">
+        <v>1.35</v>
+      </c>
+      <c r="AL125">
+        <v>1.33</v>
+      </c>
+      <c r="AM125">
+        <v>1.44</v>
+      </c>
+      <c r="AN125">
+        <v>1.33</v>
+      </c>
+      <c r="AO125">
+        <v>0.17</v>
+      </c>
+      <c r="AP125">
+        <v>1.57</v>
+      </c>
+      <c r="AQ125">
+        <v>0.14</v>
+      </c>
+      <c r="AR125">
+        <v>1.62</v>
+      </c>
+      <c r="AS125">
+        <v>1.35</v>
+      </c>
+      <c r="AT125">
+        <v>2.97</v>
+      </c>
+      <c r="AU125">
+        <v>4</v>
+      </c>
+      <c r="AV125">
+        <v>6</v>
+      </c>
+      <c r="AW125">
+        <v>3</v>
+      </c>
+      <c r="AX125">
+        <v>7</v>
+      </c>
+      <c r="AY125">
+        <v>7</v>
+      </c>
+      <c r="AZ125">
+        <v>13</v>
+      </c>
+      <c r="BA125">
+        <v>1</v>
+      </c>
+      <c r="BB125">
+        <v>8</v>
+      </c>
+      <c r="BC125">
+        <v>9</v>
+      </c>
+      <c r="BD125">
+        <v>1.85</v>
+      </c>
+      <c r="BE125">
+        <v>8.5</v>
+      </c>
+      <c r="BF125">
+        <v>2.05</v>
+      </c>
+      <c r="BG125">
+        <v>1.24</v>
+      </c>
+      <c r="BH125">
+        <v>3.6</v>
+      </c>
+      <c r="BI125">
+        <v>1.36</v>
+      </c>
+      <c r="BJ125">
+        <v>2.55</v>
+      </c>
+      <c r="BK125">
+        <v>1.65</v>
+      </c>
+      <c r="BL125">
+        <v>2.04</v>
+      </c>
+      <c r="BM125">
+        <v>2.05</v>
+      </c>
+      <c r="BN125">
+        <v>1.65</v>
+      </c>
+      <c r="BO125">
+        <v>2.62</v>
+      </c>
+      <c r="BP125">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -26134,19 +26134,19 @@
         <v>9</v>
       </c>
       <c r="AV122">
+        <v>4</v>
+      </c>
+      <c r="AW122">
         <v>5</v>
       </c>
-      <c r="AW122">
-        <v>3</v>
-      </c>
       <c r="AX122">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY122">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ122">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA122">
         <v>10</v>
@@ -26343,16 +26343,16 @@
         <v>3</v>
       </c>
       <c r="AW123">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX123">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY123">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ123">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA123">
         <v>6</v>
@@ -26549,13 +26549,13 @@
         <v>4</v>
       </c>
       <c r="AW124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX124">
         <v>8</v>
       </c>
       <c r="AY124">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ124">
         <v>12</v>
@@ -26758,13 +26758,13 @@
         <v>3</v>
       </c>
       <c r="AX125">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AY125">
         <v>7</v>
       </c>
       <c r="AZ125">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BA125">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -26758,13 +26758,13 @@
         <v>3</v>
       </c>
       <c r="AX125">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AY125">
         <v>7</v>
       </c>
       <c r="AZ125">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BA125">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -26758,13 +26758,13 @@
         <v>3</v>
       </c>
       <c r="AX125">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AY125">
         <v>7</v>
       </c>
       <c r="AZ125">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BA125">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="234">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -538,6 +538,12 @@
     <t>['12', '49']</t>
   </si>
   <si>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['43', '48']</t>
+  </si>
+  <si>
     <t>['75']</t>
   </si>
   <si>
@@ -701,6 +707,15 @@
   </si>
   <si>
     <t>['57']</t>
+  </si>
+  <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['9', '64']</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP125"/>
+  <dimension ref="A1:BP130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1605,7 +1620,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ3">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1730,7 +1745,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2142,7 +2157,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2632,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8">
         <v>1.14</v>
@@ -2760,7 +2775,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2966,7 +2981,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3047,7 +3062,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3172,7 +3187,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3250,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ11">
         <v>0.83</v>
@@ -3662,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ13">
         <v>0.67</v>
@@ -3868,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ14">
         <v>0</v>
@@ -4077,7 +4092,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4202,7 +4217,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4408,7 +4423,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4614,7 +4629,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -4695,7 +4710,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ18">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5232,7 +5247,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5310,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
         <v>1.17</v>
@@ -5516,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="AP22">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ22">
         <v>1.14</v>
@@ -5644,7 +5659,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5928,10 +5943,10 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR24">
         <v>1.52</v>
@@ -6262,7 +6277,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6468,7 +6483,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6674,7 +6689,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -6755,7 +6770,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR28">
         <v>1.47</v>
@@ -7292,7 +7307,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7373,7 +7388,7 @@
         <v>2</v>
       </c>
       <c r="AQ31">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>2.54</v>
@@ -7576,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ32">
         <v>0.5</v>
@@ -7704,7 +7719,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7782,10 +7797,10 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ33">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR33">
         <v>1.9</v>
@@ -7910,7 +7925,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8116,7 +8131,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8322,7 +8337,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -9224,7 +9239,7 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ40">
         <v>1.14</v>
@@ -9558,7 +9573,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9845,7 +9860,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ43">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR43">
         <v>1.55</v>
@@ -10176,7 +10191,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10588,7 +10603,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10794,7 +10809,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -11000,7 +11015,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11081,7 +11096,7 @@
         <v>2.6</v>
       </c>
       <c r="AQ49">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR49">
         <v>1.66</v>
@@ -11284,7 +11299,7 @@
         <v>0.5</v>
       </c>
       <c r="AP50">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ50">
         <v>1.33</v>
@@ -11824,7 +11839,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -11902,10 +11917,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR53">
         <v>1.35</v>
@@ -12030,7 +12045,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -12520,7 +12535,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ56">
         <v>1.17</v>
@@ -12729,7 +12744,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ57">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR57">
         <v>2.08</v>
@@ -12932,7 +12947,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ58">
         <v>1.17</v>
@@ -13266,7 +13281,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13472,7 +13487,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -13550,7 +13565,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ61">
         <v>2.17</v>
@@ -14090,7 +14105,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14374,10 +14389,10 @@
         <v>0.67</v>
       </c>
       <c r="AP65">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ65">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>1.2</v>
@@ -14708,7 +14723,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -15120,7 +15135,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15201,7 +15216,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ69">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR69">
         <v>1.46</v>
@@ -15404,7 +15419,7 @@
         <v>0.67</v>
       </c>
       <c r="AP70">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15532,7 +15547,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15944,7 +15959,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16025,7 +16040,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ73">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR73">
         <v>1.93</v>
@@ -16150,7 +16165,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16356,7 +16371,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16768,7 +16783,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17052,10 +17067,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR78">
         <v>1.7</v>
@@ -17180,7 +17195,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -17464,7 +17479,7 @@
         <v>0.75</v>
       </c>
       <c r="AP80">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ80">
         <v>0.57</v>
@@ -17670,7 +17685,7 @@
         <v>0.33</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ81">
         <v>0.83</v>
@@ -17876,7 +17891,7 @@
         <v>0.25</v>
       </c>
       <c r="AP82">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ82">
         <v>0.14</v>
@@ -18210,7 +18225,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18416,7 +18431,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18909,7 +18924,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ87">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR87">
         <v>1.46</v>
@@ -19240,7 +19255,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19318,7 +19333,7 @@
         <v>3</v>
       </c>
       <c r="AP89">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ89">
         <v>2.5</v>
@@ -19858,7 +19873,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20064,7 +20079,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20351,7 +20366,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR94">
         <v>2.33</v>
@@ -20888,7 +20903,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -20966,10 +20981,10 @@
         <v>1.75</v>
       </c>
       <c r="AP97">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AR97">
         <v>1.77</v>
@@ -21094,7 +21109,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21300,7 +21315,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21584,7 +21599,7 @@
         <v>0</v>
       </c>
       <c r="AP100">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100">
         <v>0</v>
@@ -21712,7 +21727,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21793,7 +21808,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ101">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR101">
         <v>1.36</v>
@@ -21918,7 +21933,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22330,7 +22345,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22536,7 +22551,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -22614,7 +22629,7 @@
         <v>0.4</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AQ105">
         <v>1.14</v>
@@ -23029,7 +23044,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ107">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR107">
         <v>1.58</v>
@@ -23154,7 +23169,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23232,7 +23247,7 @@
         <v>1</v>
       </c>
       <c r="AP108">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AQ108">
         <v>1.14</v>
@@ -23566,7 +23581,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23850,7 +23865,7 @@
         <v>0.5</v>
       </c>
       <c r="AP111">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AQ111">
         <v>0.83</v>
@@ -23978,7 +23993,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24056,7 +24071,7 @@
         <v>0.8</v>
       </c>
       <c r="AP112">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ112">
         <v>1.17</v>
@@ -24390,7 +24405,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24596,7 +24611,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24677,7 +24692,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ115">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AR115">
         <v>1.22</v>
@@ -24802,7 +24817,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25295,7 +25310,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ118">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR118">
         <v>2.2</v>
@@ -25501,7 +25516,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ119">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AR119">
         <v>1.94</v>
@@ -25626,7 +25641,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25832,7 +25847,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q121">
         <v>2.8</v>
@@ -26038,7 +26053,7 @@
         <v>113</v>
       </c>
       <c r="P122" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26450,7 +26465,7 @@
         <v>93</v>
       </c>
       <c r="P124" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q124">
         <v>3.17</v>
@@ -26813,6 +26828,1036 @@
       </c>
       <c r="BP125">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="126" spans="1:68">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>7834443</v>
+      </c>
+      <c r="C126" t="s">
+        <v>68</v>
+      </c>
+      <c r="D126" t="s">
+        <v>69</v>
+      </c>
+      <c r="E126" s="2">
+        <v>45854.79166666666</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126" t="s">
+        <v>76</v>
+      </c>
+      <c r="H126" t="s">
+        <v>87</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="M126">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>2</v>
+      </c>
+      <c r="O126" t="s">
+        <v>95</v>
+      </c>
+      <c r="P126" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q126">
+        <v>1.96</v>
+      </c>
+      <c r="R126">
+        <v>2.18</v>
+      </c>
+      <c r="S126">
+        <v>7.6</v>
+      </c>
+      <c r="T126">
+        <v>1.4</v>
+      </c>
+      <c r="U126">
+        <v>2.8</v>
+      </c>
+      <c r="V126">
+        <v>2.8</v>
+      </c>
+      <c r="W126">
+        <v>1.38</v>
+      </c>
+      <c r="X126">
+        <v>8</v>
+      </c>
+      <c r="Y126">
+        <v>1.08</v>
+      </c>
+      <c r="Z126">
+        <v>1.41</v>
+      </c>
+      <c r="AA126">
+        <v>4.1</v>
+      </c>
+      <c r="AB126">
+        <v>9.15</v>
+      </c>
+      <c r="AC126">
+        <v>1.06</v>
+      </c>
+      <c r="AD126">
+        <v>8.5</v>
+      </c>
+      <c r="AE126">
+        <v>1.35</v>
+      </c>
+      <c r="AF126">
+        <v>3.12</v>
+      </c>
+      <c r="AG126">
+        <v>1.95</v>
+      </c>
+      <c r="AH126">
+        <v>1.73</v>
+      </c>
+      <c r="AI126">
+        <v>2.25</v>
+      </c>
+      <c r="AJ126">
+        <v>1.6</v>
+      </c>
+      <c r="AK126">
+        <v>1.18</v>
+      </c>
+      <c r="AL126">
+        <v>1.2</v>
+      </c>
+      <c r="AM126">
+        <v>2.85</v>
+      </c>
+      <c r="AN126">
+        <v>1.4</v>
+      </c>
+      <c r="AO126">
+        <v>1</v>
+      </c>
+      <c r="AP126">
+        <v>1.33</v>
+      </c>
+      <c r="AQ126">
+        <v>1</v>
+      </c>
+      <c r="AR126">
+        <v>1.72</v>
+      </c>
+      <c r="AS126">
+        <v>1.46</v>
+      </c>
+      <c r="AT126">
+        <v>3.18</v>
+      </c>
+      <c r="AU126">
+        <v>4</v>
+      </c>
+      <c r="AV126">
+        <v>2</v>
+      </c>
+      <c r="AW126">
+        <v>13</v>
+      </c>
+      <c r="AX126">
+        <v>2</v>
+      </c>
+      <c r="AY126">
+        <v>17</v>
+      </c>
+      <c r="AZ126">
+        <v>4</v>
+      </c>
+      <c r="BA126">
+        <v>7</v>
+      </c>
+      <c r="BB126">
+        <v>3</v>
+      </c>
+      <c r="BC126">
+        <v>10</v>
+      </c>
+      <c r="BD126">
+        <v>1.18</v>
+      </c>
+      <c r="BE126">
+        <v>16</v>
+      </c>
+      <c r="BF126">
+        <v>7.5</v>
+      </c>
+      <c r="BG126">
+        <v>1.18</v>
+      </c>
+      <c r="BH126">
+        <v>4.33</v>
+      </c>
+      <c r="BI126">
+        <v>1.33</v>
+      </c>
+      <c r="BJ126">
+        <v>3</v>
+      </c>
+      <c r="BK126">
+        <v>1.68</v>
+      </c>
+      <c r="BL126">
+        <v>2.3</v>
+      </c>
+      <c r="BM126">
+        <v>1.85</v>
+      </c>
+      <c r="BN126">
+        <v>1.85</v>
+      </c>
+      <c r="BO126">
+        <v>2.4</v>
+      </c>
+      <c r="BP126">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="127" spans="1:68">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>7834449</v>
+      </c>
+      <c r="C127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D127" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="2">
+        <v>45854.8125</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127" t="s">
+        <v>81</v>
+      </c>
+      <c r="H127" t="s">
+        <v>80</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>1</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>93</v>
+      </c>
+      <c r="P127" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q127">
+        <v>3.25</v>
+      </c>
+      <c r="R127">
+        <v>1.83</v>
+      </c>
+      <c r="S127">
+        <v>3.72</v>
+      </c>
+      <c r="T127">
+        <v>1.62</v>
+      </c>
+      <c r="U127">
+        <v>2.2</v>
+      </c>
+      <c r="V127">
+        <v>3.4</v>
+      </c>
+      <c r="W127">
+        <v>1.22</v>
+      </c>
+      <c r="X127">
+        <v>9</v>
+      </c>
+      <c r="Y127">
+        <v>1.03</v>
+      </c>
+      <c r="Z127">
+        <v>2.4</v>
+      </c>
+      <c r="AA127">
+        <v>2.8</v>
+      </c>
+      <c r="AB127">
+        <v>3.25</v>
+      </c>
+      <c r="AC127">
+        <v>1.14</v>
+      </c>
+      <c r="AD127">
+        <v>5.5</v>
+      </c>
+      <c r="AE127">
+        <v>1.62</v>
+      </c>
+      <c r="AF127">
+        <v>2.2</v>
+      </c>
+      <c r="AG127">
+        <v>2.8</v>
+      </c>
+      <c r="AH127">
+        <v>1.4</v>
+      </c>
+      <c r="AI127">
+        <v>2.25</v>
+      </c>
+      <c r="AJ127">
+        <v>1.57</v>
+      </c>
+      <c r="AK127">
+        <v>1.4</v>
+      </c>
+      <c r="AL127">
+        <v>1.33</v>
+      </c>
+      <c r="AM127">
+        <v>1.53</v>
+      </c>
+      <c r="AN127">
+        <v>2.17</v>
+      </c>
+      <c r="AO127">
+        <v>0.5</v>
+      </c>
+      <c r="AP127">
+        <v>1.86</v>
+      </c>
+      <c r="AQ127">
+        <v>0.86</v>
+      </c>
+      <c r="AR127">
+        <v>1.38</v>
+      </c>
+      <c r="AS127">
+        <v>1.1</v>
+      </c>
+      <c r="AT127">
+        <v>2.48</v>
+      </c>
+      <c r="AU127">
+        <v>3</v>
+      </c>
+      <c r="AV127">
+        <v>3</v>
+      </c>
+      <c r="AW127">
+        <v>14</v>
+      </c>
+      <c r="AX127">
+        <v>3</v>
+      </c>
+      <c r="AY127">
+        <v>17</v>
+      </c>
+      <c r="AZ127">
+        <v>6</v>
+      </c>
+      <c r="BA127">
+        <v>7</v>
+      </c>
+      <c r="BB127">
+        <v>3</v>
+      </c>
+      <c r="BC127">
+        <v>10</v>
+      </c>
+      <c r="BD127">
+        <v>1.67</v>
+      </c>
+      <c r="BE127">
+        <v>6.25</v>
+      </c>
+      <c r="BF127">
+        <v>2.26</v>
+      </c>
+      <c r="BG127">
+        <v>1.33</v>
+      </c>
+      <c r="BH127">
+        <v>3</v>
+      </c>
+      <c r="BI127">
+        <v>1.57</v>
+      </c>
+      <c r="BJ127">
+        <v>2.25</v>
+      </c>
+      <c r="BK127">
+        <v>1.91</v>
+      </c>
+      <c r="BL127">
+        <v>1.8</v>
+      </c>
+      <c r="BM127">
+        <v>2.4</v>
+      </c>
+      <c r="BN127">
+        <v>1.5</v>
+      </c>
+      <c r="BO127">
+        <v>3.14</v>
+      </c>
+      <c r="BP127">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="128" spans="1:68">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>7834444</v>
+      </c>
+      <c r="C128" t="s">
+        <v>68</v>
+      </c>
+      <c r="D128" t="s">
+        <v>69</v>
+      </c>
+      <c r="E128" s="2">
+        <v>45854.83333333334</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128" t="s">
+        <v>89</v>
+      </c>
+      <c r="H128" t="s">
+        <v>75</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="O128" t="s">
+        <v>174</v>
+      </c>
+      <c r="P128" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q128">
+        <v>4.8</v>
+      </c>
+      <c r="R128">
+        <v>2</v>
+      </c>
+      <c r="S128">
+        <v>2.25</v>
+      </c>
+      <c r="T128">
+        <v>1.5</v>
+      </c>
+      <c r="U128">
+        <v>2.4</v>
+      </c>
+      <c r="V128">
+        <v>3.46</v>
+      </c>
+      <c r="W128">
+        <v>1.28</v>
+      </c>
+      <c r="X128">
+        <v>8.5</v>
+      </c>
+      <c r="Y128">
+        <v>1.04</v>
+      </c>
+      <c r="Z128">
+        <v>3.9</v>
+      </c>
+      <c r="AA128">
+        <v>3</v>
+      </c>
+      <c r="AB128">
+        <v>1.8</v>
+      </c>
+      <c r="AC128">
+        <v>1.08</v>
+      </c>
+      <c r="AD128">
+        <v>6.5</v>
+      </c>
+      <c r="AE128">
+        <v>1.4</v>
+      </c>
+      <c r="AF128">
+        <v>2.7</v>
+      </c>
+      <c r="AG128">
+        <v>2.3</v>
+      </c>
+      <c r="AH128">
+        <v>1.55</v>
+      </c>
+      <c r="AI128">
+        <v>1.97</v>
+      </c>
+      <c r="AJ128">
+        <v>1.65</v>
+      </c>
+      <c r="AK128">
+        <v>1.33</v>
+      </c>
+      <c r="AL128">
+        <v>1.3</v>
+      </c>
+      <c r="AM128">
+        <v>1.14</v>
+      </c>
+      <c r="AN128">
+        <v>1</v>
+      </c>
+      <c r="AO128">
+        <v>2</v>
+      </c>
+      <c r="AP128">
+        <v>1.33</v>
+      </c>
+      <c r="AQ128">
+        <v>1.67</v>
+      </c>
+      <c r="AR128">
+        <v>1.79</v>
+      </c>
+      <c r="AS128">
+        <v>1.56</v>
+      </c>
+      <c r="AT128">
+        <v>3.35</v>
+      </c>
+      <c r="AU128">
+        <v>5</v>
+      </c>
+      <c r="AV128">
+        <v>6</v>
+      </c>
+      <c r="AW128">
+        <v>4</v>
+      </c>
+      <c r="AX128">
+        <v>5</v>
+      </c>
+      <c r="AY128">
+        <v>9</v>
+      </c>
+      <c r="AZ128">
+        <v>11</v>
+      </c>
+      <c r="BA128">
+        <v>3</v>
+      </c>
+      <c r="BB128">
+        <v>8</v>
+      </c>
+      <c r="BC128">
+        <v>11</v>
+      </c>
+      <c r="BD128">
+        <v>2.73</v>
+      </c>
+      <c r="BE128">
+        <v>6.75</v>
+      </c>
+      <c r="BF128">
+        <v>1.63</v>
+      </c>
+      <c r="BG128">
+        <v>1.2</v>
+      </c>
+      <c r="BH128">
+        <v>3.8</v>
+      </c>
+      <c r="BI128">
+        <v>1.38</v>
+      </c>
+      <c r="BJ128">
+        <v>2.8</v>
+      </c>
+      <c r="BK128">
+        <v>1.65</v>
+      </c>
+      <c r="BL128">
+        <v>2.2</v>
+      </c>
+      <c r="BM128">
+        <v>2</v>
+      </c>
+      <c r="BN128">
+        <v>1.73</v>
+      </c>
+      <c r="BO128">
+        <v>2.5</v>
+      </c>
+      <c r="BP128">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="129" spans="1:68">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>7834445</v>
+      </c>
+      <c r="C129" t="s">
+        <v>68</v>
+      </c>
+      <c r="D129" t="s">
+        <v>69</v>
+      </c>
+      <c r="E129" s="2">
+        <v>45854.89583333334</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129" t="s">
+        <v>79</v>
+      </c>
+      <c r="H129" t="s">
+        <v>73</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>2</v>
+      </c>
+      <c r="L129">
+        <v>2</v>
+      </c>
+      <c r="M129">
+        <v>2</v>
+      </c>
+      <c r="N129">
+        <v>4</v>
+      </c>
+      <c r="O129" t="s">
+        <v>175</v>
+      </c>
+      <c r="P129" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q129">
+        <v>2.84</v>
+      </c>
+      <c r="R129">
+        <v>1.9</v>
+      </c>
+      <c r="S129">
+        <v>4.5</v>
+      </c>
+      <c r="T129">
+        <v>1.56</v>
+      </c>
+      <c r="U129">
+        <v>2.25</v>
+      </c>
+      <c r="V129">
+        <v>3.72</v>
+      </c>
+      <c r="W129">
+        <v>1.2</v>
+      </c>
+      <c r="X129">
+        <v>9.1</v>
+      </c>
+      <c r="Y129">
+        <v>1</v>
+      </c>
+      <c r="Z129">
+        <v>2.33</v>
+      </c>
+      <c r="AA129">
+        <v>3</v>
+      </c>
+      <c r="AB129">
+        <v>3.4</v>
+      </c>
+      <c r="AC129">
+        <v>1.13</v>
+      </c>
+      <c r="AD129">
+        <v>6</v>
+      </c>
+      <c r="AE129">
+        <v>1.57</v>
+      </c>
+      <c r="AF129">
+        <v>2.3</v>
+      </c>
+      <c r="AG129">
+        <v>2.75</v>
+      </c>
+      <c r="AH129">
+        <v>1.4</v>
+      </c>
+      <c r="AI129">
+        <v>2.25</v>
+      </c>
+      <c r="AJ129">
+        <v>1.57</v>
+      </c>
+      <c r="AK129">
+        <v>1.3</v>
+      </c>
+      <c r="AL129">
+        <v>1.32</v>
+      </c>
+      <c r="AM129">
+        <v>1.57</v>
+      </c>
+      <c r="AN129">
+        <v>1.86</v>
+      </c>
+      <c r="AO129">
+        <v>0.5</v>
+      </c>
+      <c r="AP129">
+        <v>1.75</v>
+      </c>
+      <c r="AQ129">
+        <v>0.57</v>
+      </c>
+      <c r="AR129">
+        <v>1.61</v>
+      </c>
+      <c r="AS129">
+        <v>1.2</v>
+      </c>
+      <c r="AT129">
+        <v>2.81</v>
+      </c>
+      <c r="AU129">
+        <v>4</v>
+      </c>
+      <c r="AV129">
+        <v>6</v>
+      </c>
+      <c r="AW129">
+        <v>14</v>
+      </c>
+      <c r="AX129">
+        <v>9</v>
+      </c>
+      <c r="AY129">
+        <v>18</v>
+      </c>
+      <c r="AZ129">
+        <v>15</v>
+      </c>
+      <c r="BA129">
+        <v>6</v>
+      </c>
+      <c r="BB129">
+        <v>4</v>
+      </c>
+      <c r="BC129">
+        <v>10</v>
+      </c>
+      <c r="BD129">
+        <v>1.58</v>
+      </c>
+      <c r="BE129">
+        <v>9.6</v>
+      </c>
+      <c r="BF129">
+        <v>3.14</v>
+      </c>
+      <c r="BG129">
+        <v>1.2</v>
+      </c>
+      <c r="BH129">
+        <v>4.05</v>
+      </c>
+      <c r="BI129">
+        <v>1.4</v>
+      </c>
+      <c r="BJ129">
+        <v>2.75</v>
+      </c>
+      <c r="BK129">
+        <v>1.83</v>
+      </c>
+      <c r="BL129">
+        <v>2.14</v>
+      </c>
+      <c r="BM129">
+        <v>2.05</v>
+      </c>
+      <c r="BN129">
+        <v>1.72</v>
+      </c>
+      <c r="BO129">
+        <v>2.6</v>
+      </c>
+      <c r="BP129">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7834442</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45854.89583333334</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130" t="s">
+        <v>82</v>
+      </c>
+      <c r="H130" t="s">
+        <v>86</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130" t="s">
+        <v>93</v>
+      </c>
+      <c r="P130" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q130">
+        <v>2.03</v>
+      </c>
+      <c r="R130">
+        <v>2.22</v>
+      </c>
+      <c r="S130">
+        <v>6.66</v>
+      </c>
+      <c r="T130">
+        <v>1.42</v>
+      </c>
+      <c r="U130">
+        <v>2.62</v>
+      </c>
+      <c r="V130">
+        <v>2.8</v>
+      </c>
+      <c r="W130">
+        <v>1.37</v>
+      </c>
+      <c r="X130">
+        <v>6.7</v>
+      </c>
+      <c r="Y130">
+        <v>1.07</v>
+      </c>
+      <c r="Z130">
+        <v>1.39</v>
+      </c>
+      <c r="AA130">
+        <v>4.46</v>
+      </c>
+      <c r="AB130">
+        <v>6.9</v>
+      </c>
+      <c r="AC130">
+        <v>1.06</v>
+      </c>
+      <c r="AD130">
+        <v>9.5</v>
+      </c>
+      <c r="AE130">
+        <v>1.28</v>
+      </c>
+      <c r="AF130">
+        <v>3.1</v>
+      </c>
+      <c r="AG130">
+        <v>2</v>
+      </c>
+      <c r="AH130">
+        <v>1.75</v>
+      </c>
+      <c r="AI130">
+        <v>2.38</v>
+      </c>
+      <c r="AJ130">
+        <v>1.53</v>
+      </c>
+      <c r="AK130">
+        <v>1.22</v>
+      </c>
+      <c r="AL130">
+        <v>1.25</v>
+      </c>
+      <c r="AM130">
+        <v>2.8</v>
+      </c>
+      <c r="AN130">
+        <v>2.6</v>
+      </c>
+      <c r="AO130">
+        <v>0.43</v>
+      </c>
+      <c r="AP130">
+        <v>2.33</v>
+      </c>
+      <c r="AQ130">
+        <v>0.5</v>
+      </c>
+      <c r="AR130">
+        <v>1.98</v>
+      </c>
+      <c r="AS130">
+        <v>1.39</v>
+      </c>
+      <c r="AT130">
+        <v>3.37</v>
+      </c>
+      <c r="AU130">
+        <v>9</v>
+      </c>
+      <c r="AV130">
+        <v>2</v>
+      </c>
+      <c r="AW130">
+        <v>15</v>
+      </c>
+      <c r="AX130">
+        <v>9</v>
+      </c>
+      <c r="AY130">
+        <v>24</v>
+      </c>
+      <c r="AZ130">
+        <v>11</v>
+      </c>
+      <c r="BA130">
+        <v>6</v>
+      </c>
+      <c r="BB130">
+        <v>5</v>
+      </c>
+      <c r="BC130">
+        <v>11</v>
+      </c>
+      <c r="BD130">
+        <v>1.28</v>
+      </c>
+      <c r="BE130">
+        <v>10.25</v>
+      </c>
+      <c r="BF130">
+        <v>3</v>
+      </c>
+      <c r="BG130">
+        <v>1.32</v>
+      </c>
+      <c r="BH130">
+        <v>3.1</v>
+      </c>
+      <c r="BI130">
+        <v>1.57</v>
+      </c>
+      <c r="BJ130">
+        <v>2.25</v>
+      </c>
+      <c r="BK130">
+        <v>1.91</v>
+      </c>
+      <c r="BL130">
+        <v>1.8</v>
+      </c>
+      <c r="BM130">
+        <v>2.42</v>
+      </c>
+      <c r="BN130">
+        <v>1.5</v>
+      </c>
+      <c r="BO130">
+        <v>3.15</v>
+      </c>
+      <c r="BP130">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -26976,16 +26976,16 @@
         <v>2</v>
       </c>
       <c r="AW126">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AX126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY126">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ126">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA126">
         <v>7</v>
@@ -27182,13 +27182,13 @@
         <v>3</v>
       </c>
       <c r="AW127">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AX127">
         <v>3</v>
       </c>
       <c r="AY127">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ127">
         <v>6</v>
@@ -27388,16 +27388,16 @@
         <v>6</v>
       </c>
       <c r="AW128">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX128">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY128">
+        <v>7</v>
+      </c>
+      <c r="AZ128">
         <v>9</v>
-      </c>
-      <c r="AZ128">
-        <v>11</v>
       </c>
       <c r="BA128">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -717,6 +717,9 @@
   <si>
     <t>['9', '64']</t>
   </si>
+  <si>
+    <t>['30', '35']</t>
+  </si>
 </sst>
 </file>
 
@@ -1077,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP130"/>
+  <dimension ref="A1:BP131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4295,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ16">
         <v>2.17</v>
@@ -5122,7 +5125,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -6564,7 +6567,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ27">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR27">
         <v>1.57</v>
@@ -6973,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ29">
         <v>0.86</v>
@@ -11093,7 +11096,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ49">
         <v>0.5</v>
@@ -11302,7 +11305,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR50">
         <v>1.82</v>
@@ -13977,7 +13980,7 @@
         <v>0.33</v>
       </c>
       <c r="AP63">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ63">
         <v>0.14</v>
@@ -16864,7 +16867,7 @@
         <v>0.4</v>
       </c>
       <c r="AQ77">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR77">
         <v>1.89</v>
@@ -19951,7 +19954,7 @@
         <v>0</v>
       </c>
       <c r="AP92">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AQ92">
         <v>0.5</v>
@@ -21396,7 +21399,7 @@
         <v>1</v>
       </c>
       <c r="AQ99">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR99">
         <v>1.53</v>
@@ -24280,7 +24283,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ113">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -27594,16 +27597,16 @@
         <v>6</v>
       </c>
       <c r="AW129">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AX129">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY129">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ129">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA129">
         <v>6</v>
@@ -27800,16 +27803,16 @@
         <v>2</v>
       </c>
       <c r="AW130">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AX130">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AY130">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ130">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="BA130">
         <v>6</v>
@@ -27858,6 +27861,212 @@
       </c>
       <c r="BP130">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7834441</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45855.8125</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131" t="s">
+        <v>84</v>
+      </c>
+      <c r="H131" t="s">
+        <v>74</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>2</v>
+      </c>
+      <c r="K131">
+        <v>2</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>2</v>
+      </c>
+      <c r="N131">
+        <v>2</v>
+      </c>
+      <c r="O131" t="s">
+        <v>93</v>
+      </c>
+      <c r="P131" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q131">
+        <v>2.9</v>
+      </c>
+      <c r="R131">
+        <v>1.85</v>
+      </c>
+      <c r="S131">
+        <v>4.5</v>
+      </c>
+      <c r="T131">
+        <v>1.57</v>
+      </c>
+      <c r="U131">
+        <v>2.5</v>
+      </c>
+      <c r="V131">
+        <v>3.8</v>
+      </c>
+      <c r="W131">
+        <v>1.27</v>
+      </c>
+      <c r="X131">
+        <v>7.5</v>
+      </c>
+      <c r="Y131">
+        <v>1.03</v>
+      </c>
+      <c r="Z131">
+        <v>2.31</v>
+      </c>
+      <c r="AA131">
+        <v>3.1</v>
+      </c>
+      <c r="AB131">
+        <v>3.05</v>
+      </c>
+      <c r="AC131">
+        <v>1.12</v>
+      </c>
+      <c r="AD131">
+        <v>6.05</v>
+      </c>
+      <c r="AE131">
+        <v>1.57</v>
+      </c>
+      <c r="AF131">
+        <v>2.25</v>
+      </c>
+      <c r="AG131">
+        <v>2.89</v>
+      </c>
+      <c r="AH131">
+        <v>1.4</v>
+      </c>
+      <c r="AI131">
+        <v>2.1</v>
+      </c>
+      <c r="AJ131">
+        <v>1.7</v>
+      </c>
+      <c r="AK131">
+        <v>1.35</v>
+      </c>
+      <c r="AL131">
+        <v>1.33</v>
+      </c>
+      <c r="AM131">
+        <v>1.62</v>
+      </c>
+      <c r="AN131">
+        <v>2.6</v>
+      </c>
+      <c r="AO131">
+        <v>1.33</v>
+      </c>
+      <c r="AP131">
+        <v>2.17</v>
+      </c>
+      <c r="AQ131">
+        <v>1.57</v>
+      </c>
+      <c r="AR131">
+        <v>1.89</v>
+      </c>
+      <c r="AS131">
+        <v>1.57</v>
+      </c>
+      <c r="AT131">
+        <v>3.46</v>
+      </c>
+      <c r="AU131">
+        <v>7</v>
+      </c>
+      <c r="AV131">
+        <v>6</v>
+      </c>
+      <c r="AW131">
+        <v>15</v>
+      </c>
+      <c r="AX131">
+        <v>3</v>
+      </c>
+      <c r="AY131">
+        <v>22</v>
+      </c>
+      <c r="AZ131">
+        <v>9</v>
+      </c>
+      <c r="BA131">
+        <v>7</v>
+      </c>
+      <c r="BB131">
+        <v>2</v>
+      </c>
+      <c r="BC131">
+        <v>9</v>
+      </c>
+      <c r="BD131">
+        <v>1.68</v>
+      </c>
+      <c r="BE131">
+        <v>7</v>
+      </c>
+      <c r="BF131">
+        <v>2.75</v>
+      </c>
+      <c r="BG131">
+        <v>1.22</v>
+      </c>
+      <c r="BH131">
+        <v>4.1</v>
+      </c>
+      <c r="BI131">
+        <v>1.41</v>
+      </c>
+      <c r="BJ131">
+        <v>2.97</v>
+      </c>
+      <c r="BK131">
+        <v>1.65</v>
+      </c>
+      <c r="BL131">
+        <v>2.3</v>
+      </c>
+      <c r="BM131">
+        <v>1.98</v>
+      </c>
+      <c r="BN131">
+        <v>1.73</v>
+      </c>
+      <c r="BO131">
+        <v>2.5</v>
+      </c>
+      <c r="BP131">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -26979,16 +26979,16 @@
         <v>2</v>
       </c>
       <c r="AW126">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY126">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ126">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA126">
         <v>7</v>
@@ -27185,13 +27185,13 @@
         <v>3</v>
       </c>
       <c r="AW127">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AX127">
         <v>3</v>
       </c>
       <c r="AY127">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ127">
         <v>6</v>
@@ -27391,16 +27391,16 @@
         <v>6</v>
       </c>
       <c r="AW128">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX128">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY128">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ128">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA128">
         <v>3</v>
@@ -27597,16 +27597,16 @@
         <v>6</v>
       </c>
       <c r="AW129">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AX129">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY129">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ129">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA129">
         <v>6</v>
@@ -27803,16 +27803,16 @@
         <v>2</v>
       </c>
       <c r="AW130">
+        <v>15</v>
+      </c>
+      <c r="AX130">
+        <v>9</v>
+      </c>
+      <c r="AY130">
+        <v>24</v>
+      </c>
+      <c r="AZ130">
         <v>11</v>
-      </c>
-      <c r="AX130">
-        <v>4</v>
-      </c>
-      <c r="AY130">
-        <v>20</v>
-      </c>
-      <c r="AZ130">
-        <v>6</v>
       </c>
       <c r="BA130">
         <v>6</v>
@@ -28009,13 +28009,13 @@
         <v>6</v>
       </c>
       <c r="AW131">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AX131">
         <v>3</v>
       </c>
       <c r="AY131">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AZ131">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -28009,13 +28009,13 @@
         <v>6</v>
       </c>
       <c r="AW131">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AX131">
         <v>3</v>
       </c>
       <c r="AY131">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AZ131">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -28009,13 +28009,13 @@
         <v>6</v>
       </c>
       <c r="AW131">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AX131">
         <v>3</v>
       </c>
       <c r="AY131">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AZ131">
         <v>9</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="237">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -544,6 +544,9 @@
     <t>['43', '48']</t>
   </si>
   <si>
+    <t>['69', '73', '90+2']</t>
+  </si>
+  <si>
     <t>['75']</t>
   </si>
   <si>
@@ -719,6 +722,9 @@
   </si>
   <si>
     <t>['30', '35']</t>
+  </si>
+  <si>
+    <t>['80']</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1748,7 +1754,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2160,7 +2166,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2778,7 +2784,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2856,10 +2862,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ9">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -2984,7 +2990,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3190,7 +3196,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3683,7 +3689,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ13">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4220,7 +4226,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4426,7 +4432,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4632,7 +4638,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -4916,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ19">
         <v>0.5</v>
@@ -5250,7 +5256,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5331,7 +5337,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ21">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5662,7 +5668,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -6152,7 +6158,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25">
         <v>0.14</v>
@@ -6280,7 +6286,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6486,7 +6492,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6692,7 +6698,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -6979,7 +6985,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ29">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR29">
         <v>1.73</v>
@@ -7310,7 +7316,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7722,7 +7728,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7928,7 +7934,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8134,7 +8140,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8212,10 +8218,10 @@
         <v>0</v>
       </c>
       <c r="AP35">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ35">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR35">
         <v>2.31</v>
@@ -8340,7 +8346,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -9451,7 +9457,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ41">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR41">
         <v>0.97</v>
@@ -9576,7 +9582,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -9860,7 +9866,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43">
         <v>1.67</v>
@@ -10194,7 +10200,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10606,7 +10612,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10687,7 +10693,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ47">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR47">
         <v>1.4</v>
@@ -10812,7 +10818,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -11018,7 +11024,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11842,7 +11848,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12048,7 +12054,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -12126,7 +12132,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ54">
         <v>1.14</v>
@@ -12953,7 +12959,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ58">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR58">
         <v>1.54</v>
@@ -13284,7 +13290,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13365,7 +13371,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ60">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR60">
         <v>1.37</v>
@@ -13490,7 +13496,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -14108,7 +14114,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14726,7 +14732,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -14804,7 +14810,7 @@
         <v>3</v>
       </c>
       <c r="AP67">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ67">
         <v>2.5</v>
@@ -15013,7 +15019,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ68">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR68">
         <v>1.24</v>
@@ -15138,7 +15144,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15550,7 +15556,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15962,7 +15968,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16040,7 +16046,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ73">
         <v>0.86</v>
@@ -16168,7 +16174,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16374,7 +16380,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16661,7 +16667,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ76">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR76">
         <v>2.03</v>
@@ -16786,7 +16792,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17198,7 +17204,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -18100,7 +18106,7 @@
         <v>0.75</v>
       </c>
       <c r="AP83">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ83">
         <v>0.5</v>
@@ -18228,7 +18234,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18309,7 +18315,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ84">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR84">
         <v>1.35</v>
@@ -18434,7 +18440,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18721,7 +18727,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ86">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR86">
         <v>1.66</v>
@@ -19258,7 +19264,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19876,7 +19882,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20082,7 +20088,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20575,7 +20581,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ95">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR95">
         <v>1.25</v>
@@ -20906,7 +20912,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21112,7 +21118,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21193,7 +21199,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ98">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR98">
         <v>1.47</v>
@@ -21318,7 +21324,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21730,7 +21736,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21936,7 +21942,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22014,7 +22020,7 @@
         <v>1.75</v>
       </c>
       <c r="AP102">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ102">
         <v>2.17</v>
@@ -22220,7 +22226,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ103">
         <v>0.14</v>
@@ -22348,7 +22354,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22429,7 +22435,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ104">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR104">
         <v>1.59</v>
@@ -22554,7 +22560,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -23172,7 +23178,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23584,7 +23590,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23996,7 +24002,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24077,7 +24083,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ112">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR112">
         <v>1.69</v>
@@ -24408,7 +24414,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24489,7 +24495,7 @@
         <v>1</v>
       </c>
       <c r="AQ114">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR114">
         <v>1.47</v>
@@ -24614,7 +24620,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24820,7 +24826,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25644,7 +25650,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25722,7 +25728,7 @@
         <v>0.83</v>
       </c>
       <c r="AP120">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ120">
         <v>1.14</v>
@@ -25850,7 +25856,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q121">
         <v>2.8</v>
@@ -26056,7 +26062,7 @@
         <v>113</v>
       </c>
       <c r="P122" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26343,7 +26349,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ123">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AR123">
         <v>1.65</v>
@@ -26468,7 +26474,7 @@
         <v>93</v>
       </c>
       <c r="P124" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q124">
         <v>3.17</v>
@@ -26880,7 +26886,7 @@
         <v>95</v>
       </c>
       <c r="P126" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q126">
         <v>1.96</v>
@@ -27086,7 +27092,7 @@
         <v>93</v>
       </c>
       <c r="P127" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27498,7 +27504,7 @@
         <v>175</v>
       </c>
       <c r="P129" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q129">
         <v>2.84</v>
@@ -27910,7 +27916,7 @@
         <v>93</v>
       </c>
       <c r="P131" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q131">
         <v>2.9</v>
@@ -28067,6 +28073,624 @@
       </c>
       <c r="BP131">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7834459</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45857.66666666666</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132" t="s">
+        <v>70</v>
+      </c>
+      <c r="H132" t="s">
+        <v>78</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>2</v>
+      </c>
+      <c r="O132" t="s">
+        <v>168</v>
+      </c>
+      <c r="P132" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q132">
+        <v>3.3</v>
+      </c>
+      <c r="R132">
+        <v>2.05</v>
+      </c>
+      <c r="S132">
+        <v>3.4</v>
+      </c>
+      <c r="T132">
+        <v>1.43</v>
+      </c>
+      <c r="U132">
+        <v>2.54</v>
+      </c>
+      <c r="V132">
+        <v>2.98</v>
+      </c>
+      <c r="W132">
+        <v>1.3</v>
+      </c>
+      <c r="X132">
+        <v>9</v>
+      </c>
+      <c r="Y132">
+        <v>1.05</v>
+      </c>
+      <c r="Z132">
+        <v>2.65</v>
+      </c>
+      <c r="AA132">
+        <v>3</v>
+      </c>
+      <c r="AB132">
+        <v>2.8</v>
+      </c>
+      <c r="AC132">
+        <v>1.1</v>
+      </c>
+      <c r="AD132">
+        <v>8.5</v>
+      </c>
+      <c r="AE132">
+        <v>1.37</v>
+      </c>
+      <c r="AF132">
+        <v>3.23</v>
+      </c>
+      <c r="AG132">
+        <v>2.05</v>
+      </c>
+      <c r="AH132">
+        <v>1.61</v>
+      </c>
+      <c r="AI132">
+        <v>1.85</v>
+      </c>
+      <c r="AJ132">
+        <v>1.91</v>
+      </c>
+      <c r="AK132">
+        <v>1.36</v>
+      </c>
+      <c r="AL132">
+        <v>1.34</v>
+      </c>
+      <c r="AM132">
+        <v>1.44</v>
+      </c>
+      <c r="AN132">
+        <v>1</v>
+      </c>
+      <c r="AO132">
+        <v>1.17</v>
+      </c>
+      <c r="AP132">
+        <v>1</v>
+      </c>
+      <c r="AQ132">
+        <v>1.14</v>
+      </c>
+      <c r="AR132">
+        <v>1.65</v>
+      </c>
+      <c r="AS132">
+        <v>1.38</v>
+      </c>
+      <c r="AT132">
+        <v>3.03</v>
+      </c>
+      <c r="AU132">
+        <v>3</v>
+      </c>
+      <c r="AV132">
+        <v>5</v>
+      </c>
+      <c r="AW132">
+        <v>8</v>
+      </c>
+      <c r="AX132">
+        <v>9</v>
+      </c>
+      <c r="AY132">
+        <v>11</v>
+      </c>
+      <c r="AZ132">
+        <v>14</v>
+      </c>
+      <c r="BA132">
+        <v>9</v>
+      </c>
+      <c r="BB132">
+        <v>3</v>
+      </c>
+      <c r="BC132">
+        <v>12</v>
+      </c>
+      <c r="BD132">
+        <v>1.73</v>
+      </c>
+      <c r="BE132">
+        <v>8</v>
+      </c>
+      <c r="BF132">
+        <v>2.38</v>
+      </c>
+      <c r="BG132">
+        <v>1.2</v>
+      </c>
+      <c r="BH132">
+        <v>3.9</v>
+      </c>
+      <c r="BI132">
+        <v>1.36</v>
+      </c>
+      <c r="BJ132">
+        <v>2.75</v>
+      </c>
+      <c r="BK132">
+        <v>1.68</v>
+      </c>
+      <c r="BL132">
+        <v>2.14</v>
+      </c>
+      <c r="BM132">
+        <v>1.97</v>
+      </c>
+      <c r="BN132">
+        <v>1.72</v>
+      </c>
+      <c r="BO132">
+        <v>2.48</v>
+      </c>
+      <c r="BP132">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7834452</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45857.72916666666</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133" t="s">
+        <v>77</v>
+      </c>
+      <c r="H133" t="s">
+        <v>72</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>136</v>
+      </c>
+      <c r="P133" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q133">
+        <v>2.82</v>
+      </c>
+      <c r="R133">
+        <v>2.09</v>
+      </c>
+      <c r="S133">
+        <v>4.89</v>
+      </c>
+      <c r="T133">
+        <v>1.44</v>
+      </c>
+      <c r="U133">
+        <v>2.4</v>
+      </c>
+      <c r="V133">
+        <v>3.3</v>
+      </c>
+      <c r="W133">
+        <v>1.32</v>
+      </c>
+      <c r="X133">
+        <v>9.4</v>
+      </c>
+      <c r="Y133">
+        <v>1.05</v>
+      </c>
+      <c r="Z133">
+        <v>2.1</v>
+      </c>
+      <c r="AA133">
+        <v>3.15</v>
+      </c>
+      <c r="AB133">
+        <v>3.8</v>
+      </c>
+      <c r="AC133">
+        <v>1.03</v>
+      </c>
+      <c r="AD133">
+        <v>7.66</v>
+      </c>
+      <c r="AE133">
+        <v>1.42</v>
+      </c>
+      <c r="AF133">
+        <v>2.6</v>
+      </c>
+      <c r="AG133">
+        <v>2.35</v>
+      </c>
+      <c r="AH133">
+        <v>1.57</v>
+      </c>
+      <c r="AI133">
+        <v>2.18</v>
+      </c>
+      <c r="AJ133">
+        <v>1.75</v>
+      </c>
+      <c r="AK133">
+        <v>1.35</v>
+      </c>
+      <c r="AL133">
+        <v>1.33</v>
+      </c>
+      <c r="AM133">
+        <v>1.75</v>
+      </c>
+      <c r="AN133">
+        <v>1.43</v>
+      </c>
+      <c r="AO133">
+        <v>0.67</v>
+      </c>
+      <c r="AP133">
+        <v>1.38</v>
+      </c>
+      <c r="AQ133">
+        <v>0.71</v>
+      </c>
+      <c r="AR133">
+        <v>1.54</v>
+      </c>
+      <c r="AS133">
+        <v>1.54</v>
+      </c>
+      <c r="AT133">
+        <v>3.08</v>
+      </c>
+      <c r="AU133">
+        <v>8</v>
+      </c>
+      <c r="AV133">
+        <v>5</v>
+      </c>
+      <c r="AW133">
+        <v>12</v>
+      </c>
+      <c r="AX133">
+        <v>4</v>
+      </c>
+      <c r="AY133">
+        <v>20</v>
+      </c>
+      <c r="AZ133">
+        <v>9</v>
+      </c>
+      <c r="BA133">
+        <v>12</v>
+      </c>
+      <c r="BB133">
+        <v>2</v>
+      </c>
+      <c r="BC133">
+        <v>14</v>
+      </c>
+      <c r="BD133">
+        <v>1.6</v>
+      </c>
+      <c r="BE133">
+        <v>9.5</v>
+      </c>
+      <c r="BF133">
+        <v>2.45</v>
+      </c>
+      <c r="BG133">
+        <v>1.24</v>
+      </c>
+      <c r="BH133">
+        <v>3.52</v>
+      </c>
+      <c r="BI133">
+        <v>1.45</v>
+      </c>
+      <c r="BJ133">
+        <v>2.55</v>
+      </c>
+      <c r="BK133">
+        <v>1.88</v>
+      </c>
+      <c r="BL133">
+        <v>1.81</v>
+      </c>
+      <c r="BM133">
+        <v>2.18</v>
+      </c>
+      <c r="BN133">
+        <v>1.64</v>
+      </c>
+      <c r="BO133">
+        <v>2.75</v>
+      </c>
+      <c r="BP133">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7834455</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45857.77083333334</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134" t="s">
+        <v>87</v>
+      </c>
+      <c r="H134" t="s">
+        <v>89</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>3</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>3</v>
+      </c>
+      <c r="O134" t="s">
+        <v>176</v>
+      </c>
+      <c r="P134" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q134">
+        <v>3.25</v>
+      </c>
+      <c r="R134">
+        <v>1.92</v>
+      </c>
+      <c r="S134">
+        <v>3.5</v>
+      </c>
+      <c r="T134">
+        <v>1.51</v>
+      </c>
+      <c r="U134">
+        <v>2.5</v>
+      </c>
+      <c r="V134">
+        <v>3.28</v>
+      </c>
+      <c r="W134">
+        <v>1.28</v>
+      </c>
+      <c r="X134">
+        <v>9</v>
+      </c>
+      <c r="Y134">
+        <v>1.03</v>
+      </c>
+      <c r="Z134">
+        <v>2.74</v>
+      </c>
+      <c r="AA134">
+        <v>3.13</v>
+      </c>
+      <c r="AB134">
+        <v>2.6</v>
+      </c>
+      <c r="AC134">
+        <v>1.06</v>
+      </c>
+      <c r="AD134">
+        <v>6.75</v>
+      </c>
+      <c r="AE134">
+        <v>1.43</v>
+      </c>
+      <c r="AF134">
+        <v>2.53</v>
+      </c>
+      <c r="AG134">
+        <v>2.51</v>
+      </c>
+      <c r="AH134">
+        <v>1.55</v>
+      </c>
+      <c r="AI134">
+        <v>1.99</v>
+      </c>
+      <c r="AJ134">
+        <v>1.78</v>
+      </c>
+      <c r="AK134">
+        <v>1.4</v>
+      </c>
+      <c r="AL134">
+        <v>1.35</v>
+      </c>
+      <c r="AM134">
+        <v>1.49</v>
+      </c>
+      <c r="AN134">
+        <v>2.2</v>
+      </c>
+      <c r="AO134">
+        <v>0.86</v>
+      </c>
+      <c r="AP134">
+        <v>2.33</v>
+      </c>
+      <c r="AQ134">
+        <v>0.75</v>
+      </c>
+      <c r="AR134">
+        <v>1.75</v>
+      </c>
+      <c r="AS134">
+        <v>1.13</v>
+      </c>
+      <c r="AT134">
+        <v>2.88</v>
+      </c>
+      <c r="AU134">
+        <v>11</v>
+      </c>
+      <c r="AV134">
+        <v>0</v>
+      </c>
+      <c r="AW134">
+        <v>3</v>
+      </c>
+      <c r="AX134">
+        <v>7</v>
+      </c>
+      <c r="AY134">
+        <v>14</v>
+      </c>
+      <c r="AZ134">
+        <v>7</v>
+      </c>
+      <c r="BA134">
+        <v>9</v>
+      </c>
+      <c r="BB134">
+        <v>2</v>
+      </c>
+      <c r="BC134">
+        <v>11</v>
+      </c>
+      <c r="BD134">
+        <v>1.98</v>
+      </c>
+      <c r="BE134">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF134">
+        <v>2.22</v>
+      </c>
+      <c r="BG134">
+        <v>1.25</v>
+      </c>
+      <c r="BH134">
+        <v>3.6</v>
+      </c>
+      <c r="BI134">
+        <v>1.39</v>
+      </c>
+      <c r="BJ134">
+        <v>2.7</v>
+      </c>
+      <c r="BK134">
+        <v>1.67</v>
+      </c>
+      <c r="BL134">
+        <v>2.05</v>
+      </c>
+      <c r="BM134">
+        <v>2.05</v>
+      </c>
+      <c r="BN134">
+        <v>1.78</v>
+      </c>
+      <c r="BO134">
+        <v>2.6</v>
+      </c>
+      <c r="BP134">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="238">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -545,6 +545,9 @@
   </si>
   <si>
     <t>['69', '73', '90+2']</t>
+  </si>
+  <si>
+    <t>['32', '35']</t>
   </si>
   <si>
     <t>['75']</t>
@@ -1086,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP134"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1754,7 +1757,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2038,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5">
         <v>0.14</v>
@@ -2166,7 +2169,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2784,7 +2787,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2990,7 +2993,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3071,7 +3074,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ10">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3196,7 +3199,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4226,7 +4229,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4432,7 +4435,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4638,7 +4641,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -5256,7 +5259,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5668,7 +5671,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5955,7 +5958,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR24">
         <v>1.52</v>
@@ -6286,7 +6289,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6492,7 +6495,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6570,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27">
         <v>1.57</v>
@@ -6698,7 +6701,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -7316,7 +7319,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7728,7 +7731,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7934,7 +7937,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8140,7 +8143,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8346,7 +8349,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -9582,7 +9585,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10200,7 +10203,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10612,7 +10615,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10690,7 +10693,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ47">
         <v>0.75</v>
@@ -10818,7 +10821,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -11024,7 +11027,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11848,7 +11851,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12054,7 +12057,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -12753,7 +12756,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ57">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR57">
         <v>2.08</v>
@@ -13290,7 +13293,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13496,7 +13499,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -13780,7 +13783,7 @@
         <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62">
         <v>0.5</v>
@@ -14114,7 +14117,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14732,7 +14735,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -15144,7 +15147,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15556,7 +15559,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15968,7 +15971,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16049,7 +16052,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ73">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR73">
         <v>1.93</v>
@@ -16174,7 +16177,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16380,7 +16383,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16792,7 +16795,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17204,7 +17207,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -18234,7 +18237,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18312,7 +18315,7 @@
         <v>0.33</v>
       </c>
       <c r="AP84">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
         <v>0.71</v>
@@ -18440,7 +18443,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -19264,7 +19267,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19882,7 +19885,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20088,7 +20091,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20166,7 +20169,7 @@
         <v>0.6</v>
       </c>
       <c r="AP93">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ93">
         <v>1</v>
@@ -20375,7 +20378,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR94">
         <v>2.33</v>
@@ -20912,7 +20915,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21118,7 +21121,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21324,7 +21327,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21736,7 +21739,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21942,7 +21945,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22354,7 +22357,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22560,7 +22563,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -23178,7 +23181,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23590,7 +23593,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -24002,7 +24005,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24414,7 +24417,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24620,7 +24623,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24701,7 +24704,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ115">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
         <v>1.22</v>
@@ -24826,7 +24829,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -24904,7 +24907,7 @@
         <v>0</v>
       </c>
       <c r="AP116">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ116">
         <v>0.5</v>
@@ -25650,7 +25653,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25856,7 +25859,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q121">
         <v>2.8</v>
@@ -26062,7 +26065,7 @@
         <v>113</v>
       </c>
       <c r="P122" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26474,7 +26477,7 @@
         <v>93</v>
       </c>
       <c r="P124" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q124">
         <v>3.17</v>
@@ -26886,7 +26889,7 @@
         <v>95</v>
       </c>
       <c r="P126" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q126">
         <v>1.96</v>
@@ -27092,7 +27095,7 @@
         <v>93</v>
       </c>
       <c r="P127" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27173,7 +27176,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ127">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR127">
         <v>1.38</v>
@@ -27504,7 +27507,7 @@
         <v>175</v>
       </c>
       <c r="P129" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q129">
         <v>2.84</v>
@@ -27916,7 +27919,7 @@
         <v>93</v>
       </c>
       <c r="P131" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q131">
         <v>2.9</v>
@@ -28122,7 +28125,7 @@
         <v>168</v>
       </c>
       <c r="P132" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q132">
         <v>3.3</v>
@@ -28221,16 +28224,16 @@
         <v>5</v>
       </c>
       <c r="AW132">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX132">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY132">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ132">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BA132">
         <v>9</v>
@@ -28328,7 +28331,7 @@
         <v>136</v>
       </c>
       <c r="P133" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q133">
         <v>2.82</v>
@@ -28427,16 +28430,16 @@
         <v>5</v>
       </c>
       <c r="AW133">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AX133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY133">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AZ133">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA133">
         <v>12</v>
@@ -28633,16 +28636,16 @@
         <v>0</v>
       </c>
       <c r="AW134">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX134">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY134">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AZ134">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA134">
         <v>9</v>
@@ -28691,6 +28694,212 @@
       </c>
       <c r="BP134">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7834454</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45857.875</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135" t="s">
+        <v>73</v>
+      </c>
+      <c r="H135" t="s">
+        <v>80</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>2</v>
+      </c>
+      <c r="L135">
+        <v>2</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>2</v>
+      </c>
+      <c r="O135" t="s">
+        <v>177</v>
+      </c>
+      <c r="P135" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q135">
+        <v>3.14</v>
+      </c>
+      <c r="R135">
+        <v>1.84</v>
+      </c>
+      <c r="S135">
+        <v>4</v>
+      </c>
+      <c r="T135">
+        <v>1.57</v>
+      </c>
+      <c r="U135">
+        <v>2.25</v>
+      </c>
+      <c r="V135">
+        <v>3.8</v>
+      </c>
+      <c r="W135">
+        <v>1.22</v>
+      </c>
+      <c r="X135">
+        <v>13</v>
+      </c>
+      <c r="Y135">
+        <v>1.05</v>
+      </c>
+      <c r="Z135">
+        <v>2.31</v>
+      </c>
+      <c r="AA135">
+        <v>2.96</v>
+      </c>
+      <c r="AB135">
+        <v>2.87</v>
+      </c>
+      <c r="AC135">
+        <v>1.1</v>
+      </c>
+      <c r="AD135">
+        <v>5.25</v>
+      </c>
+      <c r="AE135">
+        <v>1.57</v>
+      </c>
+      <c r="AF135">
+        <v>2.25</v>
+      </c>
+      <c r="AG135">
+        <v>2.55</v>
+      </c>
+      <c r="AH135">
+        <v>1.45</v>
+      </c>
+      <c r="AI135">
+        <v>2.25</v>
+      </c>
+      <c r="AJ135">
+        <v>1.56</v>
+      </c>
+      <c r="AK135">
+        <v>1.44</v>
+      </c>
+      <c r="AL135">
+        <v>1.35</v>
+      </c>
+      <c r="AM135">
+        <v>1.64</v>
+      </c>
+      <c r="AN135">
+        <v>1.29</v>
+      </c>
+      <c r="AO135">
+        <v>0.86</v>
+      </c>
+      <c r="AP135">
+        <v>1.5</v>
+      </c>
+      <c r="AQ135">
+        <v>0.75</v>
+      </c>
+      <c r="AR135">
+        <v>1.45</v>
+      </c>
+      <c r="AS135">
+        <v>1.06</v>
+      </c>
+      <c r="AT135">
+        <v>2.51</v>
+      </c>
+      <c r="AU135">
+        <v>4</v>
+      </c>
+      <c r="AV135">
+        <v>4</v>
+      </c>
+      <c r="AW135">
+        <v>13</v>
+      </c>
+      <c r="AX135">
+        <v>6</v>
+      </c>
+      <c r="AY135">
+        <v>17</v>
+      </c>
+      <c r="AZ135">
+        <v>10</v>
+      </c>
+      <c r="BA135">
+        <v>6</v>
+      </c>
+      <c r="BB135">
+        <v>5</v>
+      </c>
+      <c r="BC135">
+        <v>11</v>
+      </c>
+      <c r="BD135">
+        <v>1.65</v>
+      </c>
+      <c r="BE135">
+        <v>6.5</v>
+      </c>
+      <c r="BF135">
+        <v>2.34</v>
+      </c>
+      <c r="BG135">
+        <v>1.25</v>
+      </c>
+      <c r="BH135">
+        <v>3.2</v>
+      </c>
+      <c r="BI135">
+        <v>1.38</v>
+      </c>
+      <c r="BJ135">
+        <v>2.38</v>
+      </c>
+      <c r="BK135">
+        <v>1.68</v>
+      </c>
+      <c r="BL135">
+        <v>1.83</v>
+      </c>
+      <c r="BM135">
+        <v>2.4</v>
+      </c>
+      <c r="BN135">
+        <v>1.48</v>
+      </c>
+      <c r="BO135">
+        <v>3</v>
+      </c>
+      <c r="BP135">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="239">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -548,6 +548,9 @@
   </si>
   <si>
     <t>['32', '35']</t>
+  </si>
+  <si>
+    <t>['23']</t>
   </si>
   <si>
     <t>['75']</t>
@@ -1089,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP135"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1757,7 +1760,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -2169,7 +2172,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2787,7 +2790,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2993,7 +2996,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3199,7 +3202,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -3280,7 +3283,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ11">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4229,7 +4232,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4435,7 +4438,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4641,7 +4644,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -5131,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ20">
         <v>1.57</v>
@@ -5259,7 +5262,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5671,7 +5674,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5752,7 +5755,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ23">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR23">
         <v>1.18</v>
@@ -6289,7 +6292,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6495,7 +6498,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6701,7 +6704,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -7319,7 +7322,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7731,7 +7734,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7937,7 +7940,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8143,7 +8146,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8349,7 +8352,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -8633,7 +8636,7 @@
         <v>3</v>
       </c>
       <c r="AP37">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ37">
         <v>2.5</v>
@@ -9585,7 +9588,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10203,7 +10206,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10615,7 +10618,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10821,7 +10824,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -11027,7 +11030,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11520,7 +11523,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ51">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR51">
         <v>1.54</v>
@@ -11723,7 +11726,7 @@
         <v>0</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ52">
         <v>0</v>
@@ -11851,7 +11854,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12057,7 +12060,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -13293,7 +13296,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13499,7 +13502,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -14117,7 +14120,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14735,7 +14738,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -15147,7 +15150,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15559,7 +15562,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15971,7 +15974,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16177,7 +16180,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16383,7 +16386,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16795,7 +16798,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -17207,7 +17210,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -17700,7 +17703,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ81">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR81">
         <v>1.87</v>
@@ -18237,7 +18240,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18443,7 +18446,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -19267,7 +19270,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19757,7 +19760,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -19885,7 +19888,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20091,7 +20094,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20915,7 +20918,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -21121,7 +21124,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21327,7 +21330,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21739,7 +21742,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21945,7 +21948,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22357,7 +22360,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22563,7 +22566,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -23181,7 +23184,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23593,7 +23596,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23671,7 +23674,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ110">
         <v>1.17</v>
@@ -23880,7 +23883,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ111">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR111">
         <v>1.95</v>
@@ -24005,7 +24008,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24417,7 +24420,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24623,7 +24626,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24829,7 +24832,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25319,7 +25322,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ118">
         <v>0.5</v>
@@ -25653,7 +25656,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25859,7 +25862,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q121">
         <v>2.8</v>
@@ -26065,7 +26068,7 @@
         <v>113</v>
       </c>
       <c r="P122" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26477,7 +26480,7 @@
         <v>93</v>
       </c>
       <c r="P124" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q124">
         <v>3.17</v>
@@ -26558,7 +26561,7 @@
         <v>1</v>
       </c>
       <c r="AQ124">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR124">
         <v>1.81</v>
@@ -26889,7 +26892,7 @@
         <v>95</v>
       </c>
       <c r="P126" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q126">
         <v>1.96</v>
@@ -27095,7 +27098,7 @@
         <v>93</v>
       </c>
       <c r="P127" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27507,7 +27510,7 @@
         <v>175</v>
       </c>
       <c r="P129" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q129">
         <v>2.84</v>
@@ -27919,7 +27922,7 @@
         <v>93</v>
       </c>
       <c r="P131" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q131">
         <v>2.9</v>
@@ -28125,7 +28128,7 @@
         <v>168</v>
       </c>
       <c r="P132" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q132">
         <v>3.3</v>
@@ -28224,16 +28227,16 @@
         <v>5</v>
       </c>
       <c r="AW132">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AX132">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AY132">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ132">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA132">
         <v>9</v>
@@ -28331,7 +28334,7 @@
         <v>136</v>
       </c>
       <c r="P133" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q133">
         <v>2.82</v>
@@ -28430,16 +28433,16 @@
         <v>5</v>
       </c>
       <c r="AW133">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AX133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY133">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AZ133">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA133">
         <v>12</v>
@@ -28900,6 +28903,212 @@
       </c>
       <c r="BP135">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7834457</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45858.45833333334</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136" t="s">
+        <v>88</v>
+      </c>
+      <c r="H136" t="s">
+        <v>81</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>1</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>178</v>
+      </c>
+      <c r="P136" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q136">
+        <v>2.2</v>
+      </c>
+      <c r="R136">
+        <v>2.15</v>
+      </c>
+      <c r="S136">
+        <v>5.5</v>
+      </c>
+      <c r="T136">
+        <v>1.44</v>
+      </c>
+      <c r="U136">
+        <v>2.6</v>
+      </c>
+      <c r="V136">
+        <v>3.38</v>
+      </c>
+      <c r="W136">
+        <v>1.33</v>
+      </c>
+      <c r="X136">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y136">
+        <v>1.05</v>
+      </c>
+      <c r="Z136">
+        <v>1.55</v>
+      </c>
+      <c r="AA136">
+        <v>3.47</v>
+      </c>
+      <c r="AB136">
+        <v>5.3</v>
+      </c>
+      <c r="AC136">
+        <v>1.08</v>
+      </c>
+      <c r="AD136">
+        <v>7.5</v>
+      </c>
+      <c r="AE136">
+        <v>1.36</v>
+      </c>
+      <c r="AF136">
+        <v>2.9</v>
+      </c>
+      <c r="AG136">
+        <v>2.2</v>
+      </c>
+      <c r="AH136">
+        <v>1.59</v>
+      </c>
+      <c r="AI136">
+        <v>2.1</v>
+      </c>
+      <c r="AJ136">
+        <v>1.65</v>
+      </c>
+      <c r="AK136">
+        <v>1.3</v>
+      </c>
+      <c r="AL136">
+        <v>1.26</v>
+      </c>
+      <c r="AM136">
+        <v>2.15</v>
+      </c>
+      <c r="AN136">
+        <v>1.67</v>
+      </c>
+      <c r="AO136">
+        <v>0.83</v>
+      </c>
+      <c r="AP136">
+        <v>1.86</v>
+      </c>
+      <c r="AQ136">
+        <v>0.71</v>
+      </c>
+      <c r="AR136">
+        <v>2.18</v>
+      </c>
+      <c r="AS136">
+        <v>1.25</v>
+      </c>
+      <c r="AT136">
+        <v>3.43</v>
+      </c>
+      <c r="AU136">
+        <v>5</v>
+      </c>
+      <c r="AV136">
+        <v>4</v>
+      </c>
+      <c r="AW136">
+        <v>6</v>
+      </c>
+      <c r="AX136">
+        <v>7</v>
+      </c>
+      <c r="AY136">
+        <v>11</v>
+      </c>
+      <c r="AZ136">
+        <v>11</v>
+      </c>
+      <c r="BA136">
+        <v>7</v>
+      </c>
+      <c r="BB136">
+        <v>5</v>
+      </c>
+      <c r="BC136">
+        <v>12</v>
+      </c>
+      <c r="BD136">
+        <v>1.4</v>
+      </c>
+      <c r="BE136">
+        <v>7.5</v>
+      </c>
+      <c r="BF136">
+        <v>4.3</v>
+      </c>
+      <c r="BG136">
+        <v>1.23</v>
+      </c>
+      <c r="BH136">
+        <v>3.6</v>
+      </c>
+      <c r="BI136">
+        <v>1.42</v>
+      </c>
+      <c r="BJ136">
+        <v>2.62</v>
+      </c>
+      <c r="BK136">
+        <v>1.67</v>
+      </c>
+      <c r="BL136">
+        <v>2.1</v>
+      </c>
+      <c r="BM136">
+        <v>2.1</v>
+      </c>
+      <c r="BN136">
+        <v>1.6</v>
+      </c>
+      <c r="BO136">
+        <v>2.78</v>
+      </c>
+      <c r="BP136">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="243">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -553,6 +553,18 @@
     <t>['23']</t>
   </si>
   <si>
+    <t>['39', '51', '63', '90+2']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['33', '51', '77']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
     <t>['75']</t>
   </si>
   <si>
@@ -676,9 +688,6 @@
     <t>['34', '41']</t>
   </si>
   <si>
-    <t>['85']</t>
-  </si>
-  <si>
     <t>['2', '34']</t>
   </si>
   <si>
@@ -731,6 +740,9 @@
   </si>
   <si>
     <t>['80']</t>
+  </si>
+  <si>
+    <t>['42', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1429,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1760,7 +1772,7 @@
         <v>92</v>
       </c>
       <c r="P4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1841,7 +1853,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ4">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2172,7 +2184,7 @@
         <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q6">
         <v>2.1</v>
@@ -2250,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2456,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7">
         <v>0.57</v>
@@ -2662,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2790,7 +2802,7 @@
         <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q9">
         <v>3</v>
@@ -2996,7 +3008,7 @@
         <v>97</v>
       </c>
       <c r="P10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3202,7 +3214,7 @@
         <v>98</v>
       </c>
       <c r="P11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q11">
         <v>2.88</v>
@@ -4232,7 +4244,7 @@
         <v>102</v>
       </c>
       <c r="P16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q16">
         <v>2.6</v>
@@ -4313,7 +4325,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ16">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4438,7 +4450,7 @@
         <v>103</v>
       </c>
       <c r="P17" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -4516,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ17">
         <v>2.5</v>
@@ -4644,7 +4656,7 @@
         <v>104</v>
       </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -4722,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ18">
         <v>1.67</v>
@@ -5262,7 +5274,7 @@
         <v>107</v>
       </c>
       <c r="P21" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5549,7 +5561,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ22">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR22">
         <v>2.29</v>
@@ -5674,7 +5686,7 @@
         <v>109</v>
       </c>
       <c r="P23" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q23">
         <v>3</v>
@@ -5958,7 +5970,7 @@
         <v>1</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ24">
         <v>0.75</v>
@@ -6292,7 +6304,7 @@
         <v>112</v>
       </c>
       <c r="P26" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q26">
         <v>2.19</v>
@@ -6498,7 +6510,7 @@
         <v>113</v>
       </c>
       <c r="P27" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q27">
         <v>2.69</v>
@@ -6704,7 +6716,7 @@
         <v>93</v>
       </c>
       <c r="P28" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q28">
         <v>4.1</v>
@@ -7322,7 +7334,7 @@
         <v>115</v>
       </c>
       <c r="P31" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q31">
         <v>2.28</v>
@@ -7734,7 +7746,7 @@
         <v>117</v>
       </c>
       <c r="P33" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q33">
         <v>2.4</v>
@@ -7940,7 +7952,7 @@
         <v>93</v>
       </c>
       <c r="P34" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q34">
         <v>2.7</v>
@@ -8018,10 +8030,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ34">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR34">
         <v>1.15</v>
@@ -8146,7 +8158,7 @@
         <v>118</v>
       </c>
       <c r="P35" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q35">
         <v>3.2</v>
@@ -8352,7 +8364,7 @@
         <v>93</v>
       </c>
       <c r="P36" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q36">
         <v>2.82</v>
@@ -8433,7 +8445,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ36">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR36">
         <v>0.99</v>
@@ -8842,7 +8854,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ38">
         <v>0.5</v>
@@ -9048,7 +9060,7 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ39">
         <v>0</v>
@@ -9257,7 +9269,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ40">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>2.4</v>
@@ -9460,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="AP41">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ41">
         <v>1.14</v>
@@ -9588,7 +9600,7 @@
         <v>123</v>
       </c>
       <c r="P42" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q42">
         <v>2.25</v>
@@ -10206,7 +10218,7 @@
         <v>124</v>
       </c>
       <c r="P45" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10493,7 +10505,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR46">
         <v>2.97</v>
@@ -10618,7 +10630,7 @@
         <v>126</v>
       </c>
       <c r="P47" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q47">
         <v>2.81</v>
@@ -10824,7 +10836,7 @@
         <v>127</v>
       </c>
       <c r="P48" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q48">
         <v>4.9</v>
@@ -11030,7 +11042,7 @@
         <v>128</v>
       </c>
       <c r="P49" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q49">
         <v>2.37</v>
@@ -11854,7 +11866,7 @@
         <v>132</v>
       </c>
       <c r="P53" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q53">
         <v>3.1</v>
@@ -12060,7 +12072,7 @@
         <v>133</v>
       </c>
       <c r="P54" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q54">
         <v>3.8</v>
@@ -12141,7 +12153,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ54">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR54">
         <v>1.85</v>
@@ -12344,7 +12356,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ55">
         <v>0.5</v>
@@ -12553,7 +12565,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ56">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR56">
         <v>2.27</v>
@@ -12756,7 +12768,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ57">
         <v>0.75</v>
@@ -12962,7 +12974,7 @@
         <v>0.5</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ58">
         <v>1.14</v>
@@ -13168,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="AP59">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ59">
         <v>0.5</v>
@@ -13296,7 +13308,7 @@
         <v>137</v>
       </c>
       <c r="P60" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q60">
         <v>3.1</v>
@@ -13374,7 +13386,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ60">
         <v>0.71</v>
@@ -13502,7 +13514,7 @@
         <v>138</v>
       </c>
       <c r="P61" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q61">
         <v>2.6</v>
@@ -13583,7 +13595,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ61">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14120,7 +14132,7 @@
         <v>140</v>
       </c>
       <c r="P64" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q64">
         <v>2.95</v>
@@ -14613,7 +14625,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ66">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR66">
         <v>1.57</v>
@@ -14738,7 +14750,7 @@
         <v>93</v>
       </c>
       <c r="P67" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q67">
         <v>5.7</v>
@@ -15150,7 +15162,7 @@
         <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q69">
         <v>4.4</v>
@@ -15228,7 +15240,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ69">
         <v>1.67</v>
@@ -15562,7 +15574,7 @@
         <v>93</v>
       </c>
       <c r="P71" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q71">
         <v>3.8</v>
@@ -15643,7 +15655,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ71">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR71">
         <v>1.79</v>
@@ -15974,7 +15986,7 @@
         <v>145</v>
       </c>
       <c r="P73" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q73">
         <v>3.68</v>
@@ -16180,7 +16192,7 @@
         <v>146</v>
       </c>
       <c r="P74" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q74">
         <v>3.37</v>
@@ -16261,7 +16273,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ74">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR74">
         <v>1.19</v>
@@ -16386,7 +16398,7 @@
         <v>147</v>
       </c>
       <c r="P75" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q75">
         <v>2.75</v>
@@ -16464,7 +16476,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ75">
         <v>0.5</v>
@@ -16670,7 +16682,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ76">
         <v>1.14</v>
@@ -16798,7 +16810,7 @@
         <v>93</v>
       </c>
       <c r="P77" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q77">
         <v>3</v>
@@ -16876,7 +16888,7 @@
         <v>0.33</v>
       </c>
       <c r="AP77">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ77">
         <v>1.57</v>
@@ -17082,7 +17094,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ78">
         <v>0.57</v>
@@ -17210,7 +17222,7 @@
         <v>150</v>
       </c>
       <c r="P79" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q79">
         <v>2.59</v>
@@ -17291,7 +17303,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR79">
         <v>2.54</v>
@@ -18240,7 +18252,7 @@
         <v>154</v>
       </c>
       <c r="P84" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q84">
         <v>2.3</v>
@@ -18446,7 +18458,7 @@
         <v>155</v>
       </c>
       <c r="P85" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q85">
         <v>4.56</v>
@@ -18527,7 +18539,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ85">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR85">
         <v>1.75</v>
@@ -19142,10 +19154,10 @@
         <v>0.25</v>
       </c>
       <c r="AP88">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ88">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR88">
         <v>1.9</v>
@@ -19270,7 +19282,7 @@
         <v>157</v>
       </c>
       <c r="P89" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q89">
         <v>4.39</v>
@@ -19554,10 +19566,10 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ90">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR90">
         <v>1.65</v>
@@ -19888,7 +19900,7 @@
         <v>158</v>
       </c>
       <c r="P92" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20094,7 +20106,7 @@
         <v>93</v>
       </c>
       <c r="P93" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q93">
         <v>2.38</v>
@@ -20790,7 +20802,7 @@
         <v>0.6</v>
       </c>
       <c r="AP96">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AQ96">
         <v>0.57</v>
@@ -20918,7 +20930,7 @@
         <v>93</v>
       </c>
       <c r="P97" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q97">
         <v>2.95</v>
@@ -20996,7 +21008,7 @@
         <v>1.75</v>
       </c>
       <c r="AP97">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ97">
         <v>1.67</v>
@@ -21124,7 +21136,7 @@
         <v>93</v>
       </c>
       <c r="P98" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q98">
         <v>2.85</v>
@@ -21202,7 +21214,7 @@
         <v>0</v>
       </c>
       <c r="AP98">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ98">
         <v>0.75</v>
@@ -21330,7 +21342,7 @@
         <v>93</v>
       </c>
       <c r="P99" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q99">
         <v>3.22</v>
@@ -21742,7 +21754,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="Q101">
         <v>2.56</v>
@@ -21948,7 +21960,7 @@
         <v>93</v>
       </c>
       <c r="P102" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q102">
         <v>3.09</v>
@@ -22029,7 +22041,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ102">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR102">
         <v>1.38</v>
@@ -22360,7 +22372,7 @@
         <v>93</v>
       </c>
       <c r="P104" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q104">
         <v>3.5</v>
@@ -22566,7 +22578,7 @@
         <v>93</v>
       </c>
       <c r="P105" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q105">
         <v>3.4</v>
@@ -22647,7 +22659,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ105">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR105">
         <v>1.78</v>
@@ -22850,7 +22862,7 @@
         <v>0.6</v>
       </c>
       <c r="AP106">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ106">
         <v>0.5</v>
@@ -23184,7 +23196,7 @@
         <v>93</v>
       </c>
       <c r="P108" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q108">
         <v>3.55</v>
@@ -23265,7 +23277,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ108">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR108">
         <v>1.34</v>
@@ -23468,7 +23480,7 @@
         <v>3</v>
       </c>
       <c r="AP109">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ109">
         <v>2.5</v>
@@ -23596,7 +23608,7 @@
         <v>93</v>
       </c>
       <c r="P110" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q110">
         <v>2.45</v>
@@ -23677,7 +23689,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ110">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AR110">
         <v>2.29</v>
@@ -24008,7 +24020,7 @@
         <v>93</v>
       </c>
       <c r="P112" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q112">
         <v>2.96</v>
@@ -24292,7 +24304,7 @@
         <v>1.4</v>
       </c>
       <c r="AP113">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ113">
         <v>1.57</v>
@@ -24420,7 +24432,7 @@
         <v>167</v>
       </c>
       <c r="P114" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q114">
         <v>2.88</v>
@@ -24626,7 +24638,7 @@
         <v>168</v>
       </c>
       <c r="P115" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q115">
         <v>3.08</v>
@@ -24832,7 +24844,7 @@
         <v>105</v>
       </c>
       <c r="P116" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -25528,7 +25540,7 @@
         <v>0.6</v>
       </c>
       <c r="AP119">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AQ119">
         <v>0.57</v>
@@ -25656,7 +25668,7 @@
         <v>93</v>
       </c>
       <c r="P120" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q120">
         <v>4.47</v>
@@ -25737,7 +25749,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ120">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AR120">
         <v>1.55</v>
@@ -25862,7 +25874,7 @@
         <v>171</v>
       </c>
       <c r="P121" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q121">
         <v>2.8</v>
@@ -25943,7 +25955,7 @@
         <v>2.43</v>
       </c>
       <c r="AQ121">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>1.43</v>
@@ -26068,7 +26080,7 @@
         <v>113</v>
       </c>
       <c r="P122" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26149,7 +26161,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ122">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR122">
         <v>1.58</v>
@@ -26352,7 +26364,7 @@
         <v>0.8</v>
       </c>
       <c r="AP123">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AQ123">
         <v>0.71</v>
@@ -26480,7 +26492,7 @@
         <v>93</v>
       </c>
       <c r="P124" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q124">
         <v>3.17</v>
@@ -26892,7 +26904,7 @@
         <v>95</v>
       </c>
       <c r="P126" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q126">
         <v>1.96</v>
@@ -26970,7 +26982,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AQ126">
         <v>1</v>
@@ -27098,7 +27110,7 @@
         <v>93</v>
       </c>
       <c r="P127" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q127">
         <v>3.25</v>
@@ -27510,7 +27522,7 @@
         <v>175</v>
       </c>
       <c r="P129" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q129">
         <v>2.84</v>
@@ -27922,7 +27934,7 @@
         <v>93</v>
       </c>
       <c r="P131" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q131">
         <v>2.9</v>
@@ -28128,7 +28140,7 @@
         <v>168</v>
       </c>
       <c r="P132" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q132">
         <v>3.3</v>
@@ -28334,7 +28346,7 @@
         <v>136</v>
       </c>
       <c r="P133" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q133">
         <v>2.82</v>
@@ -28639,16 +28651,16 @@
         <v>0</v>
       </c>
       <c r="AW134">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AX134">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY134">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ134">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA134">
         <v>9</v>
@@ -28845,16 +28857,16 @@
         <v>4</v>
       </c>
       <c r="AW135">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AX135">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY135">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AZ135">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA135">
         <v>6</v>
@@ -29109,6 +29121,1036 @@
       </c>
       <c r="BP136">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7834456</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45858.66666666666</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137" t="s">
+        <v>74</v>
+      </c>
+      <c r="H137" t="s">
+        <v>71</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>4</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>4</v>
+      </c>
+      <c r="O137" t="s">
+        <v>179</v>
+      </c>
+      <c r="P137" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q137">
+        <v>1.72</v>
+      </c>
+      <c r="R137">
+        <v>2.35</v>
+      </c>
+      <c r="S137">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="T137">
+        <v>1.32</v>
+      </c>
+      <c r="U137">
+        <v>3</v>
+      </c>
+      <c r="V137">
+        <v>2.65</v>
+      </c>
+      <c r="W137">
+        <v>1.41</v>
+      </c>
+      <c r="X137">
+        <v>5.8</v>
+      </c>
+      <c r="Y137">
+        <v>1.07</v>
+      </c>
+      <c r="Z137">
+        <v>1.33</v>
+      </c>
+      <c r="AA137">
+        <v>5</v>
+      </c>
+      <c r="AB137">
+        <v>11</v>
+      </c>
+      <c r="AC137">
+        <v>1.02</v>
+      </c>
+      <c r="AD137">
+        <v>10</v>
+      </c>
+      <c r="AE137">
+        <v>1.29</v>
+      </c>
+      <c r="AF137">
+        <v>3.75</v>
+      </c>
+      <c r="AG137">
+        <v>1.75</v>
+      </c>
+      <c r="AH137">
+        <v>1.95</v>
+      </c>
+      <c r="AI137">
+        <v>2.25</v>
+      </c>
+      <c r="AJ137">
+        <v>1.57</v>
+      </c>
+      <c r="AK137">
+        <v>1.17</v>
+      </c>
+      <c r="AL137">
+        <v>1.17</v>
+      </c>
+      <c r="AM137">
+        <v>3.4</v>
+      </c>
+      <c r="AN137">
+        <v>2.71</v>
+      </c>
+      <c r="AO137">
+        <v>0</v>
+      </c>
+      <c r="AP137">
+        <v>2.75</v>
+      </c>
+      <c r="AQ137">
+        <v>0</v>
+      </c>
+      <c r="AR137">
+        <v>1.73</v>
+      </c>
+      <c r="AS137">
+        <v>0.85</v>
+      </c>
+      <c r="AT137">
+        <v>2.58</v>
+      </c>
+      <c r="AU137">
+        <v>8</v>
+      </c>
+      <c r="AV137">
+        <v>2</v>
+      </c>
+      <c r="AW137">
+        <v>7</v>
+      </c>
+      <c r="AX137">
+        <v>4</v>
+      </c>
+      <c r="AY137">
+        <v>15</v>
+      </c>
+      <c r="AZ137">
+        <v>6</v>
+      </c>
+      <c r="BA137">
+        <v>8</v>
+      </c>
+      <c r="BB137">
+        <v>3</v>
+      </c>
+      <c r="BC137">
+        <v>11</v>
+      </c>
+      <c r="BD137">
+        <v>1.17</v>
+      </c>
+      <c r="BE137">
+        <v>10</v>
+      </c>
+      <c r="BF137">
+        <v>8</v>
+      </c>
+      <c r="BG137">
+        <v>1.13</v>
+      </c>
+      <c r="BH137">
+        <v>4.1</v>
+      </c>
+      <c r="BI137">
+        <v>1.31</v>
+      </c>
+      <c r="BJ137">
+        <v>3.02</v>
+      </c>
+      <c r="BK137">
+        <v>1.5</v>
+      </c>
+      <c r="BL137">
+        <v>2.4</v>
+      </c>
+      <c r="BM137">
+        <v>1.8</v>
+      </c>
+      <c r="BN137">
+        <v>1.91</v>
+      </c>
+      <c r="BO137">
+        <v>2.25</v>
+      </c>
+      <c r="BP137">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7834458</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45858.66666666666</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138" t="s">
+        <v>86</v>
+      </c>
+      <c r="H138" t="s">
+        <v>79</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="L138">
+        <v>1</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
+      <c r="O138" t="s">
+        <v>180</v>
+      </c>
+      <c r="P138" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q138">
+        <v>3.5</v>
+      </c>
+      <c r="R138">
+        <v>1.91</v>
+      </c>
+      <c r="S138">
+        <v>3.34</v>
+      </c>
+      <c r="T138">
+        <v>1.5</v>
+      </c>
+      <c r="U138">
+        <v>2.3</v>
+      </c>
+      <c r="V138">
+        <v>3.25</v>
+      </c>
+      <c r="W138">
+        <v>1.29</v>
+      </c>
+      <c r="X138">
+        <v>8.5</v>
+      </c>
+      <c r="Y138">
+        <v>1.03</v>
+      </c>
+      <c r="Z138">
+        <v>2.54</v>
+      </c>
+      <c r="AA138">
+        <v>2.77</v>
+      </c>
+      <c r="AB138">
+        <v>2.7</v>
+      </c>
+      <c r="AC138">
+        <v>1.1</v>
+      </c>
+      <c r="AD138">
+        <v>6.5</v>
+      </c>
+      <c r="AE138">
+        <v>1.5</v>
+      </c>
+      <c r="AF138">
+        <v>2.4</v>
+      </c>
+      <c r="AG138">
+        <v>2.5</v>
+      </c>
+      <c r="AH138">
+        <v>1.5</v>
+      </c>
+      <c r="AI138">
+        <v>2.04</v>
+      </c>
+      <c r="AJ138">
+        <v>1.75</v>
+      </c>
+      <c r="AK138">
+        <v>1.36</v>
+      </c>
+      <c r="AL138">
+        <v>1.35</v>
+      </c>
+      <c r="AM138">
+        <v>1.44</v>
+      </c>
+      <c r="AN138">
+        <v>1.33</v>
+      </c>
+      <c r="AO138">
+        <v>2.17</v>
+      </c>
+      <c r="AP138">
+        <v>1.57</v>
+      </c>
+      <c r="AQ138">
+        <v>1.86</v>
+      </c>
+      <c r="AR138">
+        <v>1.57</v>
+      </c>
+      <c r="AS138">
+        <v>1.49</v>
+      </c>
+      <c r="AT138">
+        <v>3.06</v>
+      </c>
+      <c r="AU138">
+        <v>3</v>
+      </c>
+      <c r="AV138">
+        <v>4</v>
+      </c>
+      <c r="AW138">
+        <v>4</v>
+      </c>
+      <c r="AX138">
+        <v>8</v>
+      </c>
+      <c r="AY138">
+        <v>7</v>
+      </c>
+      <c r="AZ138">
+        <v>12</v>
+      </c>
+      <c r="BA138">
+        <v>2</v>
+      </c>
+      <c r="BB138">
+        <v>5</v>
+      </c>
+      <c r="BC138">
+        <v>7</v>
+      </c>
+      <c r="BD138">
+        <v>1.8</v>
+      </c>
+      <c r="BE138">
+        <v>8</v>
+      </c>
+      <c r="BF138">
+        <v>2.4</v>
+      </c>
+      <c r="BG138">
+        <v>1.15</v>
+      </c>
+      <c r="BH138">
+        <v>4.75</v>
+      </c>
+      <c r="BI138">
+        <v>1.28</v>
+      </c>
+      <c r="BJ138">
+        <v>3.34</v>
+      </c>
+      <c r="BK138">
+        <v>1.55</v>
+      </c>
+      <c r="BL138">
+        <v>2.45</v>
+      </c>
+      <c r="BM138">
+        <v>1.8</v>
+      </c>
+      <c r="BN138">
+        <v>1.71</v>
+      </c>
+      <c r="BO138">
+        <v>2.25</v>
+      </c>
+      <c r="BP138">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7834460</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45858.72916666666</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139" t="s">
+        <v>85</v>
+      </c>
+      <c r="H139" t="s">
+        <v>82</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139" t="s">
+        <v>93</v>
+      </c>
+      <c r="P139" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q139">
+        <v>4.17</v>
+      </c>
+      <c r="R139">
+        <v>1.98</v>
+      </c>
+      <c r="S139">
+        <v>2.7</v>
+      </c>
+      <c r="T139">
+        <v>1.55</v>
+      </c>
+      <c r="U139">
+        <v>2.4</v>
+      </c>
+      <c r="V139">
+        <v>3.34</v>
+      </c>
+      <c r="W139">
+        <v>1.26</v>
+      </c>
+      <c r="X139">
+        <v>8.5</v>
+      </c>
+      <c r="Y139">
+        <v>1.04</v>
+      </c>
+      <c r="Z139">
+        <v>3.75</v>
+      </c>
+      <c r="AA139">
+        <v>3.2</v>
+      </c>
+      <c r="AB139">
+        <v>2.05</v>
+      </c>
+      <c r="AC139">
+        <v>1.08</v>
+      </c>
+      <c r="AD139">
+        <v>7</v>
+      </c>
+      <c r="AE139">
+        <v>1.44</v>
+      </c>
+      <c r="AF139">
+        <v>2.5</v>
+      </c>
+      <c r="AG139">
+        <v>2.5</v>
+      </c>
+      <c r="AH139">
+        <v>1.5</v>
+      </c>
+      <c r="AI139">
+        <v>2.1</v>
+      </c>
+      <c r="AJ139">
+        <v>1.73</v>
+      </c>
+      <c r="AK139">
+        <v>1.35</v>
+      </c>
+      <c r="AL139">
+        <v>1.34</v>
+      </c>
+      <c r="AM139">
+        <v>1.29</v>
+      </c>
+      <c r="AN139">
+        <v>0.4</v>
+      </c>
+      <c r="AO139">
+        <v>1.14</v>
+      </c>
+      <c r="AP139">
+        <v>0.33</v>
+      </c>
+      <c r="AQ139">
+        <v>1.38</v>
+      </c>
+      <c r="AR139">
+        <v>1.75</v>
+      </c>
+      <c r="AS139">
+        <v>1.47</v>
+      </c>
+      <c r="AT139">
+        <v>3.22</v>
+      </c>
+      <c r="AU139">
+        <v>6</v>
+      </c>
+      <c r="AV139">
+        <v>6</v>
+      </c>
+      <c r="AW139">
+        <v>6</v>
+      </c>
+      <c r="AX139">
+        <v>7</v>
+      </c>
+      <c r="AY139">
+        <v>12</v>
+      </c>
+      <c r="AZ139">
+        <v>13</v>
+      </c>
+      <c r="BA139">
+        <v>6</v>
+      </c>
+      <c r="BB139">
+        <v>4</v>
+      </c>
+      <c r="BC139">
+        <v>10</v>
+      </c>
+      <c r="BD139">
+        <v>2</v>
+      </c>
+      <c r="BE139">
+        <v>7.5</v>
+      </c>
+      <c r="BF139">
+        <v>2.15</v>
+      </c>
+      <c r="BG139">
+        <v>1.21</v>
+      </c>
+      <c r="BH139">
+        <v>3.6</v>
+      </c>
+      <c r="BI139">
+        <v>1.41</v>
+      </c>
+      <c r="BJ139">
+        <v>2.7</v>
+      </c>
+      <c r="BK139">
+        <v>1.68</v>
+      </c>
+      <c r="BL139">
+        <v>2.13</v>
+      </c>
+      <c r="BM139">
+        <v>2.09</v>
+      </c>
+      <c r="BN139">
+        <v>1.7</v>
+      </c>
+      <c r="BO139">
+        <v>2.6</v>
+      </c>
+      <c r="BP139">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7834453</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45858.72916666666</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140" t="s">
+        <v>76</v>
+      </c>
+      <c r="H140" t="s">
+        <v>83</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="K140">
+        <v>2</v>
+      </c>
+      <c r="L140">
+        <v>3</v>
+      </c>
+      <c r="M140">
+        <v>2</v>
+      </c>
+      <c r="N140">
+        <v>5</v>
+      </c>
+      <c r="O140" t="s">
+        <v>181</v>
+      </c>
+      <c r="P140" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q140">
+        <v>2.36</v>
+      </c>
+      <c r="R140">
+        <v>2.05</v>
+      </c>
+      <c r="S140">
+        <v>5.3</v>
+      </c>
+      <c r="T140">
+        <v>1.5</v>
+      </c>
+      <c r="U140">
+        <v>2.4</v>
+      </c>
+      <c r="V140">
+        <v>3.34</v>
+      </c>
+      <c r="W140">
+        <v>1.26</v>
+      </c>
+      <c r="X140">
+        <v>8.5</v>
+      </c>
+      <c r="Y140">
+        <v>1.04</v>
+      </c>
+      <c r="Z140">
+        <v>1.69</v>
+      </c>
+      <c r="AA140">
+        <v>3.59</v>
+      </c>
+      <c r="AB140">
+        <v>5.85</v>
+      </c>
+      <c r="AC140">
+        <v>1.08</v>
+      </c>
+      <c r="AD140">
+        <v>7</v>
+      </c>
+      <c r="AE140">
+        <v>1.44</v>
+      </c>
+      <c r="AF140">
+        <v>2.63</v>
+      </c>
+      <c r="AG140">
+        <v>2.35</v>
+      </c>
+      <c r="AH140">
+        <v>1.57</v>
+      </c>
+      <c r="AI140">
+        <v>2.32</v>
+      </c>
+      <c r="AJ140">
+        <v>1.59</v>
+      </c>
+      <c r="AK140">
+        <v>1.3</v>
+      </c>
+      <c r="AL140">
+        <v>1.28</v>
+      </c>
+      <c r="AM140">
+        <v>2.1</v>
+      </c>
+      <c r="AN140">
+        <v>1.33</v>
+      </c>
+      <c r="AO140">
+        <v>1.14</v>
+      </c>
+      <c r="AP140">
+        <v>1.57</v>
+      </c>
+      <c r="AQ140">
+        <v>1</v>
+      </c>
+      <c r="AR140">
+        <v>1.72</v>
+      </c>
+      <c r="AS140">
+        <v>1.8</v>
+      </c>
+      <c r="AT140">
+        <v>3.52</v>
+      </c>
+      <c r="AU140">
+        <v>8</v>
+      </c>
+      <c r="AV140">
+        <v>4</v>
+      </c>
+      <c r="AW140">
+        <v>5</v>
+      </c>
+      <c r="AX140">
+        <v>3</v>
+      </c>
+      <c r="AY140">
+        <v>13</v>
+      </c>
+      <c r="AZ140">
+        <v>7</v>
+      </c>
+      <c r="BA140">
+        <v>9</v>
+      </c>
+      <c r="BB140">
+        <v>0</v>
+      </c>
+      <c r="BC140">
+        <v>9</v>
+      </c>
+      <c r="BD140">
+        <v>1.37</v>
+      </c>
+      <c r="BE140">
+        <v>7</v>
+      </c>
+      <c r="BF140">
+        <v>3.4</v>
+      </c>
+      <c r="BG140">
+        <v>1.16</v>
+      </c>
+      <c r="BH140">
+        <v>4.55</v>
+      </c>
+      <c r="BI140">
+        <v>1.28</v>
+      </c>
+      <c r="BJ140">
+        <v>3.08</v>
+      </c>
+      <c r="BK140">
+        <v>1.54</v>
+      </c>
+      <c r="BL140">
+        <v>2.33</v>
+      </c>
+      <c r="BM140">
+        <v>1.87</v>
+      </c>
+      <c r="BN140">
+        <v>1.87</v>
+      </c>
+      <c r="BO140">
+        <v>2.55</v>
+      </c>
+      <c r="BP140">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7834451</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45858.8125</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141" t="s">
+        <v>75</v>
+      </c>
+      <c r="H141" t="s">
+        <v>84</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141" t="s">
+        <v>182</v>
+      </c>
+      <c r="P141" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q141">
+        <v>2.45</v>
+      </c>
+      <c r="R141">
+        <v>2</v>
+      </c>
+      <c r="S141">
+        <v>5.6</v>
+      </c>
+      <c r="T141">
+        <v>1.42</v>
+      </c>
+      <c r="U141">
+        <v>2.34</v>
+      </c>
+      <c r="V141">
+        <v>3.5</v>
+      </c>
+      <c r="W141">
+        <v>1.35</v>
+      </c>
+      <c r="X141">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y141">
+        <v>1</v>
+      </c>
+      <c r="Z141">
+        <v>1.6</v>
+      </c>
+      <c r="AA141">
+        <v>3.41</v>
+      </c>
+      <c r="AB141">
+        <v>4.9</v>
+      </c>
+      <c r="AC141">
+        <v>1.07</v>
+      </c>
+      <c r="AD141">
+        <v>6.75</v>
+      </c>
+      <c r="AE141">
+        <v>1.5</v>
+      </c>
+      <c r="AF141">
+        <v>2.4</v>
+      </c>
+      <c r="AG141">
+        <v>2.22</v>
+      </c>
+      <c r="AH141">
+        <v>1.58</v>
+      </c>
+      <c r="AI141">
+        <v>2.4</v>
+      </c>
+      <c r="AJ141">
+        <v>1.5</v>
+      </c>
+      <c r="AK141">
+        <v>1.33</v>
+      </c>
+      <c r="AL141">
+        <v>1.27</v>
+      </c>
+      <c r="AM141">
+        <v>2.05</v>
+      </c>
+      <c r="AN141">
+        <v>2.43</v>
+      </c>
+      <c r="AO141">
+        <v>1.17</v>
+      </c>
+      <c r="AP141">
+        <v>2.5</v>
+      </c>
+      <c r="AQ141">
+        <v>1</v>
+      </c>
+      <c r="AR141">
+        <v>1.98</v>
+      </c>
+      <c r="AS141">
+        <v>1.22</v>
+      </c>
+      <c r="AT141">
+        <v>3.2</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>3</v>
+      </c>
+      <c r="AW141">
+        <v>4</v>
+      </c>
+      <c r="AX141">
+        <v>3</v>
+      </c>
+      <c r="AY141">
+        <v>8</v>
+      </c>
+      <c r="AZ141">
+        <v>6</v>
+      </c>
+      <c r="BA141">
+        <v>8</v>
+      </c>
+      <c r="BB141">
+        <v>3</v>
+      </c>
+      <c r="BC141">
+        <v>11</v>
+      </c>
+      <c r="BD141">
+        <v>1.31</v>
+      </c>
+      <c r="BE141">
+        <v>7.5</v>
+      </c>
+      <c r="BF141">
+        <v>3.6</v>
+      </c>
+      <c r="BG141">
+        <v>1.3</v>
+      </c>
+      <c r="BH141">
+        <v>3.22</v>
+      </c>
+      <c r="BI141">
+        <v>1.53</v>
+      </c>
+      <c r="BJ141">
+        <v>2.38</v>
+      </c>
+      <c r="BK141">
+        <v>1.8</v>
+      </c>
+      <c r="BL141">
+        <v>1.91</v>
+      </c>
+      <c r="BM141">
+        <v>2.4</v>
+      </c>
+      <c r="BN141">
+        <v>1.49</v>
+      </c>
+      <c r="BO141">
+        <v>3.07</v>
+      </c>
+      <c r="BP141">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -28239,16 +28239,16 @@
         <v>5</v>
       </c>
       <c r="AW132">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AX132">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY132">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ132">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BA132">
         <v>9</v>
@@ -28445,16 +28445,16 @@
         <v>5</v>
       </c>
       <c r="AW133">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AX133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY133">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AZ133">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA133">
         <v>12</v>
@@ -28651,16 +28651,16 @@
         <v>0</v>
       </c>
       <c r="AW134">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX134">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY134">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AZ134">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA134">
         <v>9</v>
@@ -28857,16 +28857,16 @@
         <v>4</v>
       </c>
       <c r="AW135">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AX135">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY135">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ135">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA135">
         <v>6</v>
@@ -29269,16 +29269,16 @@
         <v>2</v>
       </c>
       <c r="AW137">
+        <v>9</v>
+      </c>
+      <c r="AX137">
+        <v>5</v>
+      </c>
+      <c r="AY137">
+        <v>17</v>
+      </c>
+      <c r="AZ137">
         <v>7</v>
-      </c>
-      <c r="AX137">
-        <v>4</v>
-      </c>
-      <c r="AY137">
-        <v>15</v>
-      </c>
-      <c r="AZ137">
-        <v>6</v>
       </c>
       <c r="BA137">
         <v>8</v>
@@ -29475,16 +29475,16 @@
         <v>4</v>
       </c>
       <c r="AW138">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX138">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY138">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ138">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA138">
         <v>2</v>
@@ -29681,16 +29681,16 @@
         <v>6</v>
       </c>
       <c r="AW139">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX139">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY139">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ139">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA139">
         <v>6</v>
@@ -29887,13 +29887,13 @@
         <v>4</v>
       </c>
       <c r="AW140">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AX140">
         <v>3</v>
       </c>
       <c r="AY140">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AZ140">
         <v>7</v>
@@ -30093,16 +30093,16 @@
         <v>3</v>
       </c>
       <c r="AW141">
+        <v>6</v>
+      </c>
+      <c r="AX141">
         <v>4</v>
       </c>
-      <c r="AX141">
-        <v>3</v>
-      </c>
       <c r="AY141">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ141">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA141">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -28934,7 +28934,7 @@
         <v>45858.45833333334</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G136" t="s">
         <v>88</v>
@@ -29063,16 +29063,16 @@
         <v>4</v>
       </c>
       <c r="AW136">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX136">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY136">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ136">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA136">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Brazil Serie A_2025.xlsx
@@ -29063,16 +29063,16 @@
         <v>4</v>
       </c>
       <c r="AW136">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX136">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY136">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AZ136">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA136">
         <v>7</v>
@@ -29140,7 +29140,7 @@
         <v>45858.66666666666</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G137" t="s">
         <v>74</v>
@@ -29346,7 +29346,7 @@
         <v>45858.66666666666</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G138" t="s">
         <v>86</v>
@@ -29552,7 +29552,7 @@
         <v>45858.72916666666</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G139" t="s">
         <v>85</v>
@@ -29758,7 +29758,7 @@
         <v>45858.72916666666</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G140" t="s">
         <v>76</v>
@@ -29964,7 +29964,7 @@
         <v>45858.8125</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G141" t="s">
         <v>75</v>
